--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Player Dojo</t>
+  </si>
+  <si>
+    <t>Metadata</t>
   </si>
   <si>
     <t>Kevin Clark</t>
@@ -439,7 +442,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -514,33 +517,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -762,8 +738,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="true"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="4" min="2" width="30"/>
-    <col customWidth="true" max="26" min="5" width="10.6640625"/>
+    <col customWidth="true" max="26" min="2" width="30"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="true">
@@ -776,16 +751,19 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
@@ -793,10 +771,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
@@ -804,10 +782,10 @@
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
@@ -815,10 +793,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
@@ -826,10 +804,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -837,10 +815,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
@@ -848,10 +826,10 @@
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
@@ -859,10 +837,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
@@ -870,10 +848,10 @@
         <v>8</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
@@ -881,10 +859,10 @@
         <v>9</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -1975,11 +1953,9 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="1"/>
-    <row r="2"/>
     <row r="3">
       <c r="E3" s="24" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -1998,7 +1974,7 @@
     </row>
     <row r="7">
       <c r="E7" s="24" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="20"/>
@@ -2019,7 +1995,7 @@
     </row>
     <row r="11">
       <c r="E11" s="24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I11" s="20"/>
       <c r="K11" s="20"/>
@@ -2040,7 +2016,7 @@
     </row>
     <row r="14">
       <c r="C14" s="24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G14" s="20"/>
       <c r="K14" s="20"/>
@@ -2056,7 +2032,7 @@
     </row>
     <row r="16">
       <c r="C16" s="24" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D16" s="23"/>
       <c r="E16" s="20"/>
@@ -2072,7 +2048,7 @@
     </row>
     <row r="19">
       <c r="E19" s="24" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K19" s="20"/>
     </row>
@@ -2095,7 +2071,7 @@
     </row>
     <row r="23">
       <c r="E23" s="24" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F23" s="23"/>
       <c r="G23" s="20"/>
@@ -2118,7 +2094,7 @@
     </row>
     <row r="27">
       <c r="E27" s="24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I27" s="20"/>
     </row>
@@ -2136,7 +2112,7 @@
     </row>
     <row r="30">
       <c r="C30" s="24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G30" s="20"/>
     </row>
@@ -2150,7 +2126,7 @@
     </row>
     <row r="32">
       <c r="C32" s="24" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D32" s="23"/>
       <c r="E32" s="20"/>
@@ -2406,10 +2382,9 @@
       <c r="N1" s="27"/>
       <c r="O1" s="27"/>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" s="27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B3" s="27"/>
       <c r="C3" s="27"/>
@@ -2418,7 +2393,7 @@
       <c r="F3" s="27"/>
       <c r="G3" s="27"/>
       <c r="I3" s="27" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J3" s="27"/>
       <c r="K3" s="27"/>
@@ -2429,22 +2404,22 @@
     </row>
     <row r="4">
       <c r="A4" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" t="s">
+        <v>33</v>
+      </c>
+      <c r="I4" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="L4" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="I4" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="O4" s="31" t="s">
-        <v>32</v>
+      <c r="O4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
@@ -2591,23 +2566,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="29" t="str">
         <f>'data'!$B$5</f>
       </c>
       <c r="B12" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D12" s="29"/>
       <c r="E12" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F12" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="F12" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="G12" s="29" t="str">
         <f>'data'!$B$6</f>
@@ -2616,17 +2590,17 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="J12" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K12" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L12" s="29"/>
       <c r="M12" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="N12" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="N12" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="O12" s="29" t="str">
         <f>'data'!$B$11</f>
@@ -2634,7 +2608,7 @@
     </row>
     <row r="13">
       <c r="A13" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B13" s="29"/>
       <c r="C13" s="29"/>
@@ -2642,10 +2616,10 @@
       <c r="E13" s="29"/>
       <c r="F13" s="29"/>
       <c r="G13" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I13" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J13" s="29"/>
       <c r="K13" s="29"/>
@@ -2653,40 +2627,32 @@
       <c r="M13" s="29"/>
       <c r="N13" s="29"/>
       <c r="O13" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14"/>
+        <v>36</v>
+      </c>
+    </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G15" s="23"/>
       <c r="N15" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O15" s="23"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G16" s="23"/>
       <c r="N16" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O16" s="23"/>
     </row>
-    <row r="17"/>
-    <row r="18"/>
-    <row r="19"/>
-    <row r="20"/>
-    <row r="21"/>
-    <row r="22"/>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="27" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="27"/>
       <c r="C24" s="27"/>
@@ -2703,10 +2669,9 @@
       <c r="N24" s="27"/>
       <c r="O24" s="27"/>
     </row>
-    <row r="25"/>
     <row r="26">
       <c r="A26" s="27" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B26" s="27"/>
       <c r="C26" s="27"/>
@@ -2715,7 +2680,7 @@
       <c r="F26" s="27"/>
       <c r="G26" s="27"/>
       <c r="I26" s="27" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J26" s="27"/>
       <c r="K26" s="27"/>
@@ -2726,22 +2691,22 @@
     </row>
     <row r="27">
       <c r="A27" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D27" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G27" t="s">
+        <v>33</v>
+      </c>
+      <c r="I27" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G27" s="32" t="s">
+      <c r="L27" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="I27" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="L27" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="O27" s="33" t="s">
-        <v>32</v>
+      <c r="O27" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="28">
@@ -2888,23 +2853,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34"/>
     <row r="35">
       <c r="A35" s="29" t="str">
         <f>'data'!$B$2</f>
       </c>
       <c r="B35" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C35" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D35" s="29"/>
       <c r="E35" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F35" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="F35" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="G35" s="29" t="str">
         <f>'data'!$B$3</f>
@@ -2913,17 +2877,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="J35" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K35" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L35" s="29"/>
       <c r="M35" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="N35" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="N35" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="O35" s="29" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
@@ -2931,7 +2895,7 @@
     </row>
     <row r="36">
       <c r="A36" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B36" s="29"/>
       <c r="C36" s="29"/>
@@ -2939,10 +2903,10 @@
       <c r="E36" s="29"/>
       <c r="F36" s="29"/>
       <c r="G36" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I36" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J36" s="29"/>
       <c r="K36" s="29"/>
@@ -2950,35 +2914,32 @@
       <c r="M36" s="29"/>
       <c r="N36" s="29"/>
       <c r="O36" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37"/>
+        <v>36</v>
+      </c>
+    </row>
     <row r="38">
       <c r="F38" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G38" s="23"/>
       <c r="N38" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O38" s="23"/>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G39" s="23"/>
       <c r="N39" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O39" s="23"/>
     </row>
-    <row r="40"/>
-    <row r="41"/>
     <row r="42">
       <c r="A42" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B42" s="27"/>
       <c r="C42" s="27"/>
@@ -2987,7 +2948,7 @@
       <c r="F42" s="27"/>
       <c r="G42" s="27"/>
       <c r="I42" s="27" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J42" s="27"/>
       <c r="K42" s="27"/>
@@ -2998,22 +2959,22 @@
     </row>
     <row r="43">
       <c r="A43" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D43" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G43" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G43" s="34" t="s">
+      <c r="L43" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="I43" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="L43" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="O43" s="35" t="s">
-        <v>32</v>
+      <c r="O43" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="44">
@@ -3160,23 +3121,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50"/>
     <row r="51">
       <c r="A51" s="29" t="str">
         <f>'data'!$B$7</f>
       </c>
       <c r="B51" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C51" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D51" s="29"/>
       <c r="E51" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F51" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="F51" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="G51" s="29" t="str">
         <f>'data'!$B$8</f>
@@ -3185,17 +3145,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="J51" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K51" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L51" s="29"/>
       <c r="M51" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="N51" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="N51" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="O51" s="29" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
@@ -3203,7 +3163,7 @@
     </row>
     <row r="52">
       <c r="A52" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B52" s="29"/>
       <c r="C52" s="29"/>
@@ -3211,10 +3171,10 @@
       <c r="E52" s="29"/>
       <c r="F52" s="29"/>
       <c r="G52" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I52" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J52" s="29"/>
       <c r="K52" s="29"/>
@@ -3222,40 +3182,32 @@
       <c r="M52" s="29"/>
       <c r="N52" s="29"/>
       <c r="O52" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="53"/>
+        <v>36</v>
+      </c>
+    </row>
     <row r="54">
       <c r="F54" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G54" s="23"/>
       <c r="N54" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O54" s="23"/>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G55" s="23"/>
       <c r="N55" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O55" s="23"/>
     </row>
-    <row r="56"/>
-    <row r="57"/>
-    <row r="58"/>
-    <row r="59"/>
-    <row r="60"/>
-    <row r="61"/>
-    <row r="62"/>
     <row r="63">
       <c r="A63" s="27" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B63" s="27"/>
       <c r="C63" s="27"/>
@@ -3272,10 +3224,9 @@
       <c r="N63" s="27"/>
       <c r="O63" s="27"/>
     </row>
-    <row r="64"/>
     <row r="65">
       <c r="A65" s="27" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B65" s="27"/>
       <c r="C65" s="27"/>
@@ -3284,7 +3235,7 @@
       <c r="F65" s="27"/>
       <c r="G65" s="27"/>
       <c r="I65" s="27" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="J65" s="27"/>
       <c r="K65" s="27"/>
@@ -3295,22 +3246,22 @@
     </row>
     <row r="66">
       <c r="A66" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D66" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="G66" t="s">
+        <v>33</v>
+      </c>
+      <c r="I66" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="G66" s="36" t="s">
+      <c r="L66" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="I66" s="28" t="s">
-        <v>30</v>
-      </c>
-      <c r="L66" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="O66" s="37" t="s">
-        <v>32</v>
+      <c r="O66" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="67">
@@ -3457,23 +3408,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73"/>
     <row r="74">
       <c r="A74" s="29" t="str">
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="B74" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C74" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D74" s="29"/>
       <c r="E74" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F74" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="F74" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="G74" s="29" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
@@ -3482,17 +3432,17 @@
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
       <c r="J74" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K74" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L74" s="29"/>
       <c r="M74" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="N74" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="N74" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="O74" s="29" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
@@ -3500,7 +3450,7 @@
     </row>
     <row r="75">
       <c r="A75" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B75" s="29"/>
       <c r="C75" s="29"/>
@@ -3508,10 +3458,10 @@
       <c r="E75" s="29"/>
       <c r="F75" s="29"/>
       <c r="G75" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I75" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J75" s="29"/>
       <c r="K75" s="29"/>
@@ -3519,40 +3469,32 @@
       <c r="M75" s="29"/>
       <c r="N75" s="29"/>
       <c r="O75" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="76"/>
+        <v>36</v>
+      </c>
+    </row>
     <row r="77">
       <c r="F77" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G77" s="23"/>
       <c r="N77" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O77" s="23"/>
     </row>
     <row r="78">
       <c r="F78" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G78" s="23"/>
       <c r="N78" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O78" s="23"/>
     </row>
-    <row r="79"/>
-    <row r="80"/>
-    <row r="81"/>
-    <row r="82"/>
-    <row r="83"/>
-    <row r="84"/>
-    <row r="85"/>
     <row r="86">
       <c r="A86" s="27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B86" s="27"/>
       <c r="C86" s="27"/>
@@ -3569,10 +3511,9 @@
       <c r="N86" s="27"/>
       <c r="O86" s="27"/>
     </row>
-    <row r="87"/>
     <row r="88">
       <c r="A88" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B88" s="27"/>
       <c r="C88" s="27"/>
@@ -3583,13 +3524,13 @@
     </row>
     <row r="89">
       <c r="A89" s="28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D89" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G89" s="38" t="s">
         <v>32</v>
+      </c>
+      <c r="G89" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="90">
@@ -3670,23 +3611,22 @@
         <v>5</v>
       </c>
     </row>
-    <row r="96"/>
     <row r="97">
       <c r="A97" s="29" t="str">
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
       <c r="B97" s="29" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D97" s="29"/>
       <c r="E97" s="29" t="s">
+        <v>35</v>
+      </c>
+      <c r="F97" s="29" t="s">
         <v>34</v>
-      </c>
-      <c r="F97" s="29" t="s">
-        <v>33</v>
       </c>
       <c r="G97" s="29" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
@@ -3694,7 +3634,7 @@
     </row>
     <row r="98">
       <c r="A98" s="29" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B98" s="29"/>
       <c r="C98" s="29"/>
@@ -3702,19 +3642,18 @@
       <c r="E98" s="29"/>
       <c r="F98" s="29"/>
       <c r="G98" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="99"/>
+        <v>36</v>
+      </c>
+    </row>
     <row r="100">
       <c r="F100" s="7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G100" s="23"/>
     </row>
     <row r="101">
       <c r="F101" s="7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G101" s="23"/>
     </row>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -18,7 +18,9 @@
     <sheet name="Names to Print" sheetId="8" r:id="rId6"/>
     <sheet name="Tree 1" sheetId="10" r:id="rId13"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$20</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -308,7 +310,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -324,6 +326,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -442,7 +449,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -513,10 +520,13 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1953,183 +1963,183 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
-    <row r="3">
-      <c r="E3" s="24" t="s">
+    <row r="6">
+      <c r="E6" s="24" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="4">
-      <c r="F4" s="22"/>
-      <c r="G4" s="20"/>
-    </row>
-    <row r="5">
-      <c r="G5" s="21">
+    <row r="7">
+      <c r="F7" s="22"/>
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8">
+      <c r="G8" s="21">
         <v>3</v>
       </c>
     </row>
-    <row r="6">
-      <c r="G6" s="20"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="20"/>
-    </row>
-    <row r="7">
-      <c r="E7" s="24" t="s">
+    <row r="9">
+      <c r="G9" s="20"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="20"/>
+    </row>
+    <row r="10">
+      <c r="E10" s="24" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="23"/>
-      <c r="G7" s="20"/>
-      <c r="I7" s="20"/>
-    </row>
-    <row r="8">
-      <c r="I8" s="20"/>
-    </row>
-    <row r="9">
-      <c r="I9" s="21">
+      <c r="F10" s="23"/>
+      <c r="G10" s="20"/>
+      <c r="I10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="I11" s="20"/>
+    </row>
+    <row r="12">
+      <c r="I12" s="21">
         <v>7</v>
       </c>
     </row>
-    <row r="10">
-      <c r="I10" s="20"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="20"/>
-    </row>
-    <row r="11">
-      <c r="E11" s="24" t="s">
+    <row r="13">
+      <c r="I13" s="20"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14">
+      <c r="E14" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="I11" s="20"/>
-      <c r="K11" s="20"/>
-    </row>
-    <row r="12">
-      <c r="F12" s="22"/>
-      <c r="G12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="K12" s="20"/>
-    </row>
-    <row r="13">
-      <c r="G13" s="21">
+      <c r="I14" s="20"/>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="F15" s="22"/>
+      <c r="G15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="K15" s="20"/>
+    </row>
+    <row r="16">
+      <c r="G16" s="21">
         <v>4</v>
       </c>
-      <c r="H13" s="23"/>
-      <c r="I13" s="20"/>
-      <c r="K13" s="20"/>
-    </row>
-    <row r="14">
-      <c r="C14" s="24" t="s">
+      <c r="H16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="K16" s="20"/>
+    </row>
+    <row r="17">
+      <c r="C17" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="20"/>
-      <c r="K14" s="20"/>
-    </row>
-    <row r="15">
-      <c r="D15" s="22"/>
-      <c r="E15" s="21">
+      <c r="G17" s="20"/>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18">
+      <c r="D18" s="22"/>
+      <c r="E18" s="21">
         <v>1</v>
       </c>
-      <c r="F15" s="23"/>
-      <c r="G15" s="20"/>
-      <c r="K15" s="20"/>
-    </row>
-    <row r="16">
-      <c r="C16" s="24" t="s">
+      <c r="F18" s="23"/>
+      <c r="G18" s="20"/>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="C19" s="24" t="s">
         <v>23</v>
       </c>
-      <c r="D16" s="23"/>
-      <c r="E16" s="20"/>
-      <c r="K16" s="20"/>
-    </row>
-    <row r="17">
-      <c r="K17" s="21">
+      <c r="D19" s="23"/>
+      <c r="E19" s="20"/>
+      <c r="K19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="K20" s="21">
         <v>9</v>
       </c>
     </row>
-    <row r="18">
-      <c r="K18" s="20"/>
-    </row>
-    <row r="19">
-      <c r="E19" s="24" t="s">
+    <row r="21">
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="E22" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="K19" s="20"/>
-    </row>
-    <row r="20">
-      <c r="F20" s="22"/>
-      <c r="G20" s="20"/>
-      <c r="K20" s="20"/>
-    </row>
-    <row r="21">
-      <c r="G21" s="21">
+      <c r="K22" s="20"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="22"/>
+      <c r="G23" s="20"/>
+      <c r="K23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="21">
         <v>5</v>
       </c>
-      <c r="K21" s="20"/>
-    </row>
-    <row r="22">
-      <c r="G22" s="20"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="20"/>
-      <c r="K22" s="20"/>
-    </row>
-    <row r="23">
-      <c r="E23" s="24" t="s">
+      <c r="K24" s="20"/>
+    </row>
+    <row r="25">
+      <c r="G25" s="20"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="20"/>
+      <c r="K25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="F23" s="23"/>
-      <c r="G23" s="20"/>
-      <c r="I23" s="20"/>
-      <c r="K23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="I24" s="20"/>
-      <c r="K24" s="20"/>
-    </row>
-    <row r="25">
-      <c r="I25" s="21">
+      <c r="F26" s="23"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20"/>
+      <c r="K26" s="20"/>
+    </row>
+    <row r="27">
+      <c r="I27" s="20"/>
+      <c r="K27" s="20"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="21">
         <v>8</v>
       </c>
-      <c r="J25" s="23"/>
-      <c r="K25" s="20"/>
-    </row>
-    <row r="26">
-      <c r="I26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="E27" s="24" t="s">
+      <c r="J28" s="23"/>
+      <c r="K28" s="20"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="20"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="20"/>
-    </row>
-    <row r="28">
-      <c r="F28" s="22"/>
-      <c r="G28" s="20"/>
-      <c r="I28" s="20"/>
-    </row>
-    <row r="29">
-      <c r="G29" s="21">
+      <c r="I30" s="20"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="22"/>
+      <c r="G31" s="20"/>
+      <c r="I31" s="20"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="21">
         <v>6</v>
       </c>
-      <c r="H29" s="23"/>
-      <c r="I29" s="20"/>
-    </row>
-    <row r="30">
-      <c r="C30" s="24" t="s">
+      <c r="H32" s="23"/>
+      <c r="I32" s="20"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="20"/>
-    </row>
-    <row r="31">
-      <c r="D31" s="22"/>
-      <c r="E31" s="21">
+      <c r="G33" s="20"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="22"/>
+      <c r="E34" s="21">
         <v>2</v>
       </c>
-      <c r="F31" s="23"/>
-      <c r="G31" s="20"/>
-    </row>
-    <row r="32">
-      <c r="C32" s="24" t="s">
+      <c r="F34" s="23"/>
+      <c r="G34" s="20"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="D32" s="23"/>
-      <c r="E32" s="20"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="20"/>
     </row>
   </sheetData>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
@@ -2403,230 +2413,230 @@
       <c r="O3" s="27"/>
     </row>
     <row r="4">
-      <c r="A4" s="28" t="s">
+      <c r="A4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="28" t="s">
+      <c r="I4" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="29" t="s">
+      <c r="L4" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="O4" t="s">
+      <c r="O4" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="str">
+      <c r="A5" s="28" t="str">
         <f>'data'!$B$5</f>
       </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29" t="str">
+      <c r="B5" s="28"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28" t="str">
         <f>'data'!$B$6</f>
       </c>
-      <c r="I5" s="29" t="str">
+      <c r="I5" s="28" t="str">
         <f>'data'!$B$10</f>
       </c>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29" t="str">
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="28"/>
+      <c r="M5" s="28"/>
+      <c r="N5" s="28"/>
+      <c r="O5" s="28" t="str">
         <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="29">
+      <c r="A6" s="28">
         <v>1</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29">
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="28"/>
+      <c r="F6" s="28"/>
+      <c r="G6" s="28">
         <v>1</v>
       </c>
-      <c r="I6" s="29">
+      <c r="I6" s="28">
         <v>1</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29">
+      <c r="J6" s="28"/>
+      <c r="K6" s="28"/>
+      <c r="L6" s="28"/>
+      <c r="M6" s="28"/>
+      <c r="N6" s="28"/>
+      <c r="O6" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29">
+      <c r="A7" s="28">
         <v>2</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="29"/>
-      <c r="F7" s="29"/>
-      <c r="G7" s="29">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="28"/>
+      <c r="F7" s="28"/>
+      <c r="G7" s="28">
         <v>2</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="28">
         <v>2</v>
       </c>
-      <c r="J7" s="29"/>
-      <c r="K7" s="29"/>
-      <c r="L7" s="29"/>
-      <c r="M7" s="29"/>
-      <c r="N7" s="29"/>
-      <c r="O7" s="29">
+      <c r="J7" s="28"/>
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28"/>
+      <c r="N7" s="28"/>
+      <c r="O7" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29">
+      <c r="A8" s="28">
         <v>3</v>
       </c>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
-      <c r="D8" s="29"/>
-      <c r="E8" s="29"/>
-      <c r="F8" s="29"/>
-      <c r="G8" s="29">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="28"/>
+      <c r="F8" s="28"/>
+      <c r="G8" s="28">
         <v>3</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="28">
         <v>3</v>
       </c>
-      <c r="J8" s="29"/>
-      <c r="K8" s="29"/>
-      <c r="L8" s="29"/>
-      <c r="M8" s="29"/>
-      <c r="N8" s="29"/>
-      <c r="O8" s="29">
+      <c r="J8" s="28"/>
+      <c r="K8" s="28"/>
+      <c r="L8" s="28"/>
+      <c r="M8" s="28"/>
+      <c r="N8" s="28"/>
+      <c r="O8" s="28">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29">
+      <c r="A9" s="28">
         <v>4</v>
       </c>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="29"/>
-      <c r="F9" s="29"/>
-      <c r="G9" s="29">
+      <c r="B9" s="28"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28">
         <v>4</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="28">
         <v>4</v>
       </c>
-      <c r="J9" s="29"/>
-      <c r="K9" s="29"/>
-      <c r="L9" s="29"/>
-      <c r="M9" s="29"/>
-      <c r="N9" s="29"/>
-      <c r="O9" s="29">
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+      <c r="M9" s="28"/>
+      <c r="N9" s="28"/>
+      <c r="O9" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29">
+      <c r="A10" s="28">
         <v>5</v>
       </c>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="29"/>
-      <c r="F10" s="29"/>
-      <c r="G10" s="29">
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28">
         <v>5</v>
       </c>
-      <c r="I10" s="29">
+      <c r="I10" s="28">
         <v>5</v>
       </c>
-      <c r="J10" s="29"/>
-      <c r="K10" s="29"/>
-      <c r="L10" s="29"/>
-      <c r="M10" s="29"/>
-      <c r="N10" s="29"/>
-      <c r="O10" s="29">
+      <c r="J10" s="28"/>
+      <c r="K10" s="28"/>
+      <c r="L10" s="28"/>
+      <c r="M10" s="28"/>
+      <c r="N10" s="28"/>
+      <c r="O10" s="28">
         <v>5</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="str">
+      <c r="A12" s="28" t="str">
         <f>'data'!$B$5</f>
       </c>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="29" t="s">
+      <c r="C12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29" t="s">
+      <c r="D12" s="28"/>
+      <c r="E12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="29" t="s">
+      <c r="F12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="29" t="str">
+      <c r="G12" s="28" t="str">
         <f>'data'!$B$6</f>
       </c>
-      <c r="I12" s="29" t="str">
+      <c r="I12" s="28" t="str">
         <f>'data'!$B$10</f>
       </c>
-      <c r="J12" s="29" t="s">
+      <c r="J12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29" t="s">
+      <c r="L12" s="28"/>
+      <c r="M12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N12" s="29" t="s">
+      <c r="N12" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O12" s="29" t="str">
+      <c r="O12" s="28" t="str">
         <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="s">
+      <c r="A13" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="29"/>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29" t="s">
+      <c r="B13" s="28"/>
+      <c r="C13" s="28"/>
+      <c r="D13" s="28"/>
+      <c r="E13" s="28"/>
+      <c r="F13" s="28"/>
+      <c r="G13" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I13" s="29" t="s">
+      <c r="I13" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="29"/>
-      <c r="M13" s="29"/>
-      <c r="N13" s="29"/>
-      <c r="O13" s="29" t="s">
+      <c r="J13" s="28"/>
+      <c r="K13" s="28"/>
+      <c r="L13" s="28"/>
+      <c r="M13" s="28"/>
+      <c r="N13" s="28"/>
+      <c r="O13" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2690,230 +2700,230 @@
       <c r="O26" s="27"/>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="s">
+      <c r="A27" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D27" s="29" t="s">
+      <c r="D27" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G27" t="s">
+      <c r="G27" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="28" t="s">
+      <c r="I27" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L27" s="29" t="s">
+      <c r="L27" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="O27" t="s">
+      <c r="O27" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="str">
+      <c r="A28" s="28" t="str">
         <f>'data'!$B$2</f>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29" t="str">
+      <c r="B28" s="28"/>
+      <c r="C28" s="28"/>
+      <c r="D28" s="28"/>
+      <c r="E28" s="28"/>
+      <c r="F28" s="28"/>
+      <c r="G28" s="28" t="str">
         <f>'data'!$B$3</f>
       </c>
-      <c r="I28" s="29" t="str">
+      <c r="I28" s="28" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="J28" s="29"/>
-      <c r="K28" s="29"/>
-      <c r="L28" s="29"/>
-      <c r="M28" s="29"/>
-      <c r="N28" s="29"/>
-      <c r="O28" s="29" t="str">
+      <c r="J28" s="28"/>
+      <c r="K28" s="28"/>
+      <c r="L28" s="28"/>
+      <c r="M28" s="28"/>
+      <c r="N28" s="28"/>
+      <c r="O28" s="28" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="29">
+      <c r="A29" s="28">
         <v>1</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29">
+      <c r="B29" s="28"/>
+      <c r="C29" s="28"/>
+      <c r="D29" s="28"/>
+      <c r="E29" s="28"/>
+      <c r="F29" s="28"/>
+      <c r="G29" s="28">
         <v>1</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="28">
         <v>1</v>
       </c>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29">
+      <c r="J29" s="28"/>
+      <c r="K29" s="28"/>
+      <c r="L29" s="28"/>
+      <c r="M29" s="28"/>
+      <c r="N29" s="28"/>
+      <c r="O29" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="29">
+      <c r="A30" s="28">
         <v>2</v>
       </c>
-      <c r="B30" s="29"/>
-      <c r="C30" s="29"/>
-      <c r="D30" s="29"/>
-      <c r="E30" s="29"/>
-      <c r="F30" s="29"/>
-      <c r="G30" s="29">
+      <c r="B30" s="28"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="28"/>
+      <c r="E30" s="28"/>
+      <c r="F30" s="28"/>
+      <c r="G30" s="28">
         <v>2</v>
       </c>
-      <c r="I30" s="29">
+      <c r="I30" s="28">
         <v>2</v>
       </c>
-      <c r="J30" s="29"/>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
-      <c r="N30" s="29"/>
-      <c r="O30" s="29">
+      <c r="J30" s="28"/>
+      <c r="K30" s="28"/>
+      <c r="L30" s="28"/>
+      <c r="M30" s="28"/>
+      <c r="N30" s="28"/>
+      <c r="O30" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="29">
+      <c r="A31" s="28">
         <v>3</v>
       </c>
-      <c r="B31" s="29"/>
-      <c r="C31" s="29"/>
-      <c r="D31" s="29"/>
-      <c r="E31" s="29"/>
-      <c r="F31" s="29"/>
-      <c r="G31" s="29">
+      <c r="B31" s="28"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="28"/>
+      <c r="E31" s="28"/>
+      <c r="F31" s="28"/>
+      <c r="G31" s="28">
         <v>3</v>
       </c>
-      <c r="I31" s="29">
+      <c r="I31" s="28">
         <v>3</v>
       </c>
-      <c r="J31" s="29"/>
-      <c r="K31" s="29"/>
-      <c r="L31" s="29"/>
-      <c r="M31" s="29"/>
-      <c r="N31" s="29"/>
-      <c r="O31" s="29">
+      <c r="J31" s="28"/>
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+      <c r="O31" s="28">
         <v>3</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="29">
+      <c r="A32" s="28">
         <v>4</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29">
+      <c r="B32" s="28"/>
+      <c r="C32" s="28"/>
+      <c r="D32" s="28"/>
+      <c r="E32" s="28"/>
+      <c r="F32" s="28"/>
+      <c r="G32" s="28">
         <v>4</v>
       </c>
-      <c r="I32" s="29">
+      <c r="I32" s="28">
         <v>4</v>
       </c>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29">
+      <c r="J32" s="28"/>
+      <c r="K32" s="28"/>
+      <c r="L32" s="28"/>
+      <c r="M32" s="28"/>
+      <c r="N32" s="28"/>
+      <c r="O32" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29">
+      <c r="A33" s="28">
         <v>5</v>
       </c>
-      <c r="B33" s="29"/>
-      <c r="C33" s="29"/>
-      <c r="D33" s="29"/>
-      <c r="E33" s="29"/>
-      <c r="F33" s="29"/>
-      <c r="G33" s="29">
+      <c r="B33" s="28"/>
+      <c r="C33" s="28"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="28"/>
+      <c r="G33" s="28">
         <v>5</v>
       </c>
-      <c r="I33" s="29">
+      <c r="I33" s="28">
         <v>5</v>
       </c>
-      <c r="J33" s="29"/>
-      <c r="K33" s="29"/>
-      <c r="L33" s="29"/>
-      <c r="M33" s="29"/>
-      <c r="N33" s="29"/>
-      <c r="O33" s="29">
+      <c r="J33" s="28"/>
+      <c r="K33" s="28"/>
+      <c r="L33" s="28"/>
+      <c r="M33" s="28"/>
+      <c r="N33" s="28"/>
+      <c r="O33" s="28">
         <v>5</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="str">
+      <c r="A35" s="28" t="str">
         <f>'data'!$B$2</f>
       </c>
-      <c r="B35" s="29" t="s">
+      <c r="B35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C35" s="29" t="s">
+      <c r="C35" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="29"/>
-      <c r="E35" s="29" t="s">
+      <c r="D35" s="28"/>
+      <c r="E35" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G35" s="29" t="str">
+      <c r="G35" s="28" t="str">
         <f>'data'!$B$3</f>
       </c>
-      <c r="I35" s="29" t="str">
+      <c r="I35" s="28" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="J35" s="29" t="s">
+      <c r="J35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K35" s="29" t="s">
+      <c r="K35" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="L35" s="29"/>
-      <c r="M35" s="29" t="s">
+      <c r="L35" s="28"/>
+      <c r="M35" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N35" s="29" t="s">
+      <c r="N35" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O35" s="29" t="str">
+      <c r="O35" s="28" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
-      <c r="D36" s="29"/>
-      <c r="E36" s="29"/>
-      <c r="F36" s="29"/>
-      <c r="G36" s="29" t="s">
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
+      <c r="D36" s="28"/>
+      <c r="E36" s="28"/>
+      <c r="F36" s="28"/>
+      <c r="G36" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J36" s="29"/>
-      <c r="K36" s="29"/>
-      <c r="L36" s="29"/>
-      <c r="M36" s="29"/>
-      <c r="N36" s="29"/>
-      <c r="O36" s="29" t="s">
+      <c r="J36" s="28"/>
+      <c r="K36" s="28"/>
+      <c r="L36" s="28"/>
+      <c r="M36" s="28"/>
+      <c r="N36" s="28"/>
+      <c r="O36" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2958,230 +2968,230 @@
       <c r="O42" s="27"/>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D43" s="29" t="s">
+      <c r="D43" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G43" t="s">
+      <c r="G43" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I43" s="28" t="s">
+      <c r="I43" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L43" s="29" t="s">
+      <c r="L43" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="O43" t="s">
+      <c r="O43" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="str">
+      <c r="A44" s="28" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
-      <c r="F44" s="29"/>
-      <c r="G44" s="29" t="str">
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
+      <c r="D44" s="28"/>
+      <c r="E44" s="28"/>
+      <c r="F44" s="28"/>
+      <c r="G44" s="28" t="str">
         <f>'data'!$B$8</f>
       </c>
-      <c r="I44" s="29" t="str">
+      <c r="I44" s="28" t="str">
         <f>'data'!$B$9</f>
       </c>
-      <c r="J44" s="29"/>
-      <c r="K44" s="29"/>
-      <c r="L44" s="29"/>
-      <c r="M44" s="29"/>
-      <c r="N44" s="29"/>
-      <c r="O44" s="29" t="str">
+      <c r="J44" s="28"/>
+      <c r="K44" s="28"/>
+      <c r="L44" s="28"/>
+      <c r="M44" s="28"/>
+      <c r="N44" s="28"/>
+      <c r="O44" s="28" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="29">
+      <c r="A45" s="28">
         <v>1</v>
       </c>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
-      <c r="F45" s="29"/>
-      <c r="G45" s="29">
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
+      <c r="D45" s="28"/>
+      <c r="E45" s="28"/>
+      <c r="F45" s="28"/>
+      <c r="G45" s="28">
         <v>1</v>
       </c>
-      <c r="I45" s="29">
+      <c r="I45" s="28">
         <v>1</v>
       </c>
-      <c r="J45" s="29"/>
-      <c r="K45" s="29"/>
-      <c r="L45" s="29"/>
-      <c r="M45" s="29"/>
-      <c r="N45" s="29"/>
-      <c r="O45" s="29">
+      <c r="J45" s="28"/>
+      <c r="K45" s="28"/>
+      <c r="L45" s="28"/>
+      <c r="M45" s="28"/>
+      <c r="N45" s="28"/>
+      <c r="O45" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="29">
+      <c r="A46" s="28">
         <v>2</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29">
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
+      <c r="D46" s="28"/>
+      <c r="E46" s="28"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28">
         <v>2</v>
       </c>
-      <c r="I46" s="29">
+      <c r="I46" s="28">
         <v>2</v>
       </c>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29">
+      <c r="J46" s="28"/>
+      <c r="K46" s="28"/>
+      <c r="L46" s="28"/>
+      <c r="M46" s="28"/>
+      <c r="N46" s="28"/>
+      <c r="O46" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="29">
+      <c r="A47" s="28">
         <v>3</v>
       </c>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29">
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="28"/>
+      <c r="F47" s="28"/>
+      <c r="G47" s="28">
         <v>3</v>
       </c>
-      <c r="I47" s="29">
+      <c r="I47" s="28">
         <v>3</v>
       </c>
-      <c r="J47" s="29"/>
-      <c r="K47" s="29"/>
-      <c r="L47" s="29"/>
-      <c r="M47" s="29"/>
-      <c r="N47" s="29"/>
-      <c r="O47" s="29">
+      <c r="J47" s="28"/>
+      <c r="K47" s="28"/>
+      <c r="L47" s="28"/>
+      <c r="M47" s="28"/>
+      <c r="N47" s="28"/>
+      <c r="O47" s="28">
         <v>3</v>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="29">
+      <c r="A48" s="28">
         <v>4</v>
       </c>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
-      <c r="F48" s="29"/>
-      <c r="G48" s="29">
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
+      <c r="F48" s="28"/>
+      <c r="G48" s="28">
         <v>4</v>
       </c>
-      <c r="I48" s="29">
+      <c r="I48" s="28">
         <v>4</v>
       </c>
-      <c r="J48" s="29"/>
-      <c r="K48" s="29"/>
-      <c r="L48" s="29"/>
-      <c r="M48" s="29"/>
-      <c r="N48" s="29"/>
-      <c r="O48" s="29">
+      <c r="J48" s="28"/>
+      <c r="K48" s="28"/>
+      <c r="L48" s="28"/>
+      <c r="M48" s="28"/>
+      <c r="N48" s="28"/>
+      <c r="O48" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="29">
+      <c r="A49" s="28">
         <v>5</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29">
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
+      <c r="D49" s="28"/>
+      <c r="E49" s="28"/>
+      <c r="F49" s="28"/>
+      <c r="G49" s="28">
         <v>5</v>
       </c>
-      <c r="I49" s="29">
+      <c r="I49" s="28">
         <v>5</v>
       </c>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29">
+      <c r="J49" s="28"/>
+      <c r="K49" s="28"/>
+      <c r="L49" s="28"/>
+      <c r="M49" s="28"/>
+      <c r="N49" s="28"/>
+      <c r="O49" s="28">
         <v>5</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="str">
+      <c r="A51" s="28" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B51" s="29" t="s">
+      <c r="B51" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C51" s="29" t="s">
+      <c r="C51" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29" t="s">
+      <c r="D51" s="28"/>
+      <c r="E51" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F51" s="29" t="s">
+      <c r="F51" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G51" s="29" t="str">
+      <c r="G51" s="28" t="str">
         <f>'data'!$B$8</f>
       </c>
-      <c r="I51" s="29" t="str">
+      <c r="I51" s="28" t="str">
         <f>'data'!$B$9</f>
       </c>
-      <c r="J51" s="29" t="s">
+      <c r="J51" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K51" s="29" t="s">
+      <c r="K51" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="L51" s="29"/>
-      <c r="M51" s="29" t="s">
+      <c r="L51" s="28"/>
+      <c r="M51" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N51" s="29" t="s">
+      <c r="N51" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O51" s="29" t="str">
+      <c r="O51" s="28" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="s">
+      <c r="A52" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29" t="s">
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I52" s="29" t="s">
+      <c r="I52" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29" t="s">
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3245,230 +3255,230 @@
       <c r="O65" s="27"/>
     </row>
     <row r="66">
-      <c r="A66" s="28" t="s">
+      <c r="A66" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G66" s="30" t="s">
         <v>33</v>
       </c>
-      <c r="I66" s="28" t="s">
+      <c r="I66" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="L66" s="29" t="s">
+      <c r="L66" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="O66" t="s">
+      <c r="O66" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="str">
+      <c r="A67" s="28" t="str">
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29" t="str">
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
+      <c r="D67" s="28"/>
+      <c r="E67" s="28"/>
+      <c r="F67" s="28"/>
+      <c r="G67" s="28" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
       </c>
-      <c r="I67" s="29" t="str">
+      <c r="I67" s="28" t="str">
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29" t="str">
+      <c r="J67" s="28"/>
+      <c r="K67" s="28"/>
+      <c r="L67" s="28"/>
+      <c r="M67" s="28"/>
+      <c r="N67" s="28"/>
+      <c r="O67" s="28" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="29">
+      <c r="A68" s="28">
         <v>1</v>
       </c>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="29"/>
-      <c r="G68" s="29">
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+      <c r="F68" s="28"/>
+      <c r="G68" s="28">
         <v>1</v>
       </c>
-      <c r="I68" s="29">
+      <c r="I68" s="28">
         <v>1</v>
       </c>
-      <c r="J68" s="29"/>
-      <c r="K68" s="29"/>
-      <c r="L68" s="29"/>
-      <c r="M68" s="29"/>
-      <c r="N68" s="29"/>
-      <c r="O68" s="29">
+      <c r="J68" s="28"/>
+      <c r="K68" s="28"/>
+      <c r="L68" s="28"/>
+      <c r="M68" s="28"/>
+      <c r="N68" s="28"/>
+      <c r="O68" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="29">
+      <c r="A69" s="28">
         <v>2</v>
       </c>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="29"/>
-      <c r="G69" s="29">
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
+      <c r="D69" s="28"/>
+      <c r="E69" s="28"/>
+      <c r="F69" s="28"/>
+      <c r="G69" s="28">
         <v>2</v>
       </c>
-      <c r="I69" s="29">
+      <c r="I69" s="28">
         <v>2</v>
       </c>
-      <c r="J69" s="29"/>
-      <c r="K69" s="29"/>
-      <c r="L69" s="29"/>
-      <c r="M69" s="29"/>
-      <c r="N69" s="29"/>
-      <c r="O69" s="29">
+      <c r="J69" s="28"/>
+      <c r="K69" s="28"/>
+      <c r="L69" s="28"/>
+      <c r="M69" s="28"/>
+      <c r="N69" s="28"/>
+      <c r="O69" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="29">
+      <c r="A70" s="28">
         <v>3</v>
       </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29">
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
+      <c r="D70" s="28"/>
+      <c r="E70" s="28"/>
+      <c r="F70" s="28"/>
+      <c r="G70" s="28">
         <v>3</v>
       </c>
-      <c r="I70" s="29">
+      <c r="I70" s="28">
         <v>3</v>
       </c>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29">
+      <c r="J70" s="28"/>
+      <c r="K70" s="28"/>
+      <c r="L70" s="28"/>
+      <c r="M70" s="28"/>
+      <c r="N70" s="28"/>
+      <c r="O70" s="28">
         <v>3</v>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="29">
+      <c r="A71" s="28">
         <v>4</v>
       </c>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
-      <c r="F71" s="29"/>
-      <c r="G71" s="29">
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28"/>
+      <c r="E71" s="28"/>
+      <c r="F71" s="28"/>
+      <c r="G71" s="28">
         <v>4</v>
       </c>
-      <c r="I71" s="29">
+      <c r="I71" s="28">
         <v>4</v>
       </c>
-      <c r="J71" s="29"/>
-      <c r="K71" s="29"/>
-      <c r="L71" s="29"/>
-      <c r="M71" s="29"/>
-      <c r="N71" s="29"/>
-      <c r="O71" s="29">
+      <c r="J71" s="28"/>
+      <c r="K71" s="28"/>
+      <c r="L71" s="28"/>
+      <c r="M71" s="28"/>
+      <c r="N71" s="28"/>
+      <c r="O71" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="29">
+      <c r="A72" s="28">
         <v>5</v>
       </c>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
-      <c r="F72" s="29"/>
-      <c r="G72" s="29">
+      <c r="B72" s="28"/>
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+      <c r="F72" s="28"/>
+      <c r="G72" s="28">
         <v>5</v>
       </c>
-      <c r="I72" s="29">
+      <c r="I72" s="28">
         <v>5</v>
       </c>
-      <c r="J72" s="29"/>
-      <c r="K72" s="29"/>
-      <c r="L72" s="29"/>
-      <c r="M72" s="29"/>
-      <c r="N72" s="29"/>
-      <c r="O72" s="29">
+      <c r="J72" s="28"/>
+      <c r="K72" s="28"/>
+      <c r="L72" s="28"/>
+      <c r="M72" s="28"/>
+      <c r="N72" s="28"/>
+      <c r="O72" s="28">
         <v>5</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="str">
+      <c r="A74" s="28" t="str">
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
-      <c r="B74" s="29" t="s">
+      <c r="B74" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29" t="s">
+      <c r="D74" s="28"/>
+      <c r="E74" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F74" s="29" t="s">
+      <c r="F74" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G74" s="29" t="str">
+      <c r="G74" s="28" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
       </c>
-      <c r="I74" s="29" t="str">
+      <c r="I74" s="28" t="str">
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
-      <c r="J74" s="29" t="s">
+      <c r="J74" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="K74" s="29" t="s">
+      <c r="K74" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="L74" s="29"/>
-      <c r="M74" s="29" t="s">
+      <c r="L74" s="28"/>
+      <c r="M74" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N74" s="29" t="s">
+      <c r="N74" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O74" s="29" t="str">
+      <c r="O74" s="28" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="s">
+      <c r="A75" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
-      <c r="F75" s="29"/>
-      <c r="G75" s="29" t="s">
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
+      <c r="D75" s="28"/>
+      <c r="E75" s="28"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="I75" s="29" t="s">
+      <c r="I75" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="J75" s="29"/>
-      <c r="K75" s="29"/>
-      <c r="L75" s="29"/>
-      <c r="M75" s="29"/>
-      <c r="N75" s="29"/>
-      <c r="O75" s="29" t="s">
+      <c r="J75" s="28"/>
+      <c r="K75" s="28"/>
+      <c r="L75" s="28"/>
+      <c r="M75" s="28"/>
+      <c r="N75" s="28"/>
+      <c r="O75" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3523,125 +3533,125 @@
       <c r="G88" s="27"/>
     </row>
     <row r="89">
-      <c r="A89" s="28" t="s">
+      <c r="A89" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="D89" s="29" t="s">
+      <c r="D89" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="G89" t="s">
+      <c r="G89" s="30" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="29" t="str">
+      <c r="A90" s="28" t="str">
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
-      <c r="B90" s="29"/>
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
-      <c r="E90" s="29"/>
-      <c r="F90" s="29"/>
-      <c r="G90" s="29" t="str">
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
+      <c r="D90" s="28"/>
+      <c r="E90" s="28"/>
+      <c r="F90" s="28"/>
+      <c r="G90" s="28" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="29">
+      <c r="A91" s="28">
         <v>1</v>
       </c>
-      <c r="B91" s="29"/>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="29"/>
-      <c r="F91" s="29"/>
-      <c r="G91" s="29">
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
+      <c r="D91" s="28"/>
+      <c r="E91" s="28"/>
+      <c r="F91" s="28"/>
+      <c r="G91" s="28">
         <v>1</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="29">
+      <c r="A92" s="28">
         <v>2</v>
       </c>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
-      <c r="E92" s="29"/>
-      <c r="F92" s="29"/>
-      <c r="G92" s="29">
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
+      <c r="D92" s="28"/>
+      <c r="E92" s="28"/>
+      <c r="F92" s="28"/>
+      <c r="G92" s="28">
         <v>2</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="29">
+      <c r="A93" s="28">
         <v>3</v>
       </c>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="29"/>
-      <c r="G93" s="29">
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
+      <c r="D93" s="28"/>
+      <c r="E93" s="28"/>
+      <c r="F93" s="28"/>
+      <c r="G93" s="28">
         <v>3</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="29">
+      <c r="A94" s="28">
         <v>4</v>
       </c>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
-      <c r="F94" s="29"/>
-      <c r="G94" s="29">
+      <c r="B94" s="28"/>
+      <c r="C94" s="28"/>
+      <c r="D94" s="28"/>
+      <c r="E94" s="28"/>
+      <c r="F94" s="28"/>
+      <c r="G94" s="28">
         <v>4</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="29">
+      <c r="A95" s="28">
         <v>5</v>
       </c>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
-      <c r="E95" s="29"/>
-      <c r="F95" s="29"/>
-      <c r="G95" s="29">
+      <c r="B95" s="28"/>
+      <c r="C95" s="28"/>
+      <c r="D95" s="28"/>
+      <c r="E95" s="28"/>
+      <c r="F95" s="28"/>
+      <c r="G95" s="28">
         <v>5</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="29" t="str">
+      <c r="A97" s="28" t="str">
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
-      <c r="B97" s="29" t="s">
+      <c r="B97" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="C97" s="29" t="s">
+      <c r="C97" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29" t="s">
+      <c r="D97" s="28"/>
+      <c r="E97" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F97" s="29" t="s">
+      <c r="F97" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G97" s="29" t="str">
+      <c r="G97" s="28" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="29" t="s">
+      <c r="A98" s="28" t="s">
         <v>36</v>
       </c>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
-      <c r="E98" s="29"/>
-      <c r="F98" s="29"/>
-      <c r="G98" s="29" t="s">
+      <c r="B98" s="28"/>
+      <c r="C98" s="28"/>
+      <c r="D98" s="28"/>
+      <c r="E98" s="28"/>
+      <c r="F98" s="28"/>
+      <c r="G98" s="28" t="s">
         <v>36</v>
       </c>
     </row>
@@ -3685,8 +3695,8 @@
   <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="115" customHeight="true"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="10" width="21.6640625"/>
-    <col customWidth="true" max="2" min="2" style="9" width="170.6640625"/>
+    <col customWidth="true" max="1" min="1" style="10" width="20"/>
+    <col customWidth="true" max="2" min="2" style="9" width="170"/>
     <col max="16384" min="3" style="8" width="10.83203125"/>
   </cols>
   <sheetData>
@@ -3825,6 +3835,6 @@
   </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup fitToHeight="0" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" horizontalDpi="0" orientation="landscape" paperSize="8" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -75,6 +75,9 @@
   </si>
   <si>
     <t>Number of Elimination Matches</t>
+  </si>
+  <si>
+    <t>Title prefix:</t>
   </si>
   <si>
     <t>Number</t>
@@ -284,12 +287,12 @@
     </font>
     <font>
       <family val="2"/>
+      <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
-      <b val="1"/>
       <color rgb="FF000000"/>
       <sz val="12"/>
     </font>
@@ -398,6 +401,20 @@
       <left style="medium">
         <color rgb="FF000000"/>
       </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
     </border>
     <border>
       <left style="medium">
@@ -413,20 +430,6 @@
       </top>
     </border>
     <border>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
       </bottom>
@@ -496,37 +499,37 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -755,129 +758,131 @@
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" ht="12.75" customHeight="true">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" t="s">
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="12.75" customHeight="true">
-      <c r="A2" s="1">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
       <c r="A3" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
       <c r="A4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
       <c r="A5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
       <c r="A6" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
       <c r="A7" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
       <c r="A8" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
       <c r="A9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
       <c r="A10" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
       <c r="A11" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
-      <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="A12" s="1">
+        <v>9</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true"/>
     <row r="14" spans="1:2" ht="12.75" customHeight="true">
@@ -1963,185 +1968,208 @@
     <col customWidth="true" max="2" min="2" width="10"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="str">
+        <f>IF(data!$B$1="","Shiaijo A",data!$B$1&amp;" - Shiaijo A")</f>
+      </c>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+    </row>
     <row r="6">
-      <c r="E6" s="24" t="s">
-        <v>15</v>
+      <c r="E6" s="25" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="22"/>
-      <c r="G7" s="20"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="21"/>
     </row>
     <row r="8">
-      <c r="G8" s="21">
+      <c r="G8" s="22">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="20"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="20"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10">
-      <c r="E10" s="24" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="23"/>
-      <c r="G10" s="20"/>
-      <c r="I10" s="20"/>
+      <c r="E10" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="24"/>
+      <c r="G10" s="21"/>
+      <c r="I10" s="21"/>
     </row>
     <row r="11">
-      <c r="I11" s="20"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12">
-      <c r="I12" s="21">
+      <c r="I12" s="22">
         <v>7</v>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="20"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="20"/>
+      <c r="I13" s="21"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="21"/>
     </row>
     <row r="14">
-      <c r="E14" s="24" t="s">
-        <v>19</v>
-      </c>
-      <c r="I14" s="20"/>
-      <c r="K14" s="20"/>
+      <c r="E14" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="21"/>
+      <c r="K14" s="21"/>
     </row>
     <row r="15">
-      <c r="F15" s="22"/>
-      <c r="G15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="K15" s="20"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="K15" s="21"/>
     </row>
     <row r="16">
-      <c r="G16" s="21">
+      <c r="G16" s="22">
         <v>4</v>
       </c>
-      <c r="H16" s="23"/>
-      <c r="I16" s="20"/>
-      <c r="K16" s="20"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="21"/>
+      <c r="K16" s="21"/>
     </row>
     <row r="17">
-      <c r="C17" s="24" t="s">
-        <v>21</v>
-      </c>
-      <c r="G17" s="20"/>
-      <c r="K17" s="20"/>
+      <c r="C17" s="25" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="21"/>
+      <c r="K17" s="21"/>
     </row>
     <row r="18">
-      <c r="D18" s="22"/>
-      <c r="E18" s="21">
+      <c r="D18" s="23"/>
+      <c r="E18" s="22">
         <v>1</v>
       </c>
-      <c r="F18" s="23"/>
-      <c r="G18" s="20"/>
-      <c r="K18" s="20"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="21"/>
+      <c r="K18" s="21"/>
     </row>
     <row r="19">
-      <c r="C19" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="23"/>
-      <c r="E19" s="20"/>
-      <c r="K19" s="20"/>
+      <c r="C19" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="24"/>
+      <c r="E19" s="21"/>
+      <c r="K19" s="21"/>
     </row>
     <row r="20">
-      <c r="K20" s="21">
+      <c r="K20" s="22">
         <v>9</v>
       </c>
     </row>
     <row r="21">
-      <c r="K21" s="20"/>
+      <c r="K21" s="21"/>
     </row>
     <row r="22">
-      <c r="E22" s="24" t="s">
-        <v>25</v>
-      </c>
-      <c r="K22" s="20"/>
+      <c r="E22" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="21"/>
     </row>
     <row r="23">
-      <c r="F23" s="22"/>
-      <c r="G23" s="20"/>
-      <c r="K23" s="20"/>
+      <c r="F23" s="23"/>
+      <c r="G23" s="21"/>
+      <c r="K23" s="21"/>
     </row>
     <row r="24">
-      <c r="G24" s="21">
+      <c r="G24" s="22">
         <v>5</v>
       </c>
-      <c r="K24" s="20"/>
+      <c r="K24" s="21"/>
     </row>
     <row r="25">
-      <c r="G25" s="20"/>
-      <c r="H25" s="22"/>
-      <c r="I25" s="20"/>
-      <c r="K25" s="20"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="23"/>
+      <c r="I25" s="21"/>
+      <c r="K25" s="21"/>
     </row>
     <row r="26">
-      <c r="E26" s="24" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="23"/>
-      <c r="G26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="K26" s="20"/>
+      <c r="E26" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="F26" s="24"/>
+      <c r="G26" s="21"/>
+      <c r="I26" s="21"/>
+      <c r="K26" s="21"/>
     </row>
     <row r="27">
-      <c r="I27" s="20"/>
-      <c r="K27" s="20"/>
+      <c r="I27" s="21"/>
+      <c r="K27" s="21"/>
     </row>
     <row r="28">
-      <c r="I28" s="21">
+      <c r="I28" s="22">
         <v>8</v>
       </c>
-      <c r="J28" s="23"/>
-      <c r="K28" s="20"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="21"/>
     </row>
     <row r="29">
-      <c r="I29" s="20"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="30">
-      <c r="E30" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="I30" s="20"/>
+      <c r="E30" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="I30" s="21"/>
     </row>
     <row r="31">
-      <c r="F31" s="22"/>
-      <c r="G31" s="20"/>
-      <c r="I31" s="20"/>
+      <c r="F31" s="23"/>
+      <c r="G31" s="21"/>
+      <c r="I31" s="21"/>
     </row>
     <row r="32">
-      <c r="G32" s="21">
+      <c r="G32" s="22">
         <v>6</v>
       </c>
-      <c r="H32" s="23"/>
-      <c r="I32" s="20"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="21"/>
     </row>
     <row r="33">
-      <c r="C33" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="G33" s="20"/>
+      <c r="C33" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="G33" s="21"/>
     </row>
     <row r="34">
-      <c r="D34" s="22"/>
-      <c r="E34" s="21">
+      <c r="D34" s="23"/>
+      <c r="E34" s="22">
         <v>2</v>
       </c>
-      <c r="F34" s="23"/>
-      <c r="G34" s="20"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="21"/>
     </row>
     <row r="35">
-      <c r="C35" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="D35" s="23"/>
-      <c r="E35" s="20"/>
+      <c r="C35" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="24"/>
+      <c r="E35" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:P1"/>
+  </mergeCells>
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.25" right="0.25" top="0" bottom="0" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2374,67 +2402,67 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" thickBot="true">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-      <c r="H1" s="27"/>
-      <c r="I1" s="27"/>
-      <c r="J1" s="27"/>
-      <c r="K1" s="27"/>
-      <c r="L1" s="27"/>
-      <c r="M1" s="27"/>
-      <c r="N1" s="27"/>
-      <c r="O1" s="27"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
     </row>
     <row r="3">
-      <c r="A3" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="B3" s="27"/>
-      <c r="C3" s="27"/>
-      <c r="D3" s="27"/>
-      <c r="E3" s="27"/>
-      <c r="F3" s="27"/>
-      <c r="G3" s="27"/>
-      <c r="I3" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="J3" s="27"/>
-      <c r="K3" s="27"/>
-      <c r="L3" s="27"/>
-      <c r="M3" s="27"/>
-      <c r="N3" s="27"/>
-      <c r="O3" s="27"/>
+      <c r="A3" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="I3" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
     </row>
     <row r="4">
       <c r="A4" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D4" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="L4" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="I4" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>32</v>
-      </c>
       <c r="O4" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -2442,10 +2470,10 @@
       <c r="E5" s="28"/>
       <c r="F5" s="28"/>
       <c r="G5" s="28" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="I5" s="28" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="J5" s="28"/>
       <c r="K5" s="28"/>
@@ -2453,7 +2481,7 @@
       <c r="M5" s="28"/>
       <c r="N5" s="28"/>
       <c r="O5" s="28" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
     <row r="6">
@@ -2578,47 +2606,47 @@
     </row>
     <row r="12">
       <c r="A12" s="28" t="str">
-        <f>'data'!$B$5</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="B12" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F12" s="28" t="s">
-        <v>34</v>
-      </c>
       <c r="G12" s="28" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="I12" s="28" t="str">
-        <f>'data'!$B$10</f>
+        <f>'data'!$B$11</f>
       </c>
       <c r="J12" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L12" s="28"/>
       <c r="M12" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N12" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="N12" s="28" t="s">
-        <v>34</v>
-      </c>
       <c r="O12" s="28" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -2626,10 +2654,10 @@
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
@@ -2637,91 +2665,91 @@
       <c r="M13" s="28"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G15" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="G15" s="24"/>
       <c r="N15" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O15" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="O15" s="24"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G16" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="G16" s="24"/>
       <c r="N16" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O16" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="O16" s="24"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="B24" s="27"/>
-      <c r="C24" s="27"/>
-      <c r="D24" s="27"/>
-      <c r="E24" s="27"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="27"/>
-      <c r="H24" s="27"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="27"/>
-      <c r="K24" s="27"/>
-      <c r="L24" s="27"/>
-      <c r="M24" s="27"/>
-      <c r="N24" s="27"/>
-      <c r="O24" s="27"/>
+      <c r="A24" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="20"/>
+      <c r="C24" s="20"/>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
+      <c r="G24" s="20"/>
+      <c r="H24" s="20"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="20"/>
+      <c r="N24" s="20"/>
+      <c r="O24" s="20"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="27"/>
-      <c r="C26" s="27"/>
-      <c r="D26" s="27"/>
-      <c r="E26" s="27"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
-      <c r="I26" s="27" t="s">
+      <c r="A26" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="J26" s="27"/>
-      <c r="K26" s="27"/>
-      <c r="L26" s="27"/>
-      <c r="M26" s="27"/>
-      <c r="N26" s="27"/>
-      <c r="O26" s="27"/>
+      <c r="B26" s="20"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
+      <c r="G26" s="20"/>
+      <c r="I26" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="20"/>
+      <c r="N26" s="20"/>
+      <c r="O26" s="20"/>
     </row>
     <row r="27">
       <c r="A27" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D27" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="I27" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="L27" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="I27" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L27" s="28" t="s">
-        <v>32</v>
-      </c>
       <c r="O27" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="str">
-        <f>'data'!$B$2</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -2729,10 +2757,10 @@
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I28" s="28" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
@@ -2865,39 +2893,39 @@
     </row>
     <row r="35">
       <c r="A35" s="28" t="str">
-        <f>'data'!$B$2</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="B35" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F35" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F35" s="28" t="s">
-        <v>34</v>
-      </c>
       <c r="G35" s="28" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="I35" s="28" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$5</f>
       </c>
       <c r="J35" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K35" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L35" s="28"/>
       <c r="M35" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N35" s="28" t="s">
         <v>35</v>
-      </c>
-      <c r="N35" s="28" t="s">
-        <v>34</v>
       </c>
       <c r="O35" s="28" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
@@ -2905,7 +2933,7 @@
     </row>
     <row r="36">
       <c r="A36" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -2913,10 +2941,10 @@
       <c r="E36" s="28"/>
       <c r="F36" s="28"/>
       <c r="G36" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J36" s="28"/>
       <c r="K36" s="28"/>
@@ -2924,72 +2952,72 @@
       <c r="M36" s="28"/>
       <c r="N36" s="28"/>
       <c r="O36" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="38">
       <c r="F38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G38" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="G38" s="24"/>
       <c r="N38" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O38" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="O38" s="24"/>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G39" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="G39" s="24"/>
       <c r="N39" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O39" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="O39" s="24"/>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="s">
-        <v>43</v>
-      </c>
-      <c r="B42" s="27"/>
-      <c r="C42" s="27"/>
-      <c r="D42" s="27"/>
-      <c r="E42" s="27"/>
-      <c r="F42" s="27"/>
-      <c r="G42" s="27"/>
-      <c r="I42" s="27" t="s">
+      <c r="A42" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="J42" s="27"/>
-      <c r="K42" s="27"/>
-      <c r="L42" s="27"/>
-      <c r="M42" s="27"/>
-      <c r="N42" s="27"/>
-      <c r="O42" s="27"/>
+      <c r="B42" s="20"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="20"/>
+      <c r="E42" s="20"/>
+      <c r="F42" s="20"/>
+      <c r="G42" s="20"/>
+      <c r="I42" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="20"/>
+      <c r="N42" s="20"/>
+      <c r="O42" s="20"/>
     </row>
     <row r="43">
       <c r="A43" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D43" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G43" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G43" s="30" t="s">
+      <c r="L43" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="I43" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L43" s="28" t="s">
-        <v>32</v>
-      </c>
       <c r="O43" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="28" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="B44" s="28"/>
       <c r="C44" s="28"/>
@@ -2997,10 +3025,10 @@
       <c r="E44" s="28"/>
       <c r="F44" s="28"/>
       <c r="G44" s="28" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I44" s="28" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="J44" s="28"/>
       <c r="K44" s="28"/>
@@ -3133,39 +3161,39 @@
     </row>
     <row r="51">
       <c r="A51" s="28" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="B51" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F51" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F51" s="28" t="s">
-        <v>34</v>
-      </c>
       <c r="G51" s="28" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="I51" s="28" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$10</f>
       </c>
       <c r="J51" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L51" s="28"/>
       <c r="M51" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N51" s="28" t="s">
         <v>35</v>
-      </c>
-      <c r="N51" s="28" t="s">
-        <v>34</v>
       </c>
       <c r="O51" s="28" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
@@ -3173,7 +3201,7 @@
     </row>
     <row r="52">
       <c r="A52" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="28"/>
@@ -3181,10 +3209,10 @@
       <c r="E52" s="28"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J52" s="28"/>
       <c r="K52" s="28"/>
@@ -3192,86 +3220,86 @@
       <c r="M52" s="28"/>
       <c r="N52" s="28"/>
       <c r="O52" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="54">
       <c r="F54" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G54" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="G54" s="24"/>
       <c r="N54" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O54" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="O54" s="24"/>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G55" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="G55" s="24"/>
       <c r="N55" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O55" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="O55" s="24"/>
     </row>
     <row r="63">
-      <c r="A63" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="B63" s="27"/>
-      <c r="C63" s="27"/>
-      <c r="D63" s="27"/>
-      <c r="E63" s="27"/>
-      <c r="F63" s="27"/>
-      <c r="G63" s="27"/>
-      <c r="H63" s="27"/>
-      <c r="I63" s="27"/>
-      <c r="J63" s="27"/>
-      <c r="K63" s="27"/>
-      <c r="L63" s="27"/>
-      <c r="M63" s="27"/>
-      <c r="N63" s="27"/>
-      <c r="O63" s="27"/>
+      <c r="A63" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="B63" s="20"/>
+      <c r="C63" s="20"/>
+      <c r="D63" s="20"/>
+      <c r="E63" s="20"/>
+      <c r="F63" s="20"/>
+      <c r="G63" s="20"/>
+      <c r="H63" s="20"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="20"/>
+      <c r="N63" s="20"/>
+      <c r="O63" s="20"/>
     </row>
     <row r="65">
-      <c r="A65" s="27" t="s">
-        <v>46</v>
-      </c>
-      <c r="B65" s="27"/>
-      <c r="C65" s="27"/>
-      <c r="D65" s="27"/>
-      <c r="E65" s="27"/>
-      <c r="F65" s="27"/>
-      <c r="G65" s="27"/>
-      <c r="I65" s="27" t="s">
+      <c r="A65" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="J65" s="27"/>
-      <c r="K65" s="27"/>
-      <c r="L65" s="27"/>
-      <c r="M65" s="27"/>
-      <c r="N65" s="27"/>
-      <c r="O65" s="27"/>
+      <c r="B65" s="20"/>
+      <c r="C65" s="20"/>
+      <c r="D65" s="20"/>
+      <c r="E65" s="20"/>
+      <c r="F65" s="20"/>
+      <c r="G65" s="20"/>
+      <c r="I65" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="J65" s="20"/>
+      <c r="K65" s="20"/>
+      <c r="L65" s="20"/>
+      <c r="M65" s="20"/>
+      <c r="N65" s="20"/>
+      <c r="O65" s="20"/>
     </row>
     <row r="66">
       <c r="A66" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D66" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="G66" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="I66" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="G66" s="30" t="s">
+      <c r="L66" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="I66" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="L66" s="28" t="s">
-        <v>32</v>
-      </c>
       <c r="O66" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="67">
@@ -3423,17 +3451,17 @@
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="B74" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D74" s="28"/>
       <c r="E74" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F74" s="28" t="s">
         <v>35</v>
-      </c>
-      <c r="F74" s="28" t="s">
-        <v>34</v>
       </c>
       <c r="G74" s="28" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
@@ -3442,17 +3470,17 @@
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
       <c r="J74" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L74" s="28"/>
       <c r="M74" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="N74" s="28" t="s">
         <v>35</v>
-      </c>
-      <c r="N74" s="28" t="s">
-        <v>34</v>
       </c>
       <c r="O74" s="28" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
@@ -3460,7 +3488,7 @@
     </row>
     <row r="75">
       <c r="A75" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B75" s="28"/>
       <c r="C75" s="28"/>
@@ -3468,10 +3496,10 @@
       <c r="E75" s="28"/>
       <c r="F75" s="28"/>
       <c r="G75" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I75" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J75" s="28"/>
       <c r="K75" s="28"/>
@@ -3479,68 +3507,68 @@
       <c r="M75" s="28"/>
       <c r="N75" s="28"/>
       <c r="O75" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="77">
       <c r="F77" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G77" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="G77" s="24"/>
       <c r="N77" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="O77" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="O77" s="24"/>
     </row>
     <row r="78">
       <c r="F78" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G78" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="G78" s="24"/>
       <c r="N78" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="O78" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="O78" s="24"/>
     </row>
     <row r="86">
-      <c r="A86" s="27" t="s">
-        <v>48</v>
-      </c>
-      <c r="B86" s="27"/>
-      <c r="C86" s="27"/>
-      <c r="D86" s="27"/>
-      <c r="E86" s="27"/>
-      <c r="F86" s="27"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="27"/>
-      <c r="I86" s="27"/>
-      <c r="J86" s="27"/>
-      <c r="K86" s="27"/>
-      <c r="L86" s="27"/>
-      <c r="M86" s="27"/>
-      <c r="N86" s="27"/>
-      <c r="O86" s="27"/>
+      <c r="A86" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="B86" s="20"/>
+      <c r="C86" s="20"/>
+      <c r="D86" s="20"/>
+      <c r="E86" s="20"/>
+      <c r="F86" s="20"/>
+      <c r="G86" s="20"/>
+      <c r="H86" s="20"/>
+      <c r="I86" s="20"/>
+      <c r="J86" s="20"/>
+      <c r="K86" s="20"/>
+      <c r="L86" s="20"/>
+      <c r="M86" s="20"/>
+      <c r="N86" s="20"/>
+      <c r="O86" s="20"/>
     </row>
     <row r="88">
-      <c r="A88" s="27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B88" s="27"/>
-      <c r="C88" s="27"/>
-      <c r="D88" s="27"/>
-      <c r="E88" s="27"/>
-      <c r="F88" s="27"/>
-      <c r="G88" s="27"/>
+      <c r="A88" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" s="20"/>
+      <c r="C88" s="20"/>
+      <c r="D88" s="20"/>
+      <c r="E88" s="20"/>
+      <c r="F88" s="20"/>
+      <c r="G88" s="20"/>
     </row>
     <row r="89">
       <c r="A89" s="29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G89" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="90">
@@ -3626,17 +3654,17 @@
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
       <c r="B97" s="28" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D97" s="28"/>
       <c r="E97" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="F97" s="28" t="s">
         <v>35</v>
-      </c>
-      <c r="F97" s="28" t="s">
-        <v>34</v>
       </c>
       <c r="G97" s="28" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
@@ -3644,7 +3672,7 @@
     </row>
     <row r="98">
       <c r="A98" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B98" s="28"/>
       <c r="C98" s="28"/>
@@ -3652,20 +3680,20 @@
       <c r="E98" s="28"/>
       <c r="F98" s="28"/>
       <c r="G98" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100">
       <c r="F100" s="7" t="s">
-        <v>37</v>
-      </c>
-      <c r="G100" s="23"/>
+        <v>38</v>
+      </c>
+      <c r="G100" s="24"/>
     </row>
     <row r="101">
       <c r="F101" s="7" t="s">
-        <v>38</v>
-      </c>
-      <c r="G101" s="23"/>
+        <v>39</v>
+      </c>
+      <c r="G101" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -3701,124 +3729,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="25">
+      <c r="A1" s="26">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="str">
-        <f>data!$B$2</f>
+      <c r="B1" s="27" t="str">
+        <f>data!$B$3</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="25"/>
-      <c r="B2" s="26"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="27"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="25">
+      <c r="A3" s="26">
         <v>1</v>
       </c>
-      <c r="B3" s="26" t="str">
-        <f>data!$B$3</f>
+      <c r="B3" s="27" t="str">
+        <f>data!$B$4</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="25"/>
-      <c r="B4" s="26"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="27"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="25">
+      <c r="A5" s="26">
         <v>2</v>
       </c>
-      <c r="B5" s="26" t="str">
-        <f>data!$B$4</f>
+      <c r="B5" s="27" t="str">
+        <f>data!$B$5</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="25"/>
-      <c r="B6" s="26"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="27"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="25">
+      <c r="A7" s="26">
         <v>3</v>
       </c>
-      <c r="B7" s="26" t="str">
-        <f>data!$B$5</f>
+      <c r="B7" s="27" t="str">
+        <f>data!$B$6</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="25"/>
-      <c r="B8" s="26"/>
+      <c r="A8" s="26"/>
+      <c r="B8" s="27"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="25">
+      <c r="A9" s="26">
         <v>4</v>
       </c>
-      <c r="B9" s="26" t="str">
-        <f>data!$B$6</f>
+      <c r="B9" s="27" t="str">
+        <f>data!$B$7</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="25"/>
-      <c r="B10" s="26"/>
+      <c r="A10" s="26"/>
+      <c r="B10" s="27"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="25">
+      <c r="A11" s="26">
         <v>5</v>
       </c>
-      <c r="B11" s="26" t="str">
-        <f>data!$B$7</f>
+      <c r="B11" s="27" t="str">
+        <f>data!$B$8</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="25"/>
-      <c r="B12" s="26"/>
+      <c r="A12" s="26"/>
+      <c r="B12" s="27"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="25">
+      <c r="A13" s="26">
         <v>6</v>
       </c>
-      <c r="B13" s="26" t="str">
-        <f>data!$B$8</f>
+      <c r="B13" s="27" t="str">
+        <f>data!$B$9</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="25"/>
-      <c r="B14" s="26"/>
+      <c r="A14" s="26"/>
+      <c r="B14" s="27"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="25">
+      <c r="A15" s="26">
         <v>7</v>
       </c>
-      <c r="B15" s="26" t="str">
-        <f>data!$B$9</f>
+      <c r="B15" s="27" t="str">
+        <f>data!$B$10</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="25"/>
-      <c r="B16" s="26"/>
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="25">
+      <c r="A17" s="26">
         <v>8</v>
       </c>
-      <c r="B17" s="26" t="str">
-        <f>data!$B$10</f>
+      <c r="B17" s="27" t="str">
+        <f>data!$B$11</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="25"/>
-      <c r="B18" s="26"/>
+      <c r="A18" s="26"/>
+      <c r="B18" s="27"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="25">
+      <c r="A19" s="26">
         <v>9</v>
       </c>
-      <c r="B19" s="26" t="str">
-        <f>data!$B$11</f>
+      <c r="B19" s="27" t="str">
+        <f>data!$B$12</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="25"/>
-      <c r="B20" s="26"/>
+      <c r="A20" s="26"/>
+      <c r="B20" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
   <si>
     <t>Elimination Round 1</t>
   </si>
@@ -78,6 +78,9 @@
   </si>
   <si>
     <t>Title prefix:</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Number</t>
@@ -758,20 +761,22 @@
       <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
@@ -779,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
@@ -790,10 +795,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
@@ -801,10 +806,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
@@ -812,10 +817,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -823,10 +828,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
@@ -834,10 +839,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
@@ -845,10 +850,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
@@ -856,10 +861,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
@@ -867,10 +872,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -878,10 +883,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true"/>
@@ -1990,7 +1995,7 @@
     </row>
     <row r="6">
       <c r="E6" s="25" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2009,7 +2014,7 @@
     </row>
     <row r="10">
       <c r="E10" s="25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F10" s="24"/>
       <c r="G10" s="21"/>
@@ -2030,7 +2035,7 @@
     </row>
     <row r="14">
       <c r="E14" s="25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I14" s="21"/>
       <c r="K14" s="21"/>
@@ -2051,7 +2056,7 @@
     </row>
     <row r="17">
       <c r="C17" s="25" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" s="21"/>
       <c r="K17" s="21"/>
@@ -2067,7 +2072,7 @@
     </row>
     <row r="19">
       <c r="C19" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D19" s="24"/>
       <c r="E19" s="21"/>
@@ -2083,7 +2088,7 @@
     </row>
     <row r="22">
       <c r="E22" s="25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K22" s="21"/>
     </row>
@@ -2106,7 +2111,7 @@
     </row>
     <row r="26">
       <c r="E26" s="25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F26" s="24"/>
       <c r="G26" s="21"/>
@@ -2129,7 +2134,7 @@
     </row>
     <row r="30">
       <c r="E30" s="25" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I30" s="21"/>
     </row>
@@ -2147,7 +2152,7 @@
     </row>
     <row r="33">
       <c r="C33" s="25" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G33" s="21"/>
     </row>
@@ -2161,7 +2166,7 @@
     </row>
     <row r="35">
       <c r="C35" s="25" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D35" s="24"/>
       <c r="E35" s="21"/>
@@ -2387,18 +2392,19 @@
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
-    <col customWidth="true" max="1" min="1" style="7" width="34"/>
-    <col customWidth="true" max="3" min="2" style="7" width="3.83203125"/>
+    <col customWidth="true" max="1" min="1" style="7" width="30"/>
+    <col customWidth="true" max="3" min="2" style="7" width="5"/>
     <col customWidth="true" max="4" min="4" style="7" width="3"/>
-    <col customWidth="true" max="6" min="5" style="7" width="3.83203125"/>
-    <col customWidth="true" max="7" min="7" style="7" width="34"/>
-    <col customWidth="true" max="8" min="8" style="7" width="3.83203125"/>
-    <col customWidth="true" max="9" min="9" style="7" width="34"/>
-    <col customWidth="true" max="11" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="6" min="5" style="7" width="5"/>
+    <col customWidth="true" max="7" min="7" style="7" width="30"/>
+    <col customWidth="true" max="8" min="8" style="7" width="2"/>
+    <col customWidth="true" max="9" min="9" style="7" width="30"/>
+    <col customWidth="true" max="11" min="10" style="7" width="5"/>
     <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="3.83203125"/>
-    <col customWidth="true" max="15" min="15" style="7" width="34"/>
-    <col max="16384" min="16" style="7" width="10.83203125"/>
+    <col customWidth="true" max="14" min="13" style="7" width="5"/>
+    <col customWidth="true" max="15" min="15" style="7" width="30"/>
+    <col customWidth="true" max="16" min="16" style="7" width="2"/>
+    <col max="16384" min="17" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="17" thickBot="true">
@@ -2422,7 +2428,7 @@
     </row>
     <row r="3">
       <c r="A3" s="20" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -2431,7 +2437,7 @@
       <c r="F3" s="20"/>
       <c r="G3" s="20"/>
       <c r="I3" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J3" s="20"/>
       <c r="K3" s="20"/>
@@ -2442,22 +2448,22 @@
     </row>
     <row r="4">
       <c r="A4" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D4" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="L4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>33</v>
-      </c>
       <c r="O4" s="30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="5">
@@ -2609,17 +2615,17 @@
         <f>'data'!$B$6</f>
       </c>
       <c r="B12" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C12" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D12" s="28"/>
       <c r="E12" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="G12" s="28" t="str">
         <f>'data'!$B$7</f>
@@ -2628,17 +2634,17 @@
         <f>'data'!$B$11</f>
       </c>
       <c r="J12" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K12" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L12" s="28"/>
       <c r="M12" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N12" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="N12" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="O12" s="28" t="str">
         <f>'data'!$B$12</f>
@@ -2646,7 +2652,7 @@
     </row>
     <row r="13">
       <c r="A13" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
@@ -2654,10 +2660,10 @@
       <c r="E13" s="28"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I13" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J13" s="28"/>
       <c r="K13" s="28"/>
@@ -2665,32 +2671,32 @@
       <c r="M13" s="28"/>
       <c r="N13" s="28"/>
       <c r="O13" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G15" s="24"/>
       <c r="N15" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O15" s="24"/>
     </row>
     <row r="16">
       <c r="F16" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G16" s="24"/>
       <c r="N16" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O16" s="24"/>
     </row>
     <row r="24">
       <c r="A24" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="20"/>
       <c r="C24" s="20"/>
@@ -2709,7 +2715,7 @@
     </row>
     <row r="26">
       <c r="A26" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -2718,7 +2724,7 @@
       <c r="F26" s="20"/>
       <c r="G26" s="20"/>
       <c r="I26" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J26" s="20"/>
       <c r="K26" s="20"/>
@@ -2729,22 +2735,22 @@
     </row>
     <row r="27">
       <c r="A27" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D27" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G27" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I27" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="L27" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L27" s="28" t="s">
-        <v>33</v>
-      </c>
       <c r="O27" s="30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="28">
@@ -2896,17 +2902,17 @@
         <f>'data'!$B$3</f>
       </c>
       <c r="B35" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C35" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D35" s="28"/>
       <c r="E35" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F35" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="F35" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="G35" s="28" t="str">
         <f>'data'!$B$4</f>
@@ -2915,17 +2921,17 @@
         <f>'data'!$B$5</f>
       </c>
       <c r="J35" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K35" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L35" s="28"/>
       <c r="M35" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N35" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="N35" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="O35" s="28" t="str">
         <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
@@ -2933,7 +2939,7 @@
     </row>
     <row r="36">
       <c r="A36" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
@@ -2941,10 +2947,10 @@
       <c r="E36" s="28"/>
       <c r="F36" s="28"/>
       <c r="G36" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I36" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J36" s="28"/>
       <c r="K36" s="28"/>
@@ -2952,32 +2958,32 @@
       <c r="M36" s="28"/>
       <c r="N36" s="28"/>
       <c r="O36" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="F38" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G38" s="24"/>
       <c r="N38" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O38" s="24"/>
     </row>
     <row r="39">
       <c r="F39" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G39" s="24"/>
       <c r="N39" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O39" s="24"/>
     </row>
     <row r="42">
       <c r="A42" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B42" s="20"/>
       <c r="C42" s="20"/>
@@ -2986,7 +2992,7 @@
       <c r="F42" s="20"/>
       <c r="G42" s="20"/>
       <c r="I42" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J42" s="20"/>
       <c r="K42" s="20"/>
@@ -2997,22 +3003,22 @@
     </row>
     <row r="43">
       <c r="A43" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D43" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G43" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I43" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G43" s="30" t="s">
+      <c r="L43" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I43" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L43" s="28" t="s">
-        <v>33</v>
-      </c>
       <c r="O43" s="30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44">
@@ -3164,17 +3170,17 @@
         <f>'data'!$B$8</f>
       </c>
       <c r="B51" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C51" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D51" s="28"/>
       <c r="E51" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F51" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="F51" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="G51" s="28" t="str">
         <f>'data'!$B$9</f>
@@ -3183,17 +3189,17 @@
         <f>'data'!$B$10</f>
       </c>
       <c r="J51" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K51" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L51" s="28"/>
       <c r="M51" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N51" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="N51" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="O51" s="28" t="str">
         <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
@@ -3201,7 +3207,7 @@
     </row>
     <row r="52">
       <c r="A52" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B52" s="28"/>
       <c r="C52" s="28"/>
@@ -3209,10 +3215,10 @@
       <c r="E52" s="28"/>
       <c r="F52" s="28"/>
       <c r="G52" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I52" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J52" s="28"/>
       <c r="K52" s="28"/>
@@ -3220,32 +3226,32 @@
       <c r="M52" s="28"/>
       <c r="N52" s="28"/>
       <c r="O52" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="54">
       <c r="F54" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G54" s="24"/>
       <c r="N54" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O54" s="24"/>
     </row>
     <row r="55">
       <c r="F55" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G55" s="24"/>
       <c r="N55" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O55" s="24"/>
     </row>
     <row r="63">
       <c r="A63" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B63" s="20"/>
       <c r="C63" s="20"/>
@@ -3264,7 +3270,7 @@
     </row>
     <row r="65">
       <c r="A65" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B65" s="20"/>
       <c r="C65" s="20"/>
@@ -3273,7 +3279,7 @@
       <c r="F65" s="20"/>
       <c r="G65" s="20"/>
       <c r="I65" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J65" s="20"/>
       <c r="K65" s="20"/>
@@ -3284,22 +3290,22 @@
     </row>
     <row r="66">
       <c r="A66" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D66" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="G66" s="30" t="s">
+        <v>35</v>
+      </c>
+      <c r="I66" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="G66" s="30" t="s">
+      <c r="L66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="I66" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="L66" s="28" t="s">
-        <v>33</v>
-      </c>
       <c r="O66" s="30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="67">
@@ -3451,17 +3457,17 @@
         <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="B74" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C74" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D74" s="28"/>
       <c r="E74" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F74" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="F74" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="G74" s="28" t="str">
         <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
@@ -3470,17 +3476,17 @@
         <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
       <c r="J74" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K74" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="L74" s="28"/>
       <c r="M74" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="N74" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="N74" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="O74" s="28" t="str">
         <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
@@ -3488,7 +3494,7 @@
     </row>
     <row r="75">
       <c r="A75" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B75" s="28"/>
       <c r="C75" s="28"/>
@@ -3496,10 +3502,10 @@
       <c r="E75" s="28"/>
       <c r="F75" s="28"/>
       <c r="G75" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I75" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J75" s="28"/>
       <c r="K75" s="28"/>
@@ -3507,32 +3513,32 @@
       <c r="M75" s="28"/>
       <c r="N75" s="28"/>
       <c r="O75" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="77">
       <c r="F77" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G77" s="24"/>
       <c r="N77" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O77" s="24"/>
     </row>
     <row r="78">
       <c r="F78" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G78" s="24"/>
       <c r="N78" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="O78" s="24"/>
     </row>
     <row r="86">
       <c r="A86" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B86" s="20"/>
       <c r="C86" s="20"/>
@@ -3551,7 +3557,7 @@
     </row>
     <row r="88">
       <c r="A88" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B88" s="20"/>
       <c r="C88" s="20"/>
@@ -3562,13 +3568,13 @@
     </row>
     <row r="89">
       <c r="A89" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D89" s="28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G89" s="30" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="90">
@@ -3654,17 +3660,17 @@
         <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
       <c r="B97" s="28" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C97" s="28" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D97" s="28"/>
       <c r="E97" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="F97" s="28" t="s">
         <v>36</v>
-      </c>
-      <c r="F97" s="28" t="s">
-        <v>35</v>
       </c>
       <c r="G97" s="28" t="str">
         <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
@@ -3672,7 +3678,7 @@
     </row>
     <row r="98">
       <c r="A98" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B98" s="28"/>
       <c r="C98" s="28"/>
@@ -3680,18 +3686,18 @@
       <c r="E98" s="28"/>
       <c r="F98" s="28"/>
       <c r="G98" s="28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100">
       <c r="F100" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G100" s="24"/>
     </row>
     <row r="101">
       <c r="F101" s="7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G101" s="24"/>
     </row>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -143,13 +143,13 @@
     <t>Match 1</t>
   </si>
   <si>
+    <t>White</t>
+  </si>
+  <si>
+    <t>vs</t>
+  </si>
+  <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>vs</t>
-  </si>
-  <si>
-    <t>White</t>
   </si>
   <si>
     <t>V</t>
@@ -2447,28 +2447,28 @@
       <c r="O3" s="20"/>
     </row>
     <row r="4">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G4" s="30" t="s">
+      <c r="G4" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="I4" s="29" t="s">
+      <c r="I4" s="30" t="s">
         <v>33</v>
       </c>
       <c r="L4" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="30" t="s">
+      <c r="O4" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="28" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
@@ -2476,10 +2476,10 @@
       <c r="E5" s="28"/>
       <c r="F5" s="28"/>
       <c r="G5" s="28" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I5" s="28" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="J5" s="28"/>
       <c r="K5" s="28"/>
@@ -2487,7 +2487,7 @@
       <c r="M5" s="28"/>
       <c r="N5" s="28"/>
       <c r="O5" s="28" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="6">
@@ -2612,7 +2612,7 @@
     </row>
     <row r="12">
       <c r="A12" s="28" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B12" s="28" t="s">
         <v>36</v>
@@ -2628,10 +2628,10 @@
         <v>36</v>
       </c>
       <c r="G12" s="28" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$6</f>
       </c>
       <c r="I12" s="28" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$12</f>
       </c>
       <c r="J12" s="28" t="s">
         <v>36</v>
@@ -2647,7 +2647,7 @@
         <v>36</v>
       </c>
       <c r="O12" s="28" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="13">
@@ -2734,28 +2734,28 @@
       <c r="O26" s="20"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D27" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="30" t="s">
+      <c r="G27" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="29" t="s">
+      <c r="I27" s="30" t="s">
         <v>33</v>
       </c>
       <c r="L27" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O27" s="30" t="s">
+      <c r="O27" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="28" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -2763,10 +2763,10 @@
       <c r="E28" s="28"/>
       <c r="F28" s="28"/>
       <c r="G28" s="28" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I28" s="28" t="str">
-        <f>'data'!$B$5</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="J28" s="28"/>
       <c r="K28" s="28"/>
@@ -2774,7 +2774,7 @@
       <c r="M28" s="28"/>
       <c r="N28" s="28"/>
       <c r="O28" s="28" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
+        <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="29">
@@ -2899,7 +2899,7 @@
     </row>
     <row r="35">
       <c r="A35" s="28" t="str">
-        <f>'data'!$B$3</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B35" s="28" t="s">
         <v>36</v>
@@ -2915,10 +2915,10 @@
         <v>36</v>
       </c>
       <c r="G35" s="28" t="str">
-        <f>'data'!$B$4</f>
+        <f>'data'!$B$3</f>
       </c>
       <c r="I35" s="28" t="str">
-        <f>'data'!$B$5</f>
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
       </c>
       <c r="J35" s="28" t="s">
         <v>36</v>
@@ -2934,7 +2934,7 @@
         <v>36</v>
       </c>
       <c r="O35" s="28" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
+        <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="36">
@@ -3002,28 +3002,28 @@
       <c r="O42" s="20"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="s">
+      <c r="A43" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D43" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G43" s="30" t="s">
+      <c r="G43" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="I43" s="29" t="s">
+      <c r="I43" s="30" t="s">
         <v>33</v>
       </c>
       <c r="L43" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O43" s="30" t="s">
+      <c r="O43" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="28" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="B44" s="28"/>
       <c r="C44" s="28"/>
@@ -3031,10 +3031,10 @@
       <c r="E44" s="28"/>
       <c r="F44" s="28"/>
       <c r="G44" s="28" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="I44" s="28" t="str">
-        <f>'data'!$B$10</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="J44" s="28"/>
       <c r="K44" s="28"/>
@@ -3042,7 +3042,7 @@
       <c r="M44" s="28"/>
       <c r="N44" s="28"/>
       <c r="O44" s="28" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="45">
@@ -3167,7 +3167,7 @@
     </row>
     <row r="51">
       <c r="A51" s="28" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$9</f>
       </c>
       <c r="B51" s="28" t="s">
         <v>36</v>
@@ -3183,10 +3183,10 @@
         <v>36</v>
       </c>
       <c r="G51" s="28" t="str">
-        <f>'data'!$B$9</f>
+        <f>'data'!$B$8</f>
       </c>
       <c r="I51" s="28" t="str">
-        <f>'data'!$B$10</f>
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
       </c>
       <c r="J51" s="28" t="s">
         <v>36</v>
@@ -3202,7 +3202,7 @@
         <v>36</v>
       </c>
       <c r="O51" s="28" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="52">
@@ -3289,28 +3289,28 @@
       <c r="O65" s="20"/>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G66" s="30" t="s">
+      <c r="G66" s="29" t="s">
         <v>35</v>
       </c>
-      <c r="I66" s="29" t="s">
+      <c r="I66" s="30" t="s">
         <v>33</v>
       </c>
       <c r="L66" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="O66" s="30" t="s">
+      <c r="O66" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="28" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
       </c>
       <c r="B67" s="28"/>
       <c r="C67" s="28"/>
@@ -3318,10 +3318,10 @@
       <c r="E67" s="28"/>
       <c r="F67" s="28"/>
       <c r="G67" s="28" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="I67" s="28" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
       </c>
       <c r="J67" s="28"/>
       <c r="K67" s="28"/>
@@ -3329,7 +3329,7 @@
       <c r="M67" s="28"/>
       <c r="N67" s="28"/>
       <c r="O67" s="28" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
     </row>
     <row r="68">
@@ -3454,7 +3454,7 @@
     </row>
     <row r="74">
       <c r="A74" s="28" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
       </c>
       <c r="B74" s="28" t="s">
         <v>36</v>
@@ -3470,10 +3470,10 @@
         <v>36</v>
       </c>
       <c r="G74" s="28" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
       </c>
       <c r="I74" s="28" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
       </c>
       <c r="J74" s="28" t="s">
         <v>36</v>
@@ -3489,7 +3489,7 @@
         <v>36</v>
       </c>
       <c r="O74" s="28" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
       </c>
     </row>
     <row r="75">
@@ -3567,19 +3567,19 @@
       <c r="G88" s="20"/>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="s">
+      <c r="A89" s="30" t="s">
         <v>33</v>
       </c>
       <c r="D89" s="28" t="s">
         <v>34</v>
       </c>
-      <c r="G89" s="30" t="s">
+      <c r="G89" s="29" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="28" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
       </c>
       <c r="B90" s="28"/>
       <c r="C90" s="28"/>
@@ -3587,7 +3587,7 @@
       <c r="E90" s="28"/>
       <c r="F90" s="28"/>
       <c r="G90" s="28" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
     </row>
     <row r="91">
@@ -3657,7 +3657,7 @@
     </row>
     <row r="97">
       <c r="A97" s="28" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
       </c>
       <c r="B97" s="28" t="s">
         <v>36</v>
@@ -3673,7 +3673,7 @@
         <v>36</v>
       </c>
       <c r="G97" s="28" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
       </c>
     </row>
     <row r="98">

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="26060" windowHeight="21580" activeTab="1"/>
+    <workbookView xWindow="34720" yWindow="1400" windowWidth="38080" windowHeight="20800" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,7 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$20</definedName>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -42,10 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
-  <si>
-    <t>Elimination Round 1</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
   <si>
     <t>Tournament Pools</t>
   </si>
@@ -140,7 +138,10 @@
     <t>Thomas King</t>
   </si>
   <si>
-    <t>Match 1</t>
+    <t>Shiaijo A</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 1</t>
   </si>
   <si>
     <t>White</t>
@@ -167,37 +168,49 @@
     <t>2.</t>
   </si>
   <si>
-    <t>Match 2</t>
-  </si>
-  <si>
-    <t>Elimination Round 2</t>
-  </si>
-  <si>
-    <t>Match 3</t>
-  </si>
-  <si>
-    <t>Match 4</t>
-  </si>
-  <si>
-    <t>Match 5</t>
-  </si>
-  <si>
-    <t>Match 6</t>
-  </si>
-  <si>
-    <t>Elimination Round 3</t>
-  </si>
-  <si>
-    <t>Match 7</t>
-  </si>
-  <si>
-    <t>Match 8</t>
-  </si>
-  <si>
-    <t>Elimination Round 4</t>
-  </si>
-  <si>
-    <t>Match 9</t>
+    <t>Round 1 - Match 2</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 4</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 5</t>
+  </si>
+  <si>
+    <t>Round 2 - Match 6</t>
+  </si>
+  <si>
+    <t>Round 3 - Match 7</t>
+  </si>
+  <si>
+    <t>Round 3 - Match 8</t>
+  </si>
+  <si>
+    <t>Round 4 - Match 9</t>
+  </si>
+  <si>
+    <t>Tournament Summary</t>
+  </si>
+  <si>
+    <t>Total Pool Time</t>
+  </si>
+  <si>
+    <t>Total Elimination Time</t>
+  </si>
+  <si>
+    <t>Grand Total (Sequential)</t>
+  </si>
+  <si>
+    <t>Grand Total (Parallel across Courts)</t>
+  </si>
+  <si>
+    <t>Start Time:</t>
+  </si>
+  <si>
+    <t>Estimated Finish Time</t>
   </si>
 </sst>
 </file>
@@ -340,7 +353,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -360,43 +373,6 @@
       </top>
       <bottom style="medium">
         <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -455,7 +431,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
@@ -493,46 +469,41 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
+      <alignment/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="true" applyAlignment="false">
-      <alignment/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="10" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -759,24 +730,24 @@
   <sheetData>
     <row r="1" spans="1:2" ht="12.75" customHeight="true">
       <c r="A1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="12.75" customHeight="true">
       <c r="A2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
         <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="12.75" customHeight="true">
@@ -784,10 +755,10 @@
         <v>0</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
-      </c>
-      <c r="C3" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="12.75" customHeight="true">
@@ -795,10 +766,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="12.75" customHeight="true">
@@ -806,10 +777,10 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="12.75" customHeight="true">
@@ -817,10 +788,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="12.75" customHeight="true">
@@ -828,10 +799,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="12.75" customHeight="true">
@@ -839,10 +810,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="12.75" customHeight="true">
@@ -850,10 +821,10 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="12.75" customHeight="true">
@@ -861,10 +832,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="12.75" customHeight="true">
@@ -872,10 +843,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="12.75" customHeight="true">
@@ -883,10 +854,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="13" spans="1:2" ht="12.75" customHeight="true"/>
@@ -1974,202 +1945,202 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="20" t="str">
+      <c r="A1" s="18" t="str">
         <f>IF(data!$B$1="","Shiaijo A",data!$B$1&amp;" - Shiaijo A")</f>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18"/>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
     </row>
     <row r="6">
-      <c r="E6" s="25" t="s">
-        <v>17</v>
+      <c r="E6" s="23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="23"/>
-      <c r="G7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="19"/>
     </row>
     <row r="8">
-      <c r="G8" s="22">
+      <c r="G8" s="20">
         <v>3</v>
       </c>
     </row>
     <row r="9">
-      <c r="G9" s="21"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="21"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="19"/>
     </row>
     <row r="10">
-      <c r="E10" s="25" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" s="24"/>
-      <c r="G10" s="21"/>
-      <c r="I10" s="21"/>
+      <c r="E10" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" s="22"/>
+      <c r="G10" s="19"/>
+      <c r="I10" s="19"/>
     </row>
     <row r="11">
-      <c r="I11" s="21"/>
+      <c r="I11" s="19"/>
     </row>
     <row r="12">
-      <c r="I12" s="22">
+      <c r="I12" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="13">
-      <c r="I13" s="21"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="21"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="19"/>
     </row>
     <row r="14">
-      <c r="E14" s="25" t="s">
-        <v>21</v>
-      </c>
-      <c r="I14" s="21"/>
-      <c r="K14" s="21"/>
+      <c r="E14" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" s="19"/>
+      <c r="K14" s="19"/>
     </row>
     <row r="15">
-      <c r="F15" s="23"/>
-      <c r="G15" s="21"/>
-      <c r="I15" s="21"/>
-      <c r="K15" s="21"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="K15" s="19"/>
     </row>
     <row r="16">
-      <c r="G16" s="22">
+      <c r="G16" s="20">
         <v>4</v>
       </c>
-      <c r="H16" s="24"/>
-      <c r="I16" s="21"/>
-      <c r="K16" s="21"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="19"/>
+      <c r="K16" s="19"/>
     </row>
     <row r="17">
-      <c r="C17" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="21"/>
-      <c r="K17" s="21"/>
+      <c r="C17" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="G17" s="19"/>
+      <c r="K17" s="19"/>
     </row>
     <row r="18">
-      <c r="D18" s="23"/>
-      <c r="E18" s="22">
+      <c r="D18" s="21"/>
+      <c r="E18" s="20">
         <v>1</v>
       </c>
-      <c r="F18" s="24"/>
-      <c r="G18" s="21"/>
-      <c r="K18" s="21"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="19"/>
+      <c r="K18" s="19"/>
     </row>
     <row r="19">
-      <c r="C19" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="21"/>
-      <c r="K19" s="21"/>
+      <c r="C19" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="19"/>
+      <c r="K19" s="19"/>
     </row>
     <row r="20">
-      <c r="K20" s="22">
+      <c r="K20" s="20">
         <v>9</v>
       </c>
     </row>
     <row r="21">
-      <c r="K21" s="21"/>
+      <c r="K21" s="19"/>
     </row>
     <row r="22">
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22" s="19"/>
+    </row>
+    <row r="23">
+      <c r="F23" s="21"/>
+      <c r="G23" s="19"/>
+      <c r="K23" s="19"/>
+    </row>
+    <row r="24">
+      <c r="G24" s="20">
+        <v>5</v>
+      </c>
+      <c r="K24" s="19"/>
+    </row>
+    <row r="25">
+      <c r="G25" s="19"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="19"/>
+      <c r="K25" s="19"/>
+    </row>
+    <row r="26">
+      <c r="E26" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="K22" s="21"/>
-    </row>
-    <row r="23">
-      <c r="F23" s="23"/>
-      <c r="G23" s="21"/>
-      <c r="K23" s="21"/>
-    </row>
-    <row r="24">
-      <c r="G24" s="22">
-        <v>5</v>
-      </c>
-      <c r="K24" s="21"/>
-    </row>
-    <row r="25">
-      <c r="G25" s="21"/>
-      <c r="H25" s="23"/>
-      <c r="I25" s="21"/>
-      <c r="K25" s="21"/>
-    </row>
-    <row r="26">
-      <c r="E26" s="25" t="s">
+      <c r="F26" s="22"/>
+      <c r="G26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="K26" s="19"/>
+    </row>
+    <row r="27">
+      <c r="I27" s="19"/>
+      <c r="K27" s="19"/>
+    </row>
+    <row r="28">
+      <c r="I28" s="20">
+        <v>8</v>
+      </c>
+      <c r="J28" s="22"/>
+      <c r="K28" s="19"/>
+    </row>
+    <row r="29">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30">
+      <c r="E30" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="F26" s="24"/>
-      <c r="G26" s="21"/>
-      <c r="I26" s="21"/>
-      <c r="K26" s="21"/>
-    </row>
-    <row r="27">
-      <c r="I27" s="21"/>
-      <c r="K27" s="21"/>
-    </row>
-    <row r="28">
-      <c r="I28" s="22">
-        <v>8</v>
-      </c>
-      <c r="J28" s="24"/>
-      <c r="K28" s="21"/>
-    </row>
-    <row r="29">
-      <c r="I29" s="21"/>
-    </row>
-    <row r="30">
-      <c r="E30" s="25" t="s">
+      <c r="I30" s="19"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="21"/>
+      <c r="G31" s="19"/>
+      <c r="I31" s="19"/>
+    </row>
+    <row r="32">
+      <c r="G32" s="20">
+        <v>6</v>
+      </c>
+      <c r="H32" s="22"/>
+      <c r="I32" s="19"/>
+    </row>
+    <row r="33">
+      <c r="C33" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="I30" s="21"/>
-    </row>
-    <row r="31">
-      <c r="F31" s="23"/>
-      <c r="G31" s="21"/>
-      <c r="I31" s="21"/>
-    </row>
-    <row r="32">
-      <c r="G32" s="22">
-        <v>6</v>
-      </c>
-      <c r="H32" s="24"/>
-      <c r="I32" s="21"/>
-    </row>
-    <row r="33">
-      <c r="C33" s="25" t="s">
+      <c r="G33" s="19"/>
+    </row>
+    <row r="34">
+      <c r="D34" s="21"/>
+      <c r="E34" s="20">
+        <v>2</v>
+      </c>
+      <c r="F34" s="22"/>
+      <c r="G34" s="19"/>
+    </row>
+    <row r="35">
+      <c r="C35" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="21"/>
-    </row>
-    <row r="34">
-      <c r="D34" s="23"/>
-      <c r="E34" s="22">
-        <v>2</v>
-      </c>
-      <c r="F34" s="24"/>
-      <c r="G34" s="21"/>
-    </row>
-    <row r="35">
-      <c r="C35" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="24"/>
-      <c r="E35" s="21"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2193,28 +2164,28 @@
   <sheetData>
     <row r="1" spans="1:8" ht="51">
       <c r="A1" s="13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="C1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="D1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="F1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="G1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="H1" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="11" customFormat="true" ht="16">
@@ -2240,8 +2211,8 @@
       <c r="G2" s="12">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="H2" s="12">
-        <f>E2+(A2*C2*F2)+G2</f>
+      <c r="H2" s="12" t="str">
+        <f>C2*I2+J2</f>
         <v>6.041666666666666E-2</v>
       </c>
     </row>
@@ -2305,26 +2276,26 @@
     </row>
     <row r="7" spans="1:8" ht="51">
       <c r="A7" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C7" s="13"/>
       <c r="D7" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="F7" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="G7" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="H7" s="13" t="s">
         <v>8</v>
-      </c>
-      <c r="H7" s="13" t="s">
-        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="11" customFormat="true" ht="16">
@@ -2382,13 +2353,90 @@
       <c r="G11" s="14"/>
       <c r="H11" s="14"/>
     </row>
+    <row r="13">
+      <c r="E13" s="18" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26" t="str">
+        <f>H2</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="F15" s="26"/>
+      <c r="G15" s="26"/>
+      <c r="H15" s="26" t="str">
+        <f>H8</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26" t="str">
+        <f>H14+H15</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="26" t="str">
+        <f>H16/A14</f>
+      </c>
+    </row>
+    <row r="18">
+      <c r="E18" s="18" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="29">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="E19" s="18" t="s">
+        <v>55</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="29" t="str">
+        <f>H18+H17</f>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="E13:H13"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3D4E4C4-15C1-724B-94C9-DD9C94F4D3CF}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
@@ -2398,1326 +2446,1368 @@
     <col customWidth="true" max="6" min="5" style="7" width="5"/>
     <col customWidth="true" max="7" min="7" style="7" width="30"/>
     <col customWidth="true" max="8" min="8" style="7" width="2"/>
-    <col customWidth="true" max="9" min="9" style="7" width="30"/>
-    <col customWidth="true" max="11" min="10" style="7" width="5"/>
-    <col customWidth="true" max="12" min="12" style="7" width="3"/>
-    <col customWidth="true" max="14" min="13" style="7" width="5"/>
-    <col customWidth="true" max="15" min="15" style="7" width="30"/>
-    <col customWidth="true" max="16" min="16" style="7" width="2"/>
-    <col max="16384" min="17" style="7" width="10.83203125"/>
+    <col customWidth="true" max="9" min="9" style="7" width="34.83203125"/>
+    <col customWidth="true" max="14" min="10" style="7" width="3.83203125"/>
+    <col customWidth="true" max="15" min="15" style="7" width="34.83203125"/>
+    <col max="16384" min="16" style="7" width="10.83203125"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="17" thickBot="true">
-      <c r="A1" s="20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
+    <row r="1" spans="1:15">
+      <c r="A1" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
+      <c r="M1" s="17"/>
+      <c r="N1" s="17"/>
+      <c r="O1" s="17"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
     </row>
     <row r="3">
-      <c r="A3" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-      <c r="I3" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="20"/>
-      <c r="N3" s="20"/>
-      <c r="O3" s="20"/>
+      <c r="A3" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="27" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D4" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G4" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="I4" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O4" s="29" t="s">
-        <v>35</v>
+      <c r="A4" s="26" t="str">
+        <f>'data'!$B$7</f>
+      </c>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26" t="str">
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="str">
+      <c r="A5" s="26">
+        <v>1</v>
+      </c>
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="26">
+        <v>2</v>
+      </c>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="26">
+        <v>3</v>
+      </c>
+      <c r="B7" s="26"/>
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="26">
+        <v>4</v>
+      </c>
+      <c r="B8" s="26"/>
+      <c r="C8" s="26"/>
+      <c r="D8" s="26"/>
+      <c r="E8" s="26"/>
+      <c r="F8" s="26"/>
+      <c r="G8" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="26">
+        <v>5</v>
+      </c>
+      <c r="B9" s="26"/>
+      <c r="C9" s="26"/>
+      <c r="D9" s="26"/>
+      <c r="E9" s="26"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="26" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28" t="str">
+      <c r="B11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="26" t="str">
         <f>'data'!$B$6</f>
       </c>
-      <c r="I5" s="28" t="str">
-        <f>'data'!$B$12</f>
-      </c>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="28"/>
-      <c r="M5" s="28"/>
-      <c r="N5" s="28"/>
-      <c r="O5" s="28" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="28">
-        <v>1</v>
-      </c>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="28">
-        <v>1</v>
-      </c>
-      <c r="I6" s="28">
-        <v>1</v>
-      </c>
-      <c r="J6" s="28"/>
-      <c r="K6" s="28"/>
-      <c r="L6" s="28"/>
-      <c r="M6" s="28"/>
-      <c r="N6" s="28"/>
-      <c r="O6" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="28">
-        <v>2</v>
-      </c>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="28"/>
-      <c r="F7" s="28"/>
-      <c r="G7" s="28">
-        <v>2</v>
-      </c>
-      <c r="I7" s="28">
-        <v>2</v>
-      </c>
-      <c r="J7" s="28"/>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28"/>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="28">
-        <v>3</v>
-      </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
-      <c r="F8" s="28"/>
-      <c r="G8" s="28">
-        <v>3</v>
-      </c>
-      <c r="I8" s="28">
-        <v>3</v>
-      </c>
-      <c r="J8" s="28"/>
-      <c r="K8" s="28"/>
-      <c r="L8" s="28"/>
-      <c r="M8" s="28"/>
-      <c r="N8" s="28"/>
-      <c r="O8" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="28">
-        <v>4</v>
-      </c>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28">
-        <v>4</v>
-      </c>
-      <c r="I9" s="28">
-        <v>4</v>
-      </c>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-      <c r="M9" s="28"/>
-      <c r="N9" s="28"/>
-      <c r="O9" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="28">
-        <v>5</v>
-      </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28">
-        <v>5</v>
-      </c>
-      <c r="I10" s="28">
-        <v>5</v>
-      </c>
-      <c r="J10" s="28"/>
-      <c r="K10" s="28"/>
-      <c r="L10" s="28"/>
-      <c r="M10" s="28"/>
-      <c r="N10" s="28"/>
-      <c r="O10" s="28">
-        <v>5</v>
-      </c>
     </row>
     <row r="12">
-      <c r="A12" s="28" t="str">
-        <f>'data'!$B$7</f>
-      </c>
-      <c r="B12" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="28"/>
-      <c r="E12" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F12" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12" s="28" t="str">
-        <f>'data'!$B$6</f>
-      </c>
-      <c r="I12" s="28" t="str">
-        <f>'data'!$B$12</f>
-      </c>
-      <c r="J12" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="K12" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L12" s="28"/>
-      <c r="M12" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N12" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="O12" s="28" t="str">
-        <f>'data'!$B$11</f>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="28" t="s">
+      <c r="A12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="28"/>
-      <c r="E13" s="28"/>
-      <c r="F13" s="28"/>
-      <c r="G13" s="28" t="s">
+      <c r="B12" s="26"/>
+      <c r="C12" s="26"/>
+      <c r="D12" s="26"/>
+      <c r="E12" s="26"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="I13" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J13" s="28"/>
-      <c r="K13" s="28"/>
-      <c r="L13" s="28"/>
-      <c r="M13" s="28"/>
-      <c r="N13" s="28"/>
-      <c r="O13" s="28" t="s">
-        <v>38</v>
-      </c>
+    </row>
+    <row r="14">
+      <c r="F14" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G14" s="22"/>
     </row>
     <row r="15">
       <c r="F15" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G15" s="22"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G19" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="B20" s="26"/>
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26"/>
+      <c r="G20" s="26" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="26">
+        <v>1</v>
+      </c>
+      <c r="B21" s="26"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="26"/>
+      <c r="G21" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="26">
+        <v>2</v>
+      </c>
+      <c r="B22" s="26"/>
+      <c r="C22" s="26"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="26">
+        <v>3</v>
+      </c>
+      <c r="B23" s="26"/>
+      <c r="C23" s="26"/>
+      <c r="D23" s="26"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="26"/>
+      <c r="G23" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="26">
+        <v>4</v>
+      </c>
+      <c r="B24" s="26"/>
+      <c r="C24" s="26"/>
+      <c r="D24" s="26"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="26"/>
+      <c r="G24" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="26">
+        <v>5</v>
+      </c>
+      <c r="B25" s="26"/>
+      <c r="C25" s="26"/>
+      <c r="D25" s="26"/>
+      <c r="E25" s="26"/>
+      <c r="F25" s="26"/>
+      <c r="G25" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="26" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="26" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
+      <c r="D28" s="26"/>
+      <c r="E28" s="26"/>
+      <c r="F28" s="26"/>
+      <c r="G28" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="F30" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G15" s="24"/>
-      <c r="N15" s="7" t="s">
+      <c r="G30" s="22"/>
+    </row>
+    <row r="31">
+      <c r="F31" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="22"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" s="18"/>
+      <c r="C39" s="18"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D40" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G40" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="26" t="str">
+        <f>'data'!$B$4</f>
+      </c>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="D41" s="26"/>
+      <c r="E41" s="26"/>
+      <c r="F41" s="26"/>
+      <c r="G41" s="26" t="str">
+        <f>'data'!$B$3</f>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="26">
+        <v>1</v>
+      </c>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="D42" s="26"/>
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="26">
+        <v>2</v>
+      </c>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="D43" s="26"/>
+      <c r="E43" s="26"/>
+      <c r="F43" s="26"/>
+      <c r="G43" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="26">
+        <v>3</v>
+      </c>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="26"/>
+      <c r="G44" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="26">
+        <v>4</v>
+      </c>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="D45" s="26"/>
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="26">
+        <v>5</v>
+      </c>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="D46" s="26"/>
+      <c r="E46" s="26"/>
+      <c r="F46" s="26"/>
+      <c r="G46" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="26" t="str">
+        <f>'data'!$B$4</f>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C48" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D48" s="26"/>
+      <c r="E48" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F48" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G48" s="26" t="str">
+        <f>'data'!$B$3</f>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="D49" s="26"/>
+      <c r="E49" s="26"/>
+      <c r="F49" s="26"/>
+      <c r="G49" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="F51" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="O15" s="24"/>
-    </row>
-    <row r="16">
-      <c r="F16" s="7" t="s">
+      <c r="G51" s="22"/>
+    </row>
+    <row r="52">
+      <c r="F52" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G16" s="24"/>
-      <c r="N16" s="7" t="s">
+      <c r="G52" s="22"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="26" t="str">
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G14)</f>
+      </c>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
+      <c r="D57" s="26"/>
+      <c r="E57" s="26"/>
+      <c r="F57" s="26"/>
+      <c r="G57" s="26" t="str">
+        <f>'data'!$B$5</f>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="26">
+        <v>1</v>
+      </c>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="26"/>
+      <c r="E58" s="26"/>
+      <c r="F58" s="26"/>
+      <c r="G58" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="26">
+        <v>2</v>
+      </c>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
+      <c r="D59" s="26"/>
+      <c r="E59" s="26"/>
+      <c r="F59" s="26"/>
+      <c r="G59" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="26">
+        <v>3</v>
+      </c>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
+      <c r="D60" s="26"/>
+      <c r="E60" s="26"/>
+      <c r="F60" s="26"/>
+      <c r="G60" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="26">
+        <v>4</v>
+      </c>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="26"/>
+      <c r="G61" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="26">
+        <v>5</v>
+      </c>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
+      <c r="D62" s="26"/>
+      <c r="E62" s="26"/>
+      <c r="F62" s="26"/>
+      <c r="G62" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="26" t="str">
+        <f>CONCATENATE("M 1 ",'Elimination Matches'!G14)</f>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C64" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D64" s="26"/>
+      <c r="E64" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F64" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G64" s="26" t="str">
+        <f>'data'!$B$5</f>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
+      <c r="D65" s="26"/>
+      <c r="E65" s="26"/>
+      <c r="F65" s="26"/>
+      <c r="G65" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="F67" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G67" s="22"/>
+    </row>
+    <row r="68">
+      <c r="F68" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="O16" s="24"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="20"/>
-      <c r="C24" s="20"/>
-      <c r="D24" s="20"/>
-      <c r="E24" s="20"/>
-      <c r="F24" s="20"/>
-      <c r="G24" s="20"/>
-      <c r="H24" s="20"/>
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="20"/>
-      <c r="N24" s="20"/>
-      <c r="O24" s="20"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B26" s="20"/>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="I26" s="20" t="s">
+      <c r="G68" s="22"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="30" t="s">
+      <c r="B71" s="18"/>
+      <c r="C71" s="18"/>
+      <c r="D71" s="18"/>
+      <c r="E71" s="18"/>
+      <c r="F71" s="18"/>
+      <c r="G71" s="18"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="D27" s="28" t="s">
+      <c r="D72" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G72" s="27" t="s">
         <v>35</v>
       </c>
-      <c r="I27" s="30" t="s">
+    </row>
+    <row r="73">
+      <c r="A73" s="26" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
+      <c r="D73" s="26"/>
+      <c r="E73" s="26"/>
+      <c r="F73" s="26"/>
+      <c r="G73" s="26" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="26">
+        <v>1</v>
+      </c>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="26"/>
+      <c r="E74" s="26"/>
+      <c r="F74" s="26"/>
+      <c r="G74" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="26">
+        <v>2</v>
+      </c>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
+      <c r="D75" s="26"/>
+      <c r="E75" s="26"/>
+      <c r="F75" s="26"/>
+      <c r="G75" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="26">
+        <v>3</v>
+      </c>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
+      <c r="D76" s="26"/>
+      <c r="E76" s="26"/>
+      <c r="F76" s="26"/>
+      <c r="G76" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="26">
+        <v>4</v>
+      </c>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
+      <c r="D77" s="26"/>
+      <c r="E77" s="26"/>
+      <c r="F77" s="26"/>
+      <c r="G77" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="26">
+        <v>5</v>
+      </c>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
+      <c r="D78" s="26"/>
+      <c r="E78" s="26"/>
+      <c r="F78" s="26"/>
+      <c r="G78" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="26" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C80" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D80" s="26"/>
+      <c r="E80" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F80" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" s="26" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
+      <c r="D81" s="26"/>
+      <c r="E81" s="26"/>
+      <c r="F81" s="26"/>
+      <c r="G81" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="F83" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G83" s="22"/>
+    </row>
+    <row r="84">
+      <c r="F84" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G84" s="22"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B87" s="18"/>
+      <c r="C87" s="18"/>
+      <c r="D87" s="18"/>
+      <c r="E87" s="18"/>
+      <c r="F87" s="18"/>
+      <c r="G87" s="18"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="L27" s="28" t="s">
+      <c r="D88" s="26" t="s">
         <v>34</v>
       </c>
-      <c r="O27" s="29" t="s">
+      <c r="G88" s="27" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="28" t="str">
-        <f>'data'!$B$4</f>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28" t="str">
-        <f>'data'!$B$3</f>
-      </c>
-      <c r="I28" s="28" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
-      </c>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
-      <c r="L28" s="28"/>
-      <c r="M28" s="28"/>
-      <c r="N28" s="28"/>
-      <c r="O28" s="28" t="str">
-        <f>'data'!$B$5</f>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="28">
+    <row r="89">
+      <c r="A89" s="26" t="str">
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!G30)</f>
+      </c>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
+      <c r="D89" s="26"/>
+      <c r="E89" s="26"/>
+      <c r="F89" s="26"/>
+      <c r="G89" s="26" t="str">
+        <f>'data'!$B$10</f>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="26">
         <v>1</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28">
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
+      <c r="D90" s="26"/>
+      <c r="E90" s="26"/>
+      <c r="F90" s="26"/>
+      <c r="G90" s="26">
         <v>1</v>
       </c>
-      <c r="I29" s="28">
-        <v>1</v>
-      </c>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="28">
+    </row>
+    <row r="91">
+      <c r="A91" s="26">
         <v>2</v>
       </c>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28">
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
+      <c r="D91" s="26"/>
+      <c r="E91" s="26"/>
+      <c r="F91" s="26"/>
+      <c r="G91" s="26">
         <v>2</v>
       </c>
-      <c r="I30" s="28">
-        <v>2</v>
-      </c>
-      <c r="J30" s="28"/>
-      <c r="K30" s="28"/>
-      <c r="L30" s="28"/>
-      <c r="M30" s="28"/>
-      <c r="N30" s="28"/>
-      <c r="O30" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="28">
+    </row>
+    <row r="92">
+      <c r="A92" s="26">
         <v>3</v>
       </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28">
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
+      <c r="D92" s="26"/>
+      <c r="E92" s="26"/>
+      <c r="F92" s="26"/>
+      <c r="G92" s="26">
         <v>3</v>
       </c>
-      <c r="I31" s="28">
-        <v>3</v>
-      </c>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-      <c r="O31" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="28">
+    </row>
+    <row r="93">
+      <c r="A93" s="26">
         <v>4</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28">
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
+      <c r="D93" s="26"/>
+      <c r="E93" s="26"/>
+      <c r="F93" s="26"/>
+      <c r="G93" s="26">
         <v>4</v>
       </c>
-      <c r="I32" s="28">
-        <v>4</v>
-      </c>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="28">
+    </row>
+    <row r="94">
+      <c r="A94" s="26">
         <v>5</v>
       </c>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="F33" s="28"/>
-      <c r="G33" s="28">
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
+      <c r="D94" s="26"/>
+      <c r="E94" s="26"/>
+      <c r="F94" s="26"/>
+      <c r="G94" s="26">
         <v>5</v>
       </c>
-      <c r="I33" s="28">
-        <v>5</v>
-      </c>
-      <c r="J33" s="28"/>
-      <c r="K33" s="28"/>
-      <c r="L33" s="28"/>
-      <c r="M33" s="28"/>
-      <c r="N33" s="28"/>
-      <c r="O33" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="28" t="str">
-        <f>'data'!$B$4</f>
-      </c>
-      <c r="B35" s="28" t="s">
+    </row>
+    <row r="96">
+      <c r="A96" s="26" t="str">
+        <f>CONCATENATE("M 2 ",'Elimination Matches'!G30)</f>
+      </c>
+      <c r="B96" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="C35" s="28" t="s">
+      <c r="C96" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28" t="s">
+      <c r="D96" s="26"/>
+      <c r="E96" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="28" t="s">
+      <c r="F96" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="G35" s="28" t="str">
-        <f>'data'!$B$3</f>
-      </c>
-      <c r="I35" s="28" t="str">
-        <f>CONCATENATE("M 1 ",'Elimination Matches'!G15)</f>
-      </c>
-      <c r="J35" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="K35" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L35" s="28"/>
-      <c r="M35" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N35" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="O35" s="28" t="str">
-        <f>'data'!$B$5</f>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="28" t="s">
+      <c r="G96" s="26" t="str">
+        <f>'data'!$B$10</f>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28" t="s">
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
+      <c r="D97" s="26"/>
+      <c r="E97" s="26"/>
+      <c r="F97" s="26"/>
+      <c r="G97" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="I36" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
-      <c r="L36" s="28"/>
-      <c r="M36" s="28"/>
-      <c r="N36" s="28"/>
-      <c r="O36" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="F38" s="7" t="s">
+    </row>
+    <row r="99">
+      <c r="F99" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G38" s="24"/>
-      <c r="N38" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O38" s="24"/>
-    </row>
-    <row r="39">
-      <c r="F39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G39" s="24"/>
-      <c r="N39" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O39" s="24"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="I42" s="20" t="s">
-        <v>46</v>
-      </c>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="20"/>
-      <c r="N42" s="20"/>
-      <c r="O42" s="20"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D43" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G43" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="I43" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L43" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O43" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="28" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
-      <c r="D44" s="28"/>
-      <c r="E44" s="28"/>
-      <c r="F44" s="28"/>
-      <c r="G44" s="28" t="str">
-        <f>'data'!$B$8</f>
-      </c>
-      <c r="I44" s="28" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
-      </c>
-      <c r="J44" s="28"/>
-      <c r="K44" s="28"/>
-      <c r="L44" s="28"/>
-      <c r="M44" s="28"/>
-      <c r="N44" s="28"/>
-      <c r="O44" s="28" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="28">
-        <v>1</v>
-      </c>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28">
-        <v>1</v>
-      </c>
-      <c r="I45" s="28">
-        <v>1</v>
-      </c>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
-      <c r="L45" s="28"/>
-      <c r="M45" s="28"/>
-      <c r="N45" s="28"/>
-      <c r="O45" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="28">
-        <v>2</v>
-      </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28">
-        <v>2</v>
-      </c>
-      <c r="I46" s="28">
-        <v>2</v>
-      </c>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="28">
-        <v>3</v>
-      </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28">
-        <v>3</v>
-      </c>
-      <c r="I47" s="28">
-        <v>3</v>
-      </c>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
-      <c r="L47" s="28"/>
-      <c r="M47" s="28"/>
-      <c r="N47" s="28"/>
-      <c r="O47" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="28">
-        <v>4</v>
-      </c>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
-      <c r="F48" s="28"/>
-      <c r="G48" s="28">
-        <v>4</v>
-      </c>
-      <c r="I48" s="28">
-        <v>4</v>
-      </c>
-      <c r="J48" s="28"/>
-      <c r="K48" s="28"/>
-      <c r="L48" s="28"/>
-      <c r="M48" s="28"/>
-      <c r="N48" s="28"/>
-      <c r="O48" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="28">
-        <v>5</v>
-      </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28">
-        <v>5</v>
-      </c>
-      <c r="I49" s="28">
-        <v>5</v>
-      </c>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="28" t="str">
-        <f>'data'!$B$9</f>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F51" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G51" s="28" t="str">
-        <f>'data'!$B$8</f>
-      </c>
-      <c r="I51" s="28" t="str">
-        <f>CONCATENATE("M 2 ",'Elimination Matches'!O15)</f>
-      </c>
-      <c r="J51" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="K51" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N51" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="O51" s="28" t="str">
-        <f>'data'!$B$10</f>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="I52" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="F54" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G54" s="24"/>
-      <c r="N54" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O54" s="24"/>
-    </row>
-    <row r="55">
-      <c r="F55" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G55" s="24"/>
-      <c r="N55" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O55" s="24"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="B63" s="20"/>
-      <c r="C63" s="20"/>
-      <c r="D63" s="20"/>
-      <c r="E63" s="20"/>
-      <c r="F63" s="20"/>
-      <c r="G63" s="20"/>
-      <c r="H63" s="20"/>
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="20"/>
-      <c r="N63" s="20"/>
-      <c r="O63" s="20"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="20" t="s">
-        <v>48</v>
-      </c>
-      <c r="B65" s="20"/>
-      <c r="C65" s="20"/>
-      <c r="D65" s="20"/>
-      <c r="E65" s="20"/>
-      <c r="F65" s="20"/>
-      <c r="G65" s="20"/>
-      <c r="I65" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="J65" s="20"/>
-      <c r="K65" s="20"/>
-      <c r="L65" s="20"/>
-      <c r="M65" s="20"/>
-      <c r="N65" s="20"/>
-      <c r="O65" s="20"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D66" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G66" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="I66" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="L66" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="O66" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="28" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
-      </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
-      </c>
-      <c r="I67" s="28" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
-      </c>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="28">
-        <v>1</v>
-      </c>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-      <c r="F68" s="28"/>
-      <c r="G68" s="28">
-        <v>1</v>
-      </c>
-      <c r="I68" s="28">
-        <v>1</v>
-      </c>
-      <c r="J68" s="28"/>
-      <c r="K68" s="28"/>
-      <c r="L68" s="28"/>
-      <c r="M68" s="28"/>
-      <c r="N68" s="28"/>
-      <c r="O68" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="28">
-        <v>2</v>
-      </c>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="28"/>
-      <c r="F69" s="28"/>
-      <c r="G69" s="28">
-        <v>2</v>
-      </c>
-      <c r="I69" s="28">
-        <v>2</v>
-      </c>
-      <c r="J69" s="28"/>
-      <c r="K69" s="28"/>
-      <c r="L69" s="28"/>
-      <c r="M69" s="28"/>
-      <c r="N69" s="28"/>
-      <c r="O69" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="28">
-        <v>3</v>
-      </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28">
-        <v>3</v>
-      </c>
-      <c r="I70" s="28">
-        <v>3</v>
-      </c>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="28">
-        <v>4</v>
-      </c>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
-      <c r="D71" s="28"/>
-      <c r="E71" s="28"/>
-      <c r="F71" s="28"/>
-      <c r="G71" s="28">
-        <v>4</v>
-      </c>
-      <c r="I71" s="28">
-        <v>4</v>
-      </c>
-      <c r="J71" s="28"/>
-      <c r="K71" s="28"/>
-      <c r="L71" s="28"/>
-      <c r="M71" s="28"/>
-      <c r="N71" s="28"/>
-      <c r="O71" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="28">
-        <v>5</v>
-      </c>
-      <c r="B72" s="28"/>
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-      <c r="F72" s="28"/>
-      <c r="G72" s="28">
-        <v>5</v>
-      </c>
-      <c r="I72" s="28">
-        <v>5</v>
-      </c>
-      <c r="J72" s="28"/>
-      <c r="K72" s="28"/>
-      <c r="L72" s="28"/>
-      <c r="M72" s="28"/>
-      <c r="N72" s="28"/>
-      <c r="O72" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="28" t="str">
-        <f>CONCATENATE("M 4 ",'Elimination Matches'!O38)</f>
-      </c>
-      <c r="B74" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C74" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D74" s="28"/>
-      <c r="E74" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F74" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G74" s="28" t="str">
-        <f>CONCATENATE("M 3 ",'Elimination Matches'!G38)</f>
-      </c>
-      <c r="I74" s="28" t="str">
-        <f>CONCATENATE("M 6 ",'Elimination Matches'!O54)</f>
-      </c>
-      <c r="J74" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="K74" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="L74" s="28"/>
-      <c r="M74" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="N74" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="O74" s="28" t="str">
-        <f>CONCATENATE("M 5 ",'Elimination Matches'!G54)</f>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B75" s="28"/>
-      <c r="C75" s="28"/>
-      <c r="D75" s="28"/>
-      <c r="E75" s="28"/>
-      <c r="F75" s="28"/>
-      <c r="G75" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="I75" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="J75" s="28"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="28"/>
-      <c r="M75" s="28"/>
-      <c r="N75" s="28"/>
-      <c r="O75" s="28" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="F77" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="G77" s="24"/>
-      <c r="N77" s="7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O77" s="24"/>
-    </row>
-    <row r="78">
-      <c r="F78" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G78" s="24"/>
-      <c r="N78" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="O78" s="24"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="20" t="s">
-        <v>50</v>
-      </c>
-      <c r="B86" s="20"/>
-      <c r="C86" s="20"/>
-      <c r="D86" s="20"/>
-      <c r="E86" s="20"/>
-      <c r="F86" s="20"/>
-      <c r="G86" s="20"/>
-      <c r="H86" s="20"/>
-      <c r="I86" s="20"/>
-      <c r="J86" s="20"/>
-      <c r="K86" s="20"/>
-      <c r="L86" s="20"/>
-      <c r="M86" s="20"/>
-      <c r="N86" s="20"/>
-      <c r="O86" s="20"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B88" s="20"/>
-      <c r="C88" s="20"/>
-      <c r="D88" s="20"/>
-      <c r="E88" s="20"/>
-      <c r="F88" s="20"/>
-      <c r="G88" s="20"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="D89" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="G89" s="29" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="28" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
-      </c>
-      <c r="B90" s="28"/>
-      <c r="C90" s="28"/>
-      <c r="D90" s="28"/>
-      <c r="E90" s="28"/>
-      <c r="F90" s="28"/>
-      <c r="G90" s="28" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="28">
-        <v>1</v>
-      </c>
-      <c r="B91" s="28"/>
-      <c r="C91" s="28"/>
-      <c r="D91" s="28"/>
-      <c r="E91" s="28"/>
-      <c r="F91" s="28"/>
-      <c r="G91" s="28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="28">
-        <v>2</v>
-      </c>
-      <c r="B92" s="28"/>
-      <c r="C92" s="28"/>
-      <c r="D92" s="28"/>
-      <c r="E92" s="28"/>
-      <c r="F92" s="28"/>
-      <c r="G92" s="28">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="28">
-        <v>3</v>
-      </c>
-      <c r="B93" s="28"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="28"/>
-      <c r="E93" s="28"/>
-      <c r="F93" s="28"/>
-      <c r="G93" s="28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="28">
-        <v>4</v>
-      </c>
-      <c r="B94" s="28"/>
-      <c r="C94" s="28"/>
-      <c r="D94" s="28"/>
-      <c r="E94" s="28"/>
-      <c r="F94" s="28"/>
-      <c r="G94" s="28">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="28">
-        <v>5</v>
-      </c>
-      <c r="B95" s="28"/>
-      <c r="C95" s="28"/>
-      <c r="D95" s="28"/>
-      <c r="E95" s="28"/>
-      <c r="F95" s="28"/>
-      <c r="G95" s="28">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="28" t="str">
-        <f>CONCATENATE("M 8 ",'Elimination Matches'!O77)</f>
-      </c>
-      <c r="B97" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="C97" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="D97" s="28"/>
-      <c r="E97" s="28" t="s">
-        <v>37</v>
-      </c>
-      <c r="F97" s="28" t="s">
-        <v>36</v>
-      </c>
-      <c r="G97" s="28" t="str">
-        <f>CONCATENATE("M 7 ",'Elimination Matches'!G77)</f>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="B98" s="28"/>
-      <c r="C98" s="28"/>
-      <c r="D98" s="28"/>
-      <c r="E98" s="28"/>
-      <c r="F98" s="28"/>
-      <c r="G98" s="28" t="s">
-        <v>38</v>
-      </c>
+      <c r="G99" s="22"/>
     </row>
     <row r="100">
       <c r="F100" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G100" s="22"/>
+    </row>
+    <row r="108">
+      <c r="A108" s="18" t="s">
+        <v>46</v>
+      </c>
+      <c r="B108" s="18"/>
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="18"/>
+    </row>
+    <row r="109">
+      <c r="A109" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D109" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G109" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="26" t="str">
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!G67)</f>
+      </c>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
+      <c r="D110" s="26"/>
+      <c r="E110" s="26"/>
+      <c r="F110" s="26"/>
+      <c r="G110" s="26" t="str">
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G51)</f>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="26">
+        <v>1</v>
+      </c>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
+      <c r="D111" s="26"/>
+      <c r="E111" s="26"/>
+      <c r="F111" s="26"/>
+      <c r="G111" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="26">
+        <v>2</v>
+      </c>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
+      <c r="D112" s="26"/>
+      <c r="E112" s="26"/>
+      <c r="F112" s="26"/>
+      <c r="G112" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="26">
+        <v>3</v>
+      </c>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
+      <c r="D113" s="26"/>
+      <c r="E113" s="26"/>
+      <c r="F113" s="26"/>
+      <c r="G113" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="26">
+        <v>4</v>
+      </c>
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
+      <c r="D114" s="26"/>
+      <c r="E114" s="26"/>
+      <c r="F114" s="26"/>
+      <c r="G114" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="26">
+        <v>5</v>
+      </c>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
+      <c r="D115" s="26"/>
+      <c r="E115" s="26"/>
+      <c r="F115" s="26"/>
+      <c r="G115" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="26" t="str">
+        <f>CONCATENATE("M 4 ",'Elimination Matches'!G67)</f>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C117" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D117" s="26"/>
+      <c r="E117" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F117" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G117" s="26" t="str">
+        <f>CONCATENATE("M 3 ",'Elimination Matches'!G51)</f>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
+      <c r="D118" s="26"/>
+      <c r="E118" s="26"/>
+      <c r="F118" s="26"/>
+      <c r="G118" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="F120" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="G100" s="24"/>
-    </row>
-    <row r="101">
-      <c r="F101" s="7" t="s">
+      <c r="G120" s="22"/>
+    </row>
+    <row r="121">
+      <c r="F121" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G101" s="24"/>
+      <c r="G121" s="22"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="18" t="s">
+        <v>47</v>
+      </c>
+      <c r="B124" s="18"/>
+      <c r="C124" s="18"/>
+      <c r="D124" s="18"/>
+      <c r="E124" s="18"/>
+      <c r="F124" s="18"/>
+      <c r="G124" s="18"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D125" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G125" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="26" t="str">
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!G99)</f>
+      </c>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
+      <c r="D126" s="26"/>
+      <c r="E126" s="26"/>
+      <c r="F126" s="26"/>
+      <c r="G126" s="26" t="str">
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G83)</f>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="26">
+        <v>1</v>
+      </c>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
+      <c r="D127" s="26"/>
+      <c r="E127" s="26"/>
+      <c r="F127" s="26"/>
+      <c r="G127" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="26">
+        <v>2</v>
+      </c>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
+      <c r="D128" s="26"/>
+      <c r="E128" s="26"/>
+      <c r="F128" s="26"/>
+      <c r="G128" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="26">
+        <v>3</v>
+      </c>
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
+      <c r="D129" s="26"/>
+      <c r="E129" s="26"/>
+      <c r="F129" s="26"/>
+      <c r="G129" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="26">
+        <v>4</v>
+      </c>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
+      <c r="D130" s="26"/>
+      <c r="E130" s="26"/>
+      <c r="F130" s="26"/>
+      <c r="G130" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="26">
+        <v>5</v>
+      </c>
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
+      <c r="D131" s="26"/>
+      <c r="E131" s="26"/>
+      <c r="F131" s="26"/>
+      <c r="G131" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="26" t="str">
+        <f>CONCATENATE("M 6 ",'Elimination Matches'!G99)</f>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D133" s="26"/>
+      <c r="E133" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F133" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G133" s="26" t="str">
+        <f>CONCATENATE("M 5 ",'Elimination Matches'!G83)</f>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
+      <c r="D134" s="26"/>
+      <c r="E134" s="26"/>
+      <c r="F134" s="26"/>
+      <c r="G134" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="F136" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G136" s="22"/>
+    </row>
+    <row r="137">
+      <c r="F137" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G137" s="22"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B145" s="18"/>
+      <c r="C145" s="18"/>
+      <c r="D145" s="18"/>
+      <c r="E145" s="18"/>
+      <c r="F145" s="18"/>
+      <c r="G145" s="18"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="D146" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="G146" s="27" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="26" t="str">
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!G136)</f>
+      </c>
+      <c r="B147" s="26"/>
+      <c r="C147" s="26"/>
+      <c r="D147" s="26"/>
+      <c r="E147" s="26"/>
+      <c r="F147" s="26"/>
+      <c r="G147" s="26" t="str">
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G120)</f>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="26">
+        <v>1</v>
+      </c>
+      <c r="B148" s="26"/>
+      <c r="C148" s="26"/>
+      <c r="D148" s="26"/>
+      <c r="E148" s="26"/>
+      <c r="F148" s="26"/>
+      <c r="G148" s="26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="26">
+        <v>2</v>
+      </c>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
+      <c r="D149" s="26"/>
+      <c r="E149" s="26"/>
+      <c r="F149" s="26"/>
+      <c r="G149" s="26">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="26">
+        <v>3</v>
+      </c>
+      <c r="B150" s="26"/>
+      <c r="C150" s="26"/>
+      <c r="D150" s="26"/>
+      <c r="E150" s="26"/>
+      <c r="F150" s="26"/>
+      <c r="G150" s="26">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="26">
+        <v>4</v>
+      </c>
+      <c r="B151" s="26"/>
+      <c r="C151" s="26"/>
+      <c r="D151" s="26"/>
+      <c r="E151" s="26"/>
+      <c r="F151" s="26"/>
+      <c r="G151" s="26">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="26">
+        <v>5</v>
+      </c>
+      <c r="B152" s="26"/>
+      <c r="C152" s="26"/>
+      <c r="D152" s="26"/>
+      <c r="E152" s="26"/>
+      <c r="F152" s="26"/>
+      <c r="G152" s="26">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="26" t="str">
+        <f>CONCATENATE("M 8 ",'Elimination Matches'!G136)</f>
+      </c>
+      <c r="B154" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="C154" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D154" s="26"/>
+      <c r="E154" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="F154" s="26" t="s">
+        <v>36</v>
+      </c>
+      <c r="G154" s="26" t="str">
+        <f>CONCATENATE("M 7 ",'Elimination Matches'!G120)</f>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="26" t="s">
+        <v>38</v>
+      </c>
+      <c r="B155" s="26"/>
+      <c r="C155" s="26"/>
+      <c r="D155" s="26"/>
+      <c r="E155" s="26"/>
+      <c r="F155" s="26"/>
+      <c r="G155" s="26" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="F157" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="G157" s="22"/>
+    </row>
+    <row r="158">
+      <c r="F158" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="G158" s="22"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="I3:O3"/>
-    <mergeCell ref="A24:O24"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="I26:O26"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="I42:O42"/>
-    <mergeCell ref="A63:O63"/>
-    <mergeCell ref="A65:G65"/>
-    <mergeCell ref="I65:O65"/>
-    <mergeCell ref="A86:O86"/>
-    <mergeCell ref="A88:G88"/>
+  <mergeCells count="10">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A87:G87"/>
+    <mergeCell ref="A108:G108"/>
+    <mergeCell ref="A124:G124"/>
+    <mergeCell ref="A145:G145"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="38" max="16383" man="true"/>
+    <brk id="70" max="16383" man="true"/>
+    <brk id="107" max="16383" man="true"/>
+    <brk id="144" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
 </worksheet>
 </file>
 
@@ -3735,124 +3825,124 @@
   </cols>
   <sheetData>
     <row r="1" ht="110" customHeight="true">
-      <c r="A1" s="26">
+      <c r="A1" s="24">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="str">
+      <c r="B1" s="25" t="str">
         <f>data!$B$3</f>
       </c>
     </row>
     <row r="2" ht="115" customHeight="true">
-      <c r="A2" s="26"/>
-      <c r="B2" s="27"/>
+      <c r="A2" s="24"/>
+      <c r="B2" s="25"/>
     </row>
     <row r="3" ht="110" customHeight="true">
-      <c r="A3" s="26">
+      <c r="A3" s="24">
         <v>1</v>
       </c>
-      <c r="B3" s="27" t="str">
+      <c r="B3" s="25" t="str">
         <f>data!$B$4</f>
       </c>
     </row>
     <row r="4" ht="115" customHeight="true">
-      <c r="A4" s="26"/>
-      <c r="B4" s="27"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="25"/>
     </row>
     <row r="5" ht="110" customHeight="true">
-      <c r="A5" s="26">
+      <c r="A5" s="24">
         <v>2</v>
       </c>
-      <c r="B5" s="27" t="str">
+      <c r="B5" s="25" t="str">
         <f>data!$B$5</f>
       </c>
     </row>
     <row r="6" ht="115" customHeight="true">
-      <c r="A6" s="26"/>
-      <c r="B6" s="27"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="25"/>
     </row>
     <row r="7" ht="110" customHeight="true">
-      <c r="A7" s="26">
+      <c r="A7" s="24">
         <v>3</v>
       </c>
-      <c r="B7" s="27" t="str">
+      <c r="B7" s="25" t="str">
         <f>data!$B$6</f>
       </c>
     </row>
     <row r="8" ht="115" customHeight="true">
-      <c r="A8" s="26"/>
-      <c r="B8" s="27"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="25"/>
     </row>
     <row r="9" ht="110" customHeight="true">
-      <c r="A9" s="26">
+      <c r="A9" s="24">
         <v>4</v>
       </c>
-      <c r="B9" s="27" t="str">
+      <c r="B9" s="25" t="str">
         <f>data!$B$7</f>
       </c>
     </row>
     <row r="10" ht="115" customHeight="true">
-      <c r="A10" s="26"/>
-      <c r="B10" s="27"/>
+      <c r="A10" s="24"/>
+      <c r="B10" s="25"/>
     </row>
     <row r="11" ht="110" customHeight="true">
-      <c r="A11" s="26">
+      <c r="A11" s="24">
         <v>5</v>
       </c>
-      <c r="B11" s="27" t="str">
+      <c r="B11" s="25" t="str">
         <f>data!$B$8</f>
       </c>
     </row>
     <row r="12" ht="115" customHeight="true">
-      <c r="A12" s="26"/>
-      <c r="B12" s="27"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="25"/>
     </row>
     <row r="13" ht="110" customHeight="true">
-      <c r="A13" s="26">
+      <c r="A13" s="24">
         <v>6</v>
       </c>
-      <c r="B13" s="27" t="str">
+      <c r="B13" s="25" t="str">
         <f>data!$B$9</f>
       </c>
     </row>
     <row r="14" ht="115" customHeight="true">
-      <c r="A14" s="26"/>
-      <c r="B14" s="27"/>
+      <c r="A14" s="24"/>
+      <c r="B14" s="25"/>
     </row>
     <row r="15" ht="110" customHeight="true">
-      <c r="A15" s="26">
+      <c r="A15" s="24">
         <v>7</v>
       </c>
-      <c r="B15" s="27" t="str">
+      <c r="B15" s="25" t="str">
         <f>data!$B$10</f>
       </c>
     </row>
     <row r="16" ht="115" customHeight="true">
-      <c r="A16" s="26"/>
-      <c r="B16" s="27"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="25"/>
     </row>
     <row r="17" ht="110" customHeight="true">
-      <c r="A17" s="26">
+      <c r="A17" s="24">
         <v>8</v>
       </c>
-      <c r="B17" s="27" t="str">
+      <c r="B17" s="25" t="str">
         <f>data!$B$11</f>
       </c>
     </row>
     <row r="18" ht="115" customHeight="true">
-      <c r="A18" s="26"/>
-      <c r="B18" s="27"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="25"/>
     </row>
     <row r="19" ht="110" customHeight="true">
-      <c r="A19" s="26">
+      <c r="A19" s="24">
         <v>9</v>
       </c>
-      <c r="B19" s="27" t="str">
+      <c r="B19" s="25" t="str">
         <f>data!$B$12</f>
       </c>
     </row>
     <row r="20" ht="115" customHeight="true">
-      <c r="A20" s="26"/>
-      <c r="B20" s="27"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="10">

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -693,11 +693,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="15"/>
-    <col customWidth="true" max="26" min="2" width="30"/>
+    <col customWidth="true" max="1" min="1" width="9"/>
+    <col customWidth="true" max="3" min="2" width="20"/>
+    <col customWidth="true" max="26" min="4" width="12"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -833,7 +837,8 @@
       </c>
     </row>
   </sheetData>
-  <pageSetup orientation="landscape"/>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -2587,7 +2592,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="20.83"/>
+    <col customWidth="true" max="1" min="1" width="25"/>
     <col customWidth="true" max="2" min="2" width="10"/>
     <col customWidth="true" max="26" min="3" width="3.5"/>
   </cols>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -10,11 +10,11 @@
     <sheet name="data" sheetId="1" r:id="rId1"/>
     <sheet name="Time Estimator" sheetId="2" r:id="rId4"/>
     <sheet name="Elimination Matches" sheetId="5" r:id="rId7"/>
-    <sheet name="Names to Print" sheetId="6" r:id="rId8"/>
     <sheet name="Tree 1" sheetId="8" r:id="rId11"/>
+    <sheet name="Names to Print A" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="3" name="_xlnm.Print_Area">'Names to Print'!$A$1:$B$10</definedName>
+    <definedName localSheetId="4" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$10</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$G$165</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
@@ -2488,106 +2488,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <cols>
-    <col customWidth="true" max="1" min="1" style="9" width="30"/>
-    <col customWidth="true" max="2" min="2" style="10" width="160"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
-      </c>
-      <c r="B1" s="18" t="str">
-        <f>data!$B$3</f>
-      </c>
-    </row>
-    <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>1</v>
-      </c>
-      <c r="B2" s="18" t="str">
-        <f>data!$B$4</f>
-      </c>
-    </row>
-    <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>2</v>
-      </c>
-      <c r="B3" s="18" t="str">
-        <f>data!$B$5</f>
-      </c>
-    </row>
-    <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>3</v>
-      </c>
-      <c r="B4" s="18" t="str">
-        <f>data!$B$6</f>
-      </c>
-    </row>
-    <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>4</v>
-      </c>
-      <c r="B5" s="18" t="str">
-        <f>data!$B$7</f>
-      </c>
-    </row>
-    <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>5</v>
-      </c>
-      <c r="B6" s="18" t="str">
-        <f>data!$B$8</f>
-      </c>
-    </row>
-    <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>6</v>
-      </c>
-      <c r="B7" s="18" t="str">
-        <f>data!$B$9</f>
-      </c>
-    </row>
-    <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>7</v>
-      </c>
-      <c r="B8" s="18" t="str">
-        <f>data!$B$10</f>
-      </c>
-    </row>
-    <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>8</v>
-      </c>
-      <c r="B9" s="18" t="str">
-        <f>data!$B$11</f>
-      </c>
-    </row>
-    <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>9</v>
-      </c>
-      <c r="B10" s="18" t="str">
-        <f>data!$B$12</f>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="8"/>
-  <rowBreaks count="3" manualBreakCount="3">
-    <brk id="3" max="16383" man="true"/>
-    <brk id="6" max="16383" man="true"/>
-    <brk id="9" max="16383" man="true"/>
-  </rowBreaks>
-  <colBreaks/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
@@ -2800,4 +2700,104 @@
     <mergeCell ref="A1:P1"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1"/>
+  <cols>
+    <col customWidth="true" max="1" min="1" width="30"/>
+    <col customWidth="true" max="2" min="2" width="160"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="270" customHeight="true">
+      <c r="A1" s="17">
+        <v>0</v>
+      </c>
+      <c r="B1" s="18" t="str">
+        <f>data!$B$3</f>
+      </c>
+    </row>
+    <row r="2" ht="270" customHeight="true">
+      <c r="A2" s="17">
+        <v>1</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>data!$B$4</f>
+      </c>
+    </row>
+    <row r="3" ht="270" customHeight="true">
+      <c r="A3" s="17">
+        <v>2</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f>data!$B$5</f>
+      </c>
+    </row>
+    <row r="4" ht="270" customHeight="true">
+      <c r="A4" s="17">
+        <v>3</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f>data!$B$6</f>
+      </c>
+    </row>
+    <row r="5" ht="270" customHeight="true">
+      <c r="A5" s="17">
+        <v>4</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f>data!$B$7</f>
+      </c>
+    </row>
+    <row r="6" ht="270" customHeight="true">
+      <c r="A6" s="17">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f>data!$B$8</f>
+      </c>
+    </row>
+    <row r="7" ht="270" customHeight="true">
+      <c r="A7" s="17">
+        <v>6</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f>data!$B$9</f>
+      </c>
+    </row>
+    <row r="8" ht="270" customHeight="true">
+      <c r="A8" s="17">
+        <v>7</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f>data!$B$10</f>
+      </c>
+    </row>
+    <row r="9" ht="270" customHeight="true">
+      <c r="A9" s="17">
+        <v>8</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f>data!$B$11</f>
+      </c>
+    </row>
+    <row r="10" ht="270" customHeight="true">
+      <c r="A10" s="17">
+        <v>9</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f>data!$B$12</f>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="8"/>
+  <rowBreaks count="3" manualBreakCount="3">
+    <brk id="3" max="16383" man="true"/>
+    <brk id="6" max="16383" man="true"/>
+    <brk id="9" max="16383" man="true"/>
+  </rowBreaks>
+  <colBreaks/>
+</worksheet>
 </file>
--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>Number of pools</t>
   </si>
@@ -127,12 +127,6 @@
   </si>
   <si>
     <t>Red</t>
-  </si>
-  <si>
-    <t>V</t>
-  </si>
-  <si>
-    <t>P</t>
   </si>
   <si>
     <t>Victories / Points</t>
@@ -274,12 +268,17 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFEFEF"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -355,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
@@ -402,7 +401,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -411,16 +410,27 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center"/>
+      <protection hidden="false" locked="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false" applyProtection="true">
+      <alignment/>
+      <protection hidden="false" locked="false"/>
+    </xf>
     <xf numFmtId="165" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -902,7 +912,7 @@
       <c r="G2" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H2" s="22" t="str">
+      <c r="H2" s="24" t="str">
         <f>C2*I2+J2</f>
       </c>
     </row>
@@ -1006,7 +1016,7 @@
       <c r="G8" s="3">
         <v>0.020833333333333332</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="24" t="str">
         <f>E8+(A8*F8)+G8</f>
       </c>
     </row>
@@ -1042,7 +1052,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -1052,62 +1062,62 @@
       <c r="A14">
         <v>1</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="24" t="str">
+        <f>H2</f>
+      </c>
+    </row>
+    <row r="15">
+      <c r="E15" s="25" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="24" t="str">
+        <f>H8</f>
+      </c>
+    </row>
+    <row r="16">
+      <c r="E16" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="19"/>
-      <c r="H14" s="22" t="str">
-        <f>H2</f>
-      </c>
-    </row>
-    <row r="15">
-      <c r="E15" s="19" t="s">
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="24" t="str">
+        <f>H14+H15</f>
+      </c>
+    </row>
+    <row r="17">
+      <c r="E17" s="25" t="s">
         <v>50</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="22" t="str">
-        <f>H8</f>
-      </c>
-    </row>
-    <row r="16">
-      <c r="E16" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="19"/>
-      <c r="H16" s="22" t="str">
-        <f>H14+H15</f>
-      </c>
-    </row>
-    <row r="17">
-      <c r="E17" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="19"/>
-      <c r="H17" s="22" t="str">
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="24" t="str">
         <f>H16/A14</f>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
-      <c r="H18" s="23">
+      <c r="H18" s="26">
         <v>0.375</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="23" t="str">
+      <c r="H19" s="26" t="str">
         <f>H18+H17</f>
       </c>
     </row>
@@ -1131,9 +1141,10 @@
     <col customWidth="true" max="4" min="4" width="3"/>
     <col customWidth="true" max="6" min="5" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="8" min="8" width="2"/>
-    <col customWidth="true" max="9" min="9" width="34.83"/>
-    <col customWidth="true" max="14" min="10" width="3.83"/>
+    <col customWidth="true" max="10" min="8" width="5"/>
+    <col customWidth="true" max="11" min="11" width="30"/>
+    <col customWidth="true" max="12" min="12" width="2"/>
+    <col customWidth="true" max="14" min="13" width="3.83"/>
     <col customWidth="true" max="15" min="15" width="34.83"/>
     <col customWidth="true" max="20" min="16" width="10.83"/>
   </cols>
@@ -1175,11 +1186,11 @@
       <c r="A4" s="19" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B4" s="19"/>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="19"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
       <c r="G4" s="19" t="str">
         <f>'data'!$B$6</f>
       </c>
@@ -1188,11 +1199,11 @@
       <c r="A5" s="19">
         <v>1</v>
       </c>
-      <c r="B5" s="19"/>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
       <c r="G5" s="19">
         <v>1</v>
       </c>
@@ -1201,11 +1212,11 @@
       <c r="A6" s="19">
         <v>2</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
       <c r="G6" s="19">
         <v>2</v>
       </c>
@@ -1214,11 +1225,11 @@
       <c r="A7" s="19">
         <v>3</v>
       </c>
-      <c r="B7" s="19"/>
-      <c r="C7" s="19"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
       <c r="G7" s="19">
         <v>3</v>
       </c>
@@ -1227,11 +1238,11 @@
       <c r="A8" s="19">
         <v>4</v>
       </c>
-      <c r="B8" s="19"/>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
       <c r="G8" s="19">
         <v>4</v>
       </c>
@@ -1240,11 +1251,11 @@
       <c r="A9" s="19">
         <v>5</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="19"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
       <c r="G9" s="19">
         <v>5</v>
       </c>
@@ -1253,18 +1264,18 @@
       <c r="A11" s="19" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>36</v>
+      <c r="B11" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C11" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D11" s="19"/>
-      <c r="E11" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>35</v>
+      <c r="E11" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F11" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G11" s="19" t="str">
         <f>'data'!$B$6</f>
@@ -1272,7 +1283,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -1280,24 +1291,24 @@
       <c r="E12" s="19"/>
       <c r="F12" s="19"/>
       <c r="G12" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="F14" t="s">
-        <v>38</v>
-      </c>
-      <c r="G14" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>39</v>
-      </c>
-      <c r="G15" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16">
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1321,11 +1332,11 @@
       <c r="A20" s="19" t="str">
         <f>'data'!$B$12</f>
       </c>
-      <c r="B20" s="19"/>
-      <c r="C20" s="19"/>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="22"/>
+      <c r="E20" s="22"/>
+      <c r="F20" s="22"/>
       <c r="G20" s="19" t="str">
         <f>'data'!$B$11</f>
       </c>
@@ -1334,11 +1345,11 @@
       <c r="A21" s="19">
         <v>1</v>
       </c>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
+      <c r="B21" s="22"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22"/>
+      <c r="F21" s="22"/>
       <c r="G21" s="19">
         <v>1</v>
       </c>
@@ -1347,11 +1358,11 @@
       <c r="A22" s="19">
         <v>2</v>
       </c>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
+      <c r="B22" s="22"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="22"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="22"/>
       <c r="G22" s="19">
         <v>2</v>
       </c>
@@ -1360,11 +1371,11 @@
       <c r="A23" s="19">
         <v>3</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="22"/>
+      <c r="E23" s="22"/>
+      <c r="F23" s="22"/>
       <c r="G23" s="19">
         <v>3</v>
       </c>
@@ -1373,11 +1384,11 @@
       <c r="A24" s="19">
         <v>4</v>
       </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="22"/>
+      <c r="E24" s="22"/>
+      <c r="F24" s="22"/>
       <c r="G24" s="19">
         <v>4</v>
       </c>
@@ -1386,11 +1397,11 @@
       <c r="A25" s="19">
         <v>5</v>
       </c>
-      <c r="B25" s="19"/>
-      <c r="C25" s="19"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="B25" s="22"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22"/>
+      <c r="F25" s="22"/>
       <c r="G25" s="19">
         <v>5</v>
       </c>
@@ -1399,18 +1410,18 @@
       <c r="A27" s="19" t="str">
         <f>'data'!$B$12</f>
       </c>
-      <c r="B27" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C27" s="19" t="s">
-        <v>36</v>
+      <c r="B27" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C27" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D27" s="19"/>
-      <c r="E27" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" s="19" t="s">
-        <v>35</v>
+      <c r="E27" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F27" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G27" s="19" t="str">
         <f>'data'!$B$11</f>
@@ -1418,7 +1429,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B28" s="19"/>
       <c r="C28" s="19"/>
@@ -1426,24 +1437,24 @@
       <c r="E28" s="19"/>
       <c r="F28" s="19"/>
       <c r="G28" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="F30" t="s">
-        <v>38</v>
-      </c>
-      <c r="G30" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>39</v>
-      </c>
-      <c r="G31" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32">
+      <c r="F32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G32" s="23"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1467,11 +1478,11 @@
       <c r="A41" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
       <c r="G41" s="19" t="str">
         <f>'data'!$B$3</f>
       </c>
@@ -1480,11 +1491,11 @@
       <c r="A42" s="19">
         <v>1</v>
       </c>
-      <c r="B42" s="19"/>
-      <c r="C42" s="19"/>
-      <c r="D42" s="19"/>
-      <c r="E42" s="19"/>
-      <c r="F42" s="19"/>
+      <c r="B42" s="22"/>
+      <c r="C42" s="22"/>
+      <c r="D42" s="22"/>
+      <c r="E42" s="22"/>
+      <c r="F42" s="22"/>
       <c r="G42" s="19">
         <v>1</v>
       </c>
@@ -1493,11 +1504,11 @@
       <c r="A43" s="19">
         <v>2</v>
       </c>
-      <c r="B43" s="19"/>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
+      <c r="B43" s="22"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="22"/>
+      <c r="E43" s="22"/>
+      <c r="F43" s="22"/>
       <c r="G43" s="19">
         <v>2</v>
       </c>
@@ -1506,11 +1517,11 @@
       <c r="A44" s="19">
         <v>3</v>
       </c>
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
+      <c r="B44" s="22"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="22"/>
+      <c r="E44" s="22"/>
+      <c r="F44" s="22"/>
       <c r="G44" s="19">
         <v>3</v>
       </c>
@@ -1519,11 +1530,11 @@
       <c r="A45" s="19">
         <v>4</v>
       </c>
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
+      <c r="B45" s="22"/>
+      <c r="C45" s="22"/>
+      <c r="D45" s="22"/>
+      <c r="E45" s="22"/>
+      <c r="F45" s="22"/>
       <c r="G45" s="19">
         <v>4</v>
       </c>
@@ -1532,11 +1543,11 @@
       <c r="A46" s="19">
         <v>5</v>
       </c>
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="19"/>
+      <c r="B46" s="22"/>
+      <c r="C46" s="22"/>
+      <c r="D46" s="22"/>
+      <c r="E46" s="22"/>
+      <c r="F46" s="22"/>
       <c r="G46" s="19">
         <v>5</v>
       </c>
@@ -1545,18 +1556,18 @@
       <c r="A48" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="B48" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="19" t="s">
-        <v>36</v>
+      <c r="B48" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C48" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D48" s="19"/>
-      <c r="E48" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F48" s="19" t="s">
-        <v>35</v>
+      <c r="E48" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F48" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G48" s="19" t="str">
         <f>'data'!$B$3</f>
@@ -1564,7 +1575,7 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B49" s="19"/>
       <c r="C49" s="19"/>
@@ -1572,24 +1583,24 @@
       <c r="E49" s="19"/>
       <c r="F49" s="19"/>
       <c r="G49" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="F51" t="s">
-        <v>38</v>
-      </c>
-      <c r="G51" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>39</v>
-      </c>
-      <c r="G52" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G52" s="23"/>
+    </row>
+    <row r="53">
+      <c r="F53" t="s">
+        <v>37</v>
+      </c>
+      <c r="G53" s="23"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
@@ -1611,13 +1622,13 @@
     </row>
     <row r="57">
       <c r="A57" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G14)</f>
-      </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="19"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
       <c r="G57" s="19" t="str">
         <f>'data'!$B$5</f>
       </c>
@@ -1626,11 +1637,11 @@
       <c r="A58" s="19">
         <v>1</v>
       </c>
-      <c r="B58" s="19"/>
-      <c r="C58" s="19"/>
-      <c r="D58" s="19"/>
-      <c r="E58" s="19"/>
-      <c r="F58" s="19"/>
+      <c r="B58" s="22"/>
+      <c r="C58" s="22"/>
+      <c r="D58" s="22"/>
+      <c r="E58" s="22"/>
+      <c r="F58" s="22"/>
       <c r="G58" s="19">
         <v>1</v>
       </c>
@@ -1639,11 +1650,11 @@
       <c r="A59" s="19">
         <v>2</v>
       </c>
-      <c r="B59" s="19"/>
-      <c r="C59" s="19"/>
-      <c r="D59" s="19"/>
-      <c r="E59" s="19"/>
-      <c r="F59" s="19"/>
+      <c r="B59" s="22"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="22"/>
+      <c r="E59" s="22"/>
+      <c r="F59" s="22"/>
       <c r="G59" s="19">
         <v>2</v>
       </c>
@@ -1652,11 +1663,11 @@
       <c r="A60" s="19">
         <v>3</v>
       </c>
-      <c r="B60" s="19"/>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
+      <c r="B60" s="22"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="22"/>
+      <c r="E60" s="22"/>
+      <c r="F60" s="22"/>
       <c r="G60" s="19">
         <v>3</v>
       </c>
@@ -1665,11 +1676,11 @@
       <c r="A61" s="19">
         <v>4</v>
       </c>
-      <c r="B61" s="19"/>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
+      <c r="B61" s="22"/>
+      <c r="C61" s="22"/>
+      <c r="D61" s="22"/>
+      <c r="E61" s="22"/>
+      <c r="F61" s="22"/>
       <c r="G61" s="19">
         <v>4</v>
       </c>
@@ -1678,31 +1689,31 @@
       <c r="A62" s="19">
         <v>5</v>
       </c>
-      <c r="B62" s="19"/>
-      <c r="C62" s="19"/>
-      <c r="D62" s="19"/>
-      <c r="E62" s="19"/>
-      <c r="F62" s="19"/>
+      <c r="B62" s="22"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
       <c r="G62" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G14)</f>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>36</v>
+        <f>CONCATENATE("M 1 ",G15)</f>
+      </c>
+      <c r="B64" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C64" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D64" s="19"/>
-      <c r="E64" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>35</v>
+      <c r="E64" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F64" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G64" s="19" t="str">
         <f>'data'!$B$5</f>
@@ -1710,7 +1721,7 @@
     </row>
     <row r="65">
       <c r="A65" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B65" s="19"/>
       <c r="C65" s="19"/>
@@ -1718,24 +1729,24 @@
       <c r="E65" s="19"/>
       <c r="F65" s="19"/>
       <c r="G65" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="F67" t="s">
-        <v>38</v>
-      </c>
-      <c r="G67" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="68">
       <c r="F68" t="s">
-        <v>39</v>
-      </c>
-      <c r="G68" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G68" s="23"/>
+    </row>
+    <row r="69">
+      <c r="F69" t="s">
+        <v>37</v>
+      </c>
+      <c r="G69" s="23"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
@@ -1759,11 +1770,11 @@
       <c r="A73" s="19" t="str">
         <f>'data'!$B$9</f>
       </c>
-      <c r="B73" s="19"/>
-      <c r="C73" s="19"/>
-      <c r="D73" s="19"/>
-      <c r="E73" s="19"/>
-      <c r="F73" s="19"/>
+      <c r="B73" s="22"/>
+      <c r="C73" s="22"/>
+      <c r="D73" s="22"/>
+      <c r="E73" s="22"/>
+      <c r="F73" s="22"/>
       <c r="G73" s="19" t="str">
         <f>'data'!$B$8</f>
       </c>
@@ -1772,11 +1783,11 @@
       <c r="A74" s="19">
         <v>1</v>
       </c>
-      <c r="B74" s="19"/>
-      <c r="C74" s="19"/>
-      <c r="D74" s="19"/>
-      <c r="E74" s="19"/>
-      <c r="F74" s="19"/>
+      <c r="B74" s="22"/>
+      <c r="C74" s="22"/>
+      <c r="D74" s="22"/>
+      <c r="E74" s="22"/>
+      <c r="F74" s="22"/>
       <c r="G74" s="19">
         <v>1</v>
       </c>
@@ -1785,11 +1796,11 @@
       <c r="A75" s="19">
         <v>2</v>
       </c>
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="19"/>
+      <c r="B75" s="22"/>
+      <c r="C75" s="22"/>
+      <c r="D75" s="22"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
       <c r="G75" s="19">
         <v>2</v>
       </c>
@@ -1798,11 +1809,11 @@
       <c r="A76" s="19">
         <v>3</v>
       </c>
-      <c r="B76" s="19"/>
-      <c r="C76" s="19"/>
-      <c r="D76" s="19"/>
-      <c r="E76" s="19"/>
-      <c r="F76" s="19"/>
+      <c r="B76" s="22"/>
+      <c r="C76" s="22"/>
+      <c r="D76" s="22"/>
+      <c r="E76" s="22"/>
+      <c r="F76" s="22"/>
       <c r="G76" s="19">
         <v>3</v>
       </c>
@@ -1811,11 +1822,11 @@
       <c r="A77" s="19">
         <v>4</v>
       </c>
-      <c r="B77" s="19"/>
-      <c r="C77" s="19"/>
-      <c r="D77" s="19"/>
-      <c r="E77" s="19"/>
-      <c r="F77" s="19"/>
+      <c r="B77" s="22"/>
+      <c r="C77" s="22"/>
+      <c r="D77" s="22"/>
+      <c r="E77" s="22"/>
+      <c r="F77" s="22"/>
       <c r="G77" s="19">
         <v>4</v>
       </c>
@@ -1824,11 +1835,11 @@
       <c r="A78" s="19">
         <v>5</v>
       </c>
-      <c r="B78" s="19"/>
-      <c r="C78" s="19"/>
-      <c r="D78" s="19"/>
-      <c r="E78" s="19"/>
-      <c r="F78" s="19"/>
+      <c r="B78" s="22"/>
+      <c r="C78" s="22"/>
+      <c r="D78" s="22"/>
+      <c r="E78" s="22"/>
+      <c r="F78" s="22"/>
       <c r="G78" s="19">
         <v>5</v>
       </c>
@@ -1837,18 +1848,18 @@
       <c r="A80" s="19" t="str">
         <f>'data'!$B$9</f>
       </c>
-      <c r="B80" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>36</v>
+      <c r="B80" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C80" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D80" s="19"/>
-      <c r="E80" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F80" s="19" t="s">
-        <v>35</v>
+      <c r="E80" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F80" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G80" s="19" t="str">
         <f>'data'!$B$8</f>
@@ -1856,7 +1867,7 @@
     </row>
     <row r="81">
       <c r="A81" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B81" s="19"/>
       <c r="C81" s="19"/>
@@ -1864,24 +1875,24 @@
       <c r="E81" s="19"/>
       <c r="F81" s="19"/>
       <c r="G81" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="F83" t="s">
-        <v>38</v>
-      </c>
-      <c r="G83" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="84">
       <c r="F84" t="s">
-        <v>39</v>
-      </c>
-      <c r="G84" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G84" s="23"/>
+    </row>
+    <row r="85">
+      <c r="F85" t="s">
+        <v>37</v>
+      </c>
+      <c r="G85" s="23"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
@@ -1903,13 +1914,13 @@
     </row>
     <row r="89">
       <c r="A89" s="19" t="str">
-        <f>CONCATENATE("M 2 ",G30)</f>
-      </c>
-      <c r="B89" s="19"/>
-      <c r="C89" s="19"/>
-      <c r="D89" s="19"/>
-      <c r="E89" s="19"/>
-      <c r="F89" s="19"/>
+        <f>CONCATENATE("M 2 ",G31)</f>
+      </c>
+      <c r="B89" s="22"/>
+      <c r="C89" s="22"/>
+      <c r="D89" s="22"/>
+      <c r="E89" s="22"/>
+      <c r="F89" s="22"/>
       <c r="G89" s="19" t="str">
         <f>'data'!$B$10</f>
       </c>
@@ -1918,11 +1929,11 @@
       <c r="A90" s="19">
         <v>1</v>
       </c>
-      <c r="B90" s="19"/>
-      <c r="C90" s="19"/>
-      <c r="D90" s="19"/>
-      <c r="E90" s="19"/>
-      <c r="F90" s="19"/>
+      <c r="B90" s="22"/>
+      <c r="C90" s="22"/>
+      <c r="D90" s="22"/>
+      <c r="E90" s="22"/>
+      <c r="F90" s="22"/>
       <c r="G90" s="19">
         <v>1</v>
       </c>
@@ -1931,11 +1942,11 @@
       <c r="A91" s="19">
         <v>2</v>
       </c>
-      <c r="B91" s="19"/>
-      <c r="C91" s="19"/>
-      <c r="D91" s="19"/>
-      <c r="E91" s="19"/>
-      <c r="F91" s="19"/>
+      <c r="B91" s="22"/>
+      <c r="C91" s="22"/>
+      <c r="D91" s="22"/>
+      <c r="E91" s="22"/>
+      <c r="F91" s="22"/>
       <c r="G91" s="19">
         <v>2</v>
       </c>
@@ -1944,11 +1955,11 @@
       <c r="A92" s="19">
         <v>3</v>
       </c>
-      <c r="B92" s="19"/>
-      <c r="C92" s="19"/>
-      <c r="D92" s="19"/>
-      <c r="E92" s="19"/>
-      <c r="F92" s="19"/>
+      <c r="B92" s="22"/>
+      <c r="C92" s="22"/>
+      <c r="D92" s="22"/>
+      <c r="E92" s="22"/>
+      <c r="F92" s="22"/>
       <c r="G92" s="19">
         <v>3</v>
       </c>
@@ -1957,11 +1968,11 @@
       <c r="A93" s="19">
         <v>4</v>
       </c>
-      <c r="B93" s="19"/>
-      <c r="C93" s="19"/>
-      <c r="D93" s="19"/>
-      <c r="E93" s="19"/>
-      <c r="F93" s="19"/>
+      <c r="B93" s="22"/>
+      <c r="C93" s="22"/>
+      <c r="D93" s="22"/>
+      <c r="E93" s="22"/>
+      <c r="F93" s="22"/>
       <c r="G93" s="19">
         <v>4</v>
       </c>
@@ -1970,31 +1981,31 @@
       <c r="A94" s="19">
         <v>5</v>
       </c>
-      <c r="B94" s="19"/>
-      <c r="C94" s="19"/>
-      <c r="D94" s="19"/>
-      <c r="E94" s="19"/>
-      <c r="F94" s="19"/>
+      <c r="B94" s="22"/>
+      <c r="C94" s="22"/>
+      <c r="D94" s="22"/>
+      <c r="E94" s="22"/>
+      <c r="F94" s="22"/>
       <c r="G94" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="19" t="str">
-        <f>CONCATENATE("M 2 ",G30)</f>
-      </c>
-      <c r="B96" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C96" s="19" t="s">
-        <v>36</v>
+        <f>CONCATENATE("M 2 ",G31)</f>
+      </c>
+      <c r="B96" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C96" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D96" s="19"/>
-      <c r="E96" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F96" s="19" t="s">
-        <v>35</v>
+      <c r="E96" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F96" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G96" s="19" t="str">
         <f>'data'!$B$10</f>
@@ -2002,7 +2013,7 @@
     </row>
     <row r="97">
       <c r="A97" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B97" s="19"/>
       <c r="C97" s="19"/>
@@ -2010,24 +2021,24 @@
       <c r="E97" s="19"/>
       <c r="F97" s="19"/>
       <c r="G97" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="F99" t="s">
-        <v>38</v>
-      </c>
-      <c r="G99" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="100">
       <c r="F100" t="s">
-        <v>39</v>
-      </c>
-      <c r="G100" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G100" s="23"/>
+    </row>
+    <row r="101">
+      <c r="F101" t="s">
+        <v>37</v>
+      </c>
+      <c r="G101" s="23"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -2049,26 +2060,26 @@
     </row>
     <row r="110">
       <c r="A110" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G67)</f>
-      </c>
-      <c r="B110" s="19"/>
-      <c r="C110" s="19"/>
-      <c r="D110" s="19"/>
-      <c r="E110" s="19"/>
-      <c r="F110" s="19"/>
+        <f>CONCATENATE("M 4 ",G68)</f>
+      </c>
+      <c r="B110" s="22"/>
+      <c r="C110" s="22"/>
+      <c r="D110" s="22"/>
+      <c r="E110" s="22"/>
+      <c r="F110" s="22"/>
       <c r="G110" s="19" t="str">
-        <f>CONCATENATE("M 3 ",G51)</f>
+        <f>CONCATENATE("M 3 ",G52)</f>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="19">
         <v>1</v>
       </c>
-      <c r="B111" s="19"/>
-      <c r="C111" s="19"/>
-      <c r="D111" s="19"/>
-      <c r="E111" s="19"/>
-      <c r="F111" s="19"/>
+      <c r="B111" s="22"/>
+      <c r="C111" s="22"/>
+      <c r="D111" s="22"/>
+      <c r="E111" s="22"/>
+      <c r="F111" s="22"/>
       <c r="G111" s="19">
         <v>1</v>
       </c>
@@ -2077,11 +2088,11 @@
       <c r="A112" s="19">
         <v>2</v>
       </c>
-      <c r="B112" s="19"/>
-      <c r="C112" s="19"/>
-      <c r="D112" s="19"/>
-      <c r="E112" s="19"/>
-      <c r="F112" s="19"/>
+      <c r="B112" s="22"/>
+      <c r="C112" s="22"/>
+      <c r="D112" s="22"/>
+      <c r="E112" s="22"/>
+      <c r="F112" s="22"/>
       <c r="G112" s="19">
         <v>2</v>
       </c>
@@ -2090,11 +2101,11 @@
       <c r="A113" s="19">
         <v>3</v>
       </c>
-      <c r="B113" s="19"/>
-      <c r="C113" s="19"/>
-      <c r="D113" s="19"/>
-      <c r="E113" s="19"/>
-      <c r="F113" s="19"/>
+      <c r="B113" s="22"/>
+      <c r="C113" s="22"/>
+      <c r="D113" s="22"/>
+      <c r="E113" s="22"/>
+      <c r="F113" s="22"/>
       <c r="G113" s="19">
         <v>3</v>
       </c>
@@ -2103,11 +2114,11 @@
       <c r="A114" s="19">
         <v>4</v>
       </c>
-      <c r="B114" s="19"/>
-      <c r="C114" s="19"/>
-      <c r="D114" s="19"/>
-      <c r="E114" s="19"/>
-      <c r="F114" s="19"/>
+      <c r="B114" s="22"/>
+      <c r="C114" s="22"/>
+      <c r="D114" s="22"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="22"/>
       <c r="G114" s="19">
         <v>4</v>
       </c>
@@ -2116,39 +2127,39 @@
       <c r="A115" s="19">
         <v>5</v>
       </c>
-      <c r="B115" s="19"/>
-      <c r="C115" s="19"/>
-      <c r="D115" s="19"/>
-      <c r="E115" s="19"/>
-      <c r="F115" s="19"/>
+      <c r="B115" s="22"/>
+      <c r="C115" s="22"/>
+      <c r="D115" s="22"/>
+      <c r="E115" s="22"/>
+      <c r="F115" s="22"/>
       <c r="G115" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G67)</f>
-      </c>
-      <c r="B117" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C117" s="19" t="s">
-        <v>36</v>
+        <f>CONCATENATE("M 4 ",G68)</f>
+      </c>
+      <c r="B117" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C117" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D117" s="19"/>
-      <c r="E117" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F117" s="19" t="s">
-        <v>35</v>
+      <c r="E117" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F117" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G117" s="19" t="str">
-        <f>CONCATENATE("M 3 ",G51)</f>
+        <f>CONCATENATE("M 3 ",G52)</f>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B118" s="19"/>
       <c r="C118" s="19"/>
@@ -2156,24 +2167,24 @@
       <c r="E118" s="19"/>
       <c r="F118" s="19"/>
       <c r="G118" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="F120" t="s">
-        <v>38</v>
-      </c>
-      <c r="G120" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="121">
       <c r="F121" t="s">
-        <v>39</v>
-      </c>
-      <c r="G121" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G121" s="23"/>
+    </row>
+    <row r="122">
+      <c r="F122" t="s">
+        <v>37</v>
+      </c>
+      <c r="G122" s="23"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
@@ -2195,26 +2206,26 @@
     </row>
     <row r="126">
       <c r="A126" s="19" t="str">
-        <f>CONCATENATE("M 6 ",G99)</f>
-      </c>
-      <c r="B126" s="19"/>
-      <c r="C126" s="19"/>
-      <c r="D126" s="19"/>
-      <c r="E126" s="19"/>
-      <c r="F126" s="19"/>
+        <f>CONCATENATE("M 6 ",G100)</f>
+      </c>
+      <c r="B126" s="22"/>
+      <c r="C126" s="22"/>
+      <c r="D126" s="22"/>
+      <c r="E126" s="22"/>
+      <c r="F126" s="22"/>
       <c r="G126" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G83)</f>
+        <f>CONCATENATE("M 5 ",G84)</f>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="19">
         <v>1</v>
       </c>
-      <c r="B127" s="19"/>
-      <c r="C127" s="19"/>
-      <c r="D127" s="19"/>
-      <c r="E127" s="19"/>
-      <c r="F127" s="19"/>
+      <c r="B127" s="22"/>
+      <c r="C127" s="22"/>
+      <c r="D127" s="22"/>
+      <c r="E127" s="22"/>
+      <c r="F127" s="22"/>
       <c r="G127" s="19">
         <v>1</v>
       </c>
@@ -2223,11 +2234,11 @@
       <c r="A128" s="19">
         <v>2</v>
       </c>
-      <c r="B128" s="19"/>
-      <c r="C128" s="19"/>
-      <c r="D128" s="19"/>
-      <c r="E128" s="19"/>
-      <c r="F128" s="19"/>
+      <c r="B128" s="22"/>
+      <c r="C128" s="22"/>
+      <c r="D128" s="22"/>
+      <c r="E128" s="22"/>
+      <c r="F128" s="22"/>
       <c r="G128" s="19">
         <v>2</v>
       </c>
@@ -2236,11 +2247,11 @@
       <c r="A129" s="19">
         <v>3</v>
       </c>
-      <c r="B129" s="19"/>
-      <c r="C129" s="19"/>
-      <c r="D129" s="19"/>
-      <c r="E129" s="19"/>
-      <c r="F129" s="19"/>
+      <c r="B129" s="22"/>
+      <c r="C129" s="22"/>
+      <c r="D129" s="22"/>
+      <c r="E129" s="22"/>
+      <c r="F129" s="22"/>
       <c r="G129" s="19">
         <v>3</v>
       </c>
@@ -2249,11 +2260,11 @@
       <c r="A130" s="19">
         <v>4</v>
       </c>
-      <c r="B130" s="19"/>
-      <c r="C130" s="19"/>
-      <c r="D130" s="19"/>
-      <c r="E130" s="19"/>
-      <c r="F130" s="19"/>
+      <c r="B130" s="22"/>
+      <c r="C130" s="22"/>
+      <c r="D130" s="22"/>
+      <c r="E130" s="22"/>
+      <c r="F130" s="22"/>
       <c r="G130" s="19">
         <v>4</v>
       </c>
@@ -2262,39 +2273,39 @@
       <c r="A131" s="19">
         <v>5</v>
       </c>
-      <c r="B131" s="19"/>
-      <c r="C131" s="19"/>
-      <c r="D131" s="19"/>
-      <c r="E131" s="19"/>
-      <c r="F131" s="19"/>
+      <c r="B131" s="22"/>
+      <c r="C131" s="22"/>
+      <c r="D131" s="22"/>
+      <c r="E131" s="22"/>
+      <c r="F131" s="22"/>
       <c r="G131" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="19" t="str">
-        <f>CONCATENATE("M 6 ",G99)</f>
-      </c>
-      <c r="B133" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C133" s="19" t="s">
-        <v>36</v>
+        <f>CONCATENATE("M 6 ",G100)</f>
+      </c>
+      <c r="B133" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C133" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D133" s="19"/>
-      <c r="E133" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F133" s="19" t="s">
-        <v>35</v>
+      <c r="E133" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F133" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G133" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G83)</f>
+        <f>CONCATENATE("M 5 ",G84)</f>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B134" s="19"/>
       <c r="C134" s="19"/>
@@ -2302,24 +2313,24 @@
       <c r="E134" s="19"/>
       <c r="F134" s="19"/>
       <c r="G134" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="F136" t="s">
-        <v>38</v>
-      </c>
-      <c r="G136" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="137">
       <c r="F137" t="s">
-        <v>39</v>
-      </c>
-      <c r="G137" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G137" s="23"/>
+    </row>
+    <row r="138">
+      <c r="F138" t="s">
+        <v>37</v>
+      </c>
+      <c r="G138" s="23"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
@@ -2341,26 +2352,26 @@
     </row>
     <row r="147">
       <c r="A147" s="19" t="str">
-        <f>CONCATENATE("M 8 ",G136)</f>
-      </c>
-      <c r="B147" s="19"/>
-      <c r="C147" s="19"/>
-      <c r="D147" s="19"/>
-      <c r="E147" s="19"/>
-      <c r="F147" s="19"/>
+        <f>CONCATENATE("M 8 ",G137)</f>
+      </c>
+      <c r="B147" s="22"/>
+      <c r="C147" s="22"/>
+      <c r="D147" s="22"/>
+      <c r="E147" s="22"/>
+      <c r="F147" s="22"/>
       <c r="G147" s="19" t="str">
-        <f>CONCATENATE("M 7 ",G120)</f>
+        <f>CONCATENATE("M 7 ",G121)</f>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="19">
         <v>1</v>
       </c>
-      <c r="B148" s="19"/>
-      <c r="C148" s="19"/>
-      <c r="D148" s="19"/>
-      <c r="E148" s="19"/>
-      <c r="F148" s="19"/>
+      <c r="B148" s="22"/>
+      <c r="C148" s="22"/>
+      <c r="D148" s="22"/>
+      <c r="E148" s="22"/>
+      <c r="F148" s="22"/>
       <c r="G148" s="19">
         <v>1</v>
       </c>
@@ -2369,11 +2380,11 @@
       <c r="A149" s="19">
         <v>2</v>
       </c>
-      <c r="B149" s="19"/>
-      <c r="C149" s="19"/>
-      <c r="D149" s="19"/>
-      <c r="E149" s="19"/>
-      <c r="F149" s="19"/>
+      <c r="B149" s="22"/>
+      <c r="C149" s="22"/>
+      <c r="D149" s="22"/>
+      <c r="E149" s="22"/>
+      <c r="F149" s="22"/>
       <c r="G149" s="19">
         <v>2</v>
       </c>
@@ -2382,11 +2393,11 @@
       <c r="A150" s="19">
         <v>3</v>
       </c>
-      <c r="B150" s="19"/>
-      <c r="C150" s="19"/>
-      <c r="D150" s="19"/>
-      <c r="E150" s="19"/>
-      <c r="F150" s="19"/>
+      <c r="B150" s="22"/>
+      <c r="C150" s="22"/>
+      <c r="D150" s="22"/>
+      <c r="E150" s="22"/>
+      <c r="F150" s="22"/>
       <c r="G150" s="19">
         <v>3</v>
       </c>
@@ -2395,11 +2406,11 @@
       <c r="A151" s="19">
         <v>4</v>
       </c>
-      <c r="B151" s="19"/>
-      <c r="C151" s="19"/>
-      <c r="D151" s="19"/>
-      <c r="E151" s="19"/>
-      <c r="F151" s="19"/>
+      <c r="B151" s="22"/>
+      <c r="C151" s="22"/>
+      <c r="D151" s="22"/>
+      <c r="E151" s="22"/>
+      <c r="F151" s="22"/>
       <c r="G151" s="19">
         <v>4</v>
       </c>
@@ -2408,39 +2419,39 @@
       <c r="A152" s="19">
         <v>5</v>
       </c>
-      <c r="B152" s="19"/>
-      <c r="C152" s="19"/>
-      <c r="D152" s="19"/>
-      <c r="E152" s="19"/>
-      <c r="F152" s="19"/>
+      <c r="B152" s="22"/>
+      <c r="C152" s="22"/>
+      <c r="D152" s="22"/>
+      <c r="E152" s="22"/>
+      <c r="F152" s="22"/>
       <c r="G152" s="19">
         <v>5</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="19" t="str">
-        <f>CONCATENATE("M 8 ",G136)</f>
-      </c>
-      <c r="B154" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C154" s="19" t="s">
-        <v>36</v>
+        <f>CONCATENATE("M 8 ",G137)</f>
+      </c>
+      <c r="B154" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C154" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))</f>
       </c>
       <c r="D154" s="19"/>
-      <c r="E154" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F154" s="19" t="s">
-        <v>35</v>
+      <c r="E154" s="22" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F154" s="22" t="str">
+        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-",""))))*1)</f>
       </c>
       <c r="G154" s="19" t="str">
-        <f>CONCATENATE("M 7 ",G120)</f>
+        <f>CONCATENATE("M 7 ",G121)</f>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B155" s="19"/>
       <c r="C155" s="19"/>
@@ -2448,22 +2459,23 @@
       <c r="E155" s="19"/>
       <c r="F155" s="19"/>
       <c r="G155" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="F157" t="s">
-        <v>38</v>
-      </c>
-      <c r="G157" s="15"/>
+        <v>35</v>
+      </c>
     </row>
     <row r="158">
       <c r="F158" t="s">
-        <v>39</v>
-      </c>
-      <c r="G158" s="15"/>
+        <v>36</v>
+      </c>
+      <c r="G158" s="23"/>
+    </row>
+    <row r="159">
+      <c r="F159" t="s">
+        <v>37</v>
+      </c>
+      <c r="G159" s="23"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="10">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
@@ -2696,6 +2708,7 @@
       <c r="E35" s="12"/>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
     <mergeCell ref="A1:P1"/>
   </mergeCells>
@@ -2791,6 +2804,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <pageMargins left="0.1" right="0.1" top="0.1" bottom="0.1" header="0.1" footer="0.1"/>
   <pageSetup orientation="landscape" paperSize="8"/>
   <rowBreaks count="3" manualBreakCount="3">

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -15,14 +15,14 @@
   </sheets>
   <definedNames>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$10</definedName>
-    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$G$165</definedName>
+    <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$165</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Number of pools</t>
   </si>
@@ -127,6 +127,12 @@
   </si>
   <si>
     <t>Red</t>
+  </si>
+  <si>
+    <t>IV</t>
+  </si>
+  <si>
+    <t>PW</t>
   </si>
   <si>
     <t>Victories / Points</t>
@@ -1052,7 +1058,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -1063,7 +1069,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -1073,7 +1079,7 @@
     </row>
     <row r="15">
       <c r="E15" s="25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
@@ -1083,7 +1089,7 @@
     </row>
     <row r="16">
       <c r="E16" s="25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
@@ -1093,7 +1099,7 @@
     </row>
     <row r="17">
       <c r="E17" s="25" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
@@ -1103,7 +1109,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -1113,7 +1119,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -1137,14 +1143,11 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="3" min="2" width="5"/>
-    <col customWidth="true" max="4" min="4" width="3"/>
-    <col customWidth="true" max="6" min="5" width="5"/>
+    <col customWidth="true" max="6" min="2" width="5"/>
     <col customWidth="true" max="7" min="7" width="30"/>
-    <col customWidth="true" max="10" min="8" width="5"/>
-    <col customWidth="true" max="11" min="11" width="30"/>
-    <col customWidth="true" max="12" min="12" width="2"/>
-    <col customWidth="true" max="14" min="13" width="3.83"/>
+    <col customWidth="true" max="8" min="8" width="5"/>
+    <col customWidth="true" max="9" min="9" width="34.83"/>
+    <col customWidth="true" max="14" min="10" width="3.83"/>
     <col customWidth="true" max="15" min="15" width="34.83"/>
     <col customWidth="true" max="20" min="16" width="10.83"/>
   </cols>
@@ -1186,11 +1189,11 @@
       <c r="A4" s="19" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B4" s="22"/>
-      <c r="C4" s="22"/>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
       <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
       <c r="G4" s="19" t="str">
         <f>'data'!$B$6</f>
       </c>
@@ -1264,18 +1267,18 @@
       <c r="A11" s="19" t="str">
         <f>'data'!$B$7</f>
       </c>
-      <c r="B11" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C11" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+      <c r="B11" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D11" s="19"/>
-      <c r="E11" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F11" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E11" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G11" s="19" t="str">
         <f>'data'!$B$6</f>
@@ -1283,32 +1286,40 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B12" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C12" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
+      <c r="E12" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F12" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G12" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G15" s="23"/>
     </row>
     <row r="16">
       <c r="F16" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G16" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1332,11 +1343,11 @@
       <c r="A20" s="19" t="str">
         <f>'data'!$B$12</f>
       </c>
-      <c r="B20" s="22"/>
-      <c r="C20" s="22"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
       <c r="D20" s="22"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
       <c r="G20" s="19" t="str">
         <f>'data'!$B$11</f>
       </c>
@@ -1410,18 +1421,18 @@
       <c r="A27" s="19" t="str">
         <f>'data'!$B$12</f>
       </c>
-      <c r="B27" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C27" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+      <c r="B27" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D27" s="19"/>
-      <c r="E27" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F27" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E27" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G27" s="19" t="str">
         <f>'data'!$B$11</f>
@@ -1429,32 +1440,40 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B28" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C28" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="E28" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F28" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G28" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G31" s="23"/>
     </row>
     <row r="32">
       <c r="F32" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G32" s="23"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B39" s="11"/>
       <c r="C39" s="11"/>
@@ -1478,11 +1497,11 @@
       <c r="A41" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="B41" s="22"/>
-      <c r="C41" s="22"/>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
       <c r="D41" s="22"/>
-      <c r="E41" s="22"/>
-      <c r="F41" s="22"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
       <c r="G41" s="19" t="str">
         <f>'data'!$B$3</f>
       </c>
@@ -1556,18 +1575,18 @@
       <c r="A48" s="19" t="str">
         <f>'data'!$B$4</f>
       </c>
-      <c r="B48" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C48" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))</f>
+      <c r="B48" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C48" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D48" s="19"/>
-      <c r="E48" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F48" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E48" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G48" s="19" t="str">
         <f>'data'!$B$3</f>
@@ -1575,32 +1594,40 @@
     </row>
     <row r="49">
       <c r="A49" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B49" s="19"/>
-      <c r="C49" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B49" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C49" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D49" s="19"/>
-      <c r="E49" s="19"/>
-      <c r="F49" s="19"/>
+      <c r="E49" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F49" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G49" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="52">
       <c r="F52" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G52" s="23"/>
     </row>
     <row r="53">
       <c r="F53" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G53" s="23"/>
     </row>
     <row r="55">
       <c r="A55" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B55" s="11"/>
       <c r="C55" s="11"/>
@@ -1624,11 +1651,11 @@
       <c r="A57" s="19" t="str">
         <f>CONCATENATE("M 1 ",G15)</f>
       </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
+      <c r="B57" s="19"/>
+      <c r="C57" s="19"/>
       <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
       <c r="G57" s="19" t="str">
         <f>'data'!$B$5</f>
       </c>
@@ -1702,18 +1729,18 @@
       <c r="A64" s="19" t="str">
         <f>CONCATENATE("M 1 ",G15)</f>
       </c>
-      <c r="B64" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C64" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))</f>
+      <c r="B64" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C64" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D64" s="19"/>
-      <c r="E64" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F64" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E64" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F64" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G64" s="19" t="str">
         <f>'data'!$B$5</f>
@@ -1721,32 +1748,40 @@
     </row>
     <row r="65">
       <c r="A65" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B65" s="19"/>
-      <c r="C65" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B65" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C65" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D65" s="19"/>
-      <c r="E65" s="19"/>
-      <c r="F65" s="19"/>
+      <c r="E65" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F65" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G65" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="68">
       <c r="F68" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G68" s="23"/>
     </row>
     <row r="69">
       <c r="F69" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G69" s="23"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
@@ -1770,11 +1805,11 @@
       <c r="A73" s="19" t="str">
         <f>'data'!$B$9</f>
       </c>
-      <c r="B73" s="22"/>
-      <c r="C73" s="22"/>
+      <c r="B73" s="19"/>
+      <c r="C73" s="19"/>
       <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
+      <c r="E73" s="19"/>
+      <c r="F73" s="19"/>
       <c r="G73" s="19" t="str">
         <f>'data'!$B$8</f>
       </c>
@@ -1848,18 +1883,18 @@
       <c r="A80" s="19" t="str">
         <f>'data'!$B$9</f>
       </c>
-      <c r="B80" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C80" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))</f>
+      <c r="B80" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D80" s="19"/>
-      <c r="E80" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F80" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E80" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F80" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G80" s="19" t="str">
         <f>'data'!$B$8</f>
@@ -1867,32 +1902,40 @@
     </row>
     <row r="81">
       <c r="A81" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B81" s="19"/>
-      <c r="C81" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B81" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C81" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D81" s="19"/>
-      <c r="E81" s="19"/>
-      <c r="F81" s="19"/>
+      <c r="E81" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F81" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G81" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="84">
       <c r="F84" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G84" s="23"/>
     </row>
     <row r="85">
       <c r="F85" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G85" s="23"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
@@ -1916,11 +1959,11 @@
       <c r="A89" s="19" t="str">
         <f>CONCATENATE("M 2 ",G31)</f>
       </c>
-      <c r="B89" s="22"/>
-      <c r="C89" s="22"/>
+      <c r="B89" s="19"/>
+      <c r="C89" s="19"/>
       <c r="D89" s="22"/>
-      <c r="E89" s="22"/>
-      <c r="F89" s="22"/>
+      <c r="E89" s="19"/>
+      <c r="F89" s="19"/>
       <c r="G89" s="19" t="str">
         <f>'data'!$B$10</f>
       </c>
@@ -1994,18 +2037,18 @@
       <c r="A96" s="19" t="str">
         <f>CONCATENATE("M 2 ",G31)</f>
       </c>
-      <c r="B96" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C96" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))</f>
+      <c r="B96" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C96" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D96" s="19"/>
-      <c r="E96" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F96" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E96" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F96" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G96" s="19" t="str">
         <f>'data'!$B$10</f>
@@ -2013,32 +2056,40 @@
     </row>
     <row r="97">
       <c r="A97" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B97" s="19"/>
-      <c r="C97" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B97" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C97" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D97" s="19"/>
-      <c r="E97" s="19"/>
-      <c r="F97" s="19"/>
+      <c r="E97" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F97" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G97" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="100">
       <c r="F100" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G100" s="23"/>
     </row>
     <row r="101">
       <c r="F101" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G101" s="23"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -2062,11 +2113,11 @@
       <c r="A110" s="19" t="str">
         <f>CONCATENATE("M 4 ",G68)</f>
       </c>
-      <c r="B110" s="22"/>
-      <c r="C110" s="22"/>
+      <c r="B110" s="19"/>
+      <c r="C110" s="19"/>
       <c r="D110" s="22"/>
-      <c r="E110" s="22"/>
-      <c r="F110" s="22"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="19"/>
       <c r="G110" s="19" t="str">
         <f>CONCATENATE("M 3 ",G52)</f>
       </c>
@@ -2140,18 +2191,18 @@
       <c r="A117" s="19" t="str">
         <f>CONCATENATE("M 4 ",G68)</f>
       </c>
-      <c r="B117" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C117" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))</f>
+      <c r="B117" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C117" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D117" s="19"/>
-      <c r="E117" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F117" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E117" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F117" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G117" s="19" t="str">
         <f>CONCATENATE("M 3 ",G52)</f>
@@ -2159,32 +2210,40 @@
     </row>
     <row r="118">
       <c r="A118" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B118" s="19"/>
-      <c r="C118" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B118" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C118" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D118" s="19"/>
-      <c r="E118" s="19"/>
-      <c r="F118" s="19"/>
+      <c r="E118" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F118" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G118" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="121">
       <c r="F121" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G121" s="23"/>
     </row>
     <row r="122">
       <c r="F122" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G122" s="23"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
@@ -2208,11 +2267,11 @@
       <c r="A126" s="19" t="str">
         <f>CONCATENATE("M 6 ",G100)</f>
       </c>
-      <c r="B126" s="22"/>
-      <c r="C126" s="22"/>
+      <c r="B126" s="19"/>
+      <c r="C126" s="19"/>
       <c r="D126" s="22"/>
-      <c r="E126" s="22"/>
-      <c r="F126" s="22"/>
+      <c r="E126" s="19"/>
+      <c r="F126" s="19"/>
       <c r="G126" s="19" t="str">
         <f>CONCATENATE("M 5 ",G84)</f>
       </c>
@@ -2286,18 +2345,18 @@
       <c r="A133" s="19" t="str">
         <f>CONCATENATE("M 6 ",G100)</f>
       </c>
-      <c r="B133" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C133" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))</f>
+      <c r="B133" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C133" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D133" s="19"/>
-      <c r="E133" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F133" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E133" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F133" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G133" s="19" t="str">
         <f>CONCATENATE("M 5 ",G84)</f>
@@ -2305,32 +2364,40 @@
     </row>
     <row r="134">
       <c r="A134" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B134" s="19"/>
-      <c r="C134" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B134" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C134" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D134" s="19"/>
-      <c r="E134" s="19"/>
-      <c r="F134" s="19"/>
+      <c r="E134" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F134" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G134" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="137">
       <c r="F137" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G137" s="23"/>
     </row>
     <row r="138">
       <c r="F138" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G138" s="23"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
@@ -2354,11 +2421,11 @@
       <c r="A147" s="19" t="str">
         <f>CONCATENATE("M 8 ",G137)</f>
       </c>
-      <c r="B147" s="22"/>
-      <c r="C147" s="22"/>
+      <c r="B147" s="19"/>
+      <c r="C147" s="19"/>
       <c r="D147" s="22"/>
-      <c r="E147" s="22"/>
-      <c r="F147" s="22"/>
+      <c r="E147" s="19"/>
+      <c r="F147" s="19"/>
       <c r="G147" s="19" t="str">
         <f>CONCATENATE("M 7 ",G121)</f>
       </c>
@@ -2432,18 +2499,18 @@
       <c r="A154" s="19" t="str">
         <f>CONCATENATE("M 8 ",G137)</f>
       </c>
-      <c r="B154" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-",""))))*1)</f>
-      </c>
-      <c r="C154" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))</f>
+      <c r="B154" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C154" s="19" t="s">
+        <v>36</v>
       </c>
       <c r="D154" s="19"/>
-      <c r="E154" s="22" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))</f>
-      </c>
-      <c r="F154" s="22" t="str">
-        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-",""))))*1)</f>
+      <c r="E154" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F154" s="19" t="s">
+        <v>35</v>
       </c>
       <c r="G154" s="19" t="str">
         <f>CONCATENATE("M 7 ",G121)</f>
@@ -2451,26 +2518,34 @@
     </row>
     <row r="155">
       <c r="A155" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B155" s="19"/>
-      <c r="C155" s="19"/>
+        <v>37</v>
+      </c>
+      <c r="B155" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-",""))))*1)</f>
+      </c>
+      <c r="C155" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))</f>
+      </c>
       <c r="D155" s="19"/>
-      <c r="E155" s="19"/>
-      <c r="F155" s="19"/>
+      <c r="E155" s="19" t="str">
+        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))</f>
+      </c>
+      <c r="F155" s="19" t="str">
+        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-",""))))*1)</f>
+      </c>
       <c r="G155" s="19" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="158">
       <c r="F158" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G158" s="23"/>
     </row>
     <row r="159">
       <c r="F159" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G159" s="23"/>
     </row>
@@ -2728,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="18" t="str">
-        <f>data!$B$3</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
@@ -2736,7 +2811,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="18" t="str">
-        <f>data!$B$4</f>
+        <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
@@ -2744,7 +2819,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="18" t="str">
-        <f>data!$B$5</f>
+        <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
@@ -2752,7 +2827,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="18" t="str">
-        <f>data!$B$6</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
@@ -2760,7 +2835,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="18" t="str">
-        <f>data!$B$7</f>
+        <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
@@ -2768,7 +2843,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="18" t="str">
-        <f>data!$B$8</f>
+        <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
@@ -2776,7 +2851,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="18" t="str">
-        <f>data!$B$9</f>
+        <f>'data'!$B$9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
@@ -2784,7 +2859,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="18" t="str">
-        <f>data!$B$10</f>
+        <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
@@ -2792,7 +2867,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="18" t="str">
-        <f>data!$B$11</f>
+        <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
@@ -2800,7 +2875,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f>data!$B$12</f>
+        <f>'data'!$B$12</f>
       </c>
     </row>
   </sheetData>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -1289,17 +1289,17 @@
         <v>37</v>
       </c>
       <c r="B12" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C12" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F12" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D5:D9)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5:E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5:F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5:B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5:C9," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G12" s="19" t="s">
         <v>37</v>
@@ -1443,17 +1443,17 @@
         <v>37</v>
       </c>
       <c r="B28" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C28" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F28" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D21:D25)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21:E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21:F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21:B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21:C25," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G28" s="19" t="s">
         <v>37</v>
@@ -1597,17 +1597,17 @@
         <v>37</v>
       </c>
       <c r="B49" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C49" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F49" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D42:D46)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42:E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42:F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42:B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42:C46," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G49" s="19" t="s">
         <v>37</v>
@@ -1751,17 +1751,17 @@
         <v>37</v>
       </c>
       <c r="B65" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C65" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F65" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D58:D62)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58:E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58:F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58:B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58:C62," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G65" s="19" t="s">
         <v>37</v>
@@ -1905,17 +1905,17 @@
         <v>37</v>
       </c>
       <c r="B81" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C81" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D81" s="19"/>
       <c r="E81" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F81" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D74:D78)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74:E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74:F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74:B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74:C78," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G81" s="19" t="s">
         <v>37</v>
@@ -2059,17 +2059,17 @@
         <v>37</v>
       </c>
       <c r="B97" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C97" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F97" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D90:D94)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90:E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90:F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90:B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90:C94," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G97" s="19" t="s">
         <v>37</v>
@@ -2213,17 +2213,17 @@
         <v>37</v>
       </c>
       <c r="B118" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C118" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D118" s="19"/>
       <c r="E118" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F118" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D111:D115)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111:E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111:F115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111:B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111:C115," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G118" s="19" t="s">
         <v>37</v>
@@ -2367,17 +2367,17 @@
         <v>37</v>
       </c>
       <c r="B134" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C134" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D134" s="19"/>
       <c r="E134" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F134" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D127:D131)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127:E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127:F131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127:B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127:C131," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G134" s="19" t="s">
         <v>37</v>
@@ -2521,17 +2521,17 @@
         <v>37</v>
       </c>
       <c r="B155" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="C155" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) </f>
       </c>
       <c r="D155" s="19"/>
       <c r="E155" s="19" t="str">
-        <f>SUMPRODUCT(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))</f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) </f>
       </c>
       <c r="F155" s="19" t="str">
-        <f>SUMPRODUCT((UPPER(D148:D152)&lt;&gt;"X")*((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148:E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148:F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148:B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148:C152," ",""),"0",""),"-",""))))*1)</f>
+        <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))</f>
       </c>
       <c r="G155" s="19" t="s">
         <v>37</v>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -1289,17 +1289,17 @@
         <v>37</v>
       </c>
       <c r="B12" s="19" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C12" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F12" s="19" t="str">
-        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="19" t="s">
         <v>37</v>
@@ -1443,17 +1443,17 @@
         <v>37</v>
       </c>
       <c r="B28" s="19" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C28" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F28" s="19" t="str">
-        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G28" s="19" t="s">
         <v>37</v>
@@ -1597,17 +1597,17 @@
         <v>37</v>
       </c>
       <c r="B49" s="19" t="str">
-        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C49" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F49" s="19" t="str">
-        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G49" s="19" t="s">
         <v>37</v>
@@ -1751,17 +1751,17 @@
         <v>37</v>
       </c>
       <c r="B65" s="19" t="str">
-        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C65" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F65" s="19" t="str">
-        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G65" s="19" t="s">
         <v>37</v>
@@ -1905,17 +1905,17 @@
         <v>37</v>
       </c>
       <c r="B81" s="19" t="str">
-        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C81" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D81" s="19"/>
       <c r="E81" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F81" s="19" t="str">
-        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G81" s="19" t="s">
         <v>37</v>
@@ -2059,17 +2059,17 @@
         <v>37</v>
       </c>
       <c r="B97" s="19" t="str">
-        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C97" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D97" s="19"/>
       <c r="E97" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F97" s="19" t="str">
-        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G97" s="19" t="s">
         <v>37</v>
@@ -2213,17 +2213,17 @@
         <v>37</v>
       </c>
       <c r="B118" s="19" t="str">
-        <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C118" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D118" s="19"/>
       <c r="E118" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F118" s="19" t="str">
-        <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G118" s="19" t="s">
         <v>37</v>
@@ -2367,17 +2367,17 @@
         <v>37</v>
       </c>
       <c r="B134" s="19" t="str">
-        <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C134" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D134" s="19"/>
       <c r="E134" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F134" s="19" t="str">
-        <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G134" s="19" t="s">
         <v>37</v>
@@ -2521,17 +2521,17 @@
         <v>37</v>
       </c>
       <c r="B155" s="19" t="str">
-        <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="C155" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))</f>
       </c>
       <c r="D155" s="19"/>
       <c r="E155" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) </f>
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))</f>
       </c>
       <c r="F155" s="19" t="str">
-        <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")) ),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")) )&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-","")) +LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")) ),1,0))</f>
+        <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G155" s="19" t="s">
         <v>37</v>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Names to Print A" sheetId="9" r:id="rId12"/>
   </sheets>
   <definedNames>
+    <definedName localSheetId="3" name="_xlnm.Print_Area">'Tree 1'!$A$1:$K$35</definedName>
     <definedName localSheetId="4" name="_xlnm.Print_Area">'Names to Print A'!$A$1:$B$10</definedName>
     <definedName localSheetId="2" name="_xlnm.Print_Area">'Elimination Matches'!$A$1:$H$165</definedName>
   </definedNames>
@@ -2576,12 +2577,17 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
   <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="25"/>
-    <col customWidth="true" max="2" min="2" width="10"/>
-    <col customWidth="true" max="26" min="3" width="3.5"/>
+    <col customWidth="true" max="2" min="2" width="4"/>
+    <col customWidth="true" max="3" min="3" width="28"/>
+    <col customWidth="true" max="26" min="4" width="3.5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2598,11 +2604,6 @@
       <c r="I1" s="11"/>
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
-      <c r="N1" s="11"/>
-      <c r="O1" s="11"/>
-      <c r="P1" s="11"/>
     </row>
     <row r="6">
       <c r="E6" s="16" t="s">
@@ -2785,8 +2786,10 @@
   </sheetData>
   <sheetProtection sheet="true" objects="true" scenarios="true" formatCells="true" formatColumns="true" formatRows="true" insertColumns="true" insertRows="true" insertHyperlinks="true" deleteColumns="true" deleteRows="true" selectLockedCells="false" sort="true" autoFilter="true" pivotTables="true" selectUnlockedCells="false"/>
   <mergeCells count="1">
-    <mergeCell ref="A1:P1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <printOptions horizontalCentered="true" verticalCentered="true"/>
+  <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -408,7 +408,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
@@ -2606,6 +2606,8 @@
       <c r="K1" s="11"/>
     </row>
     <row r="6">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
       <c r="E6" s="16" t="s">
         <v>15</v>
       </c>
@@ -2625,6 +2627,8 @@
       <c r="I9" s="12"/>
     </row>
     <row r="10">
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
       <c r="E10" s="16" t="s">
         <v>17</v>
       </c>
@@ -2646,6 +2650,8 @@
       <c r="K13" s="12"/>
     </row>
     <row r="14">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
         <v>19</v>
       </c>
@@ -2699,6 +2705,8 @@
       <c r="K21" s="12"/>
     </row>
     <row r="22">
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
       <c r="E22" s="16" t="s">
         <v>25</v>
       </c>
@@ -2722,6 +2730,8 @@
       <c r="K25" s="12"/>
     </row>
     <row r="26">
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
       <c r="E26" s="16" t="s">
         <v>26</v>
       </c>
@@ -2745,6 +2755,8 @@
       <c r="I29" s="12"/>
     </row>
     <row r="30">
+      <c r="C30" s="16"/>
+      <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
         <v>27</v>
       </c>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -148,10 +148,10 @@
     <t>Round 1 - Match 2</t>
   </si>
   <si>
-    <t>Round 2 - Match 3</t>
-  </si>
-  <si>
-    <t>Round 2 - Match 4</t>
+    <t>Round 1 - Match 3</t>
+  </si>
+  <si>
+    <t>Round 1 - Match 4</t>
   </si>
   <si>
     <t>Round 2 - Match 5</t>
@@ -1188,7 +1188,7 @@
     </row>
     <row r="4">
       <c r="A4" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -1196,7 +1196,7 @@
       <c r="E4" s="19"/>
       <c r="F4" s="19"/>
       <c r="G4" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="5">
@@ -1266,7 +1266,7 @@
     </row>
     <row r="11">
       <c r="A11" s="19" t="str">
-        <f>'data'!$B$7</f>
+        <f>'data'!$B$4</f>
       </c>
       <c r="B11" s="19" t="s">
         <v>35</v>
@@ -1282,7 +1282,7 @@
         <v>35</v>
       </c>
       <c r="G11" s="19" t="str">
-        <f>'data'!$B$6</f>
+        <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="12">
@@ -1342,7 +1342,7 @@
     </row>
     <row r="20">
       <c r="A20" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B20" s="19"/>
       <c r="C20" s="19"/>
@@ -1350,7 +1350,7 @@
       <c r="E20" s="19"/>
       <c r="F20" s="19"/>
       <c r="G20" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="21">
@@ -1420,7 +1420,7 @@
     </row>
     <row r="27">
       <c r="A27" s="19" t="str">
-        <f>'data'!$B$12</f>
+        <f>'data'!$B$7</f>
       </c>
       <c r="B27" s="19" t="s">
         <v>35</v>
@@ -1436,7 +1436,7 @@
         <v>35</v>
       </c>
       <c r="G27" s="19" t="str">
-        <f>'data'!$B$11</f>
+        <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="28">
@@ -1472,313 +1472,313 @@
       </c>
       <c r="G32" s="23"/>
     </row>
+    <row r="34">
+      <c r="A34" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="11"/>
+      <c r="C34" s="11"/>
+      <c r="D34" s="11"/>
+      <c r="E34" s="11"/>
+      <c r="F34" s="11"/>
+      <c r="G34" s="11"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="D35" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" s="20" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="19" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="22"/>
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="G36" s="19" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="19">
+        <v>1</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="19">
+        <v>2</v>
+      </c>
+      <c r="B38" s="22"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="22"/>
+      <c r="E38" s="22"/>
+      <c r="F38" s="22"/>
+      <c r="G38" s="19">
+        <v>2</v>
+      </c>
+    </row>
     <row r="39">
-      <c r="A39" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11"/>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11"/>
-      <c r="G39" s="11"/>
+      <c r="A39" s="19">
+        <v>3</v>
+      </c>
+      <c r="B39" s="22"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="22"/>
+      <c r="E39" s="22"/>
+      <c r="F39" s="22"/>
+      <c r="G39" s="19">
+        <v>3</v>
+      </c>
     </row>
     <row r="40">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="19">
+        <v>4</v>
+      </c>
+      <c r="B40" s="22"/>
+      <c r="C40" s="22"/>
+      <c r="D40" s="22"/>
+      <c r="E40" s="22"/>
+      <c r="F40" s="22"/>
+      <c r="G40" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="19">
+        <v>5</v>
+      </c>
+      <c r="B41" s="22"/>
+      <c r="C41" s="22"/>
+      <c r="D41" s="22"/>
+      <c r="E41" s="22"/>
+      <c r="F41" s="22"/>
+      <c r="G41" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="19" t="str">
+        <f>'data'!$B$9</f>
+      </c>
+      <c r="B43" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C43" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="F43" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43" s="19" t="str">
+        <f>'data'!$B$8</f>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B44" s="19" t="str">
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C44" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F44" s="19" t="str">
+        <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G44" s="19" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="F47" t="s">
+        <v>38</v>
+      </c>
+      <c r="G47" s="23"/>
+    </row>
+    <row r="48">
+      <c r="F48" t="s">
+        <v>39</v>
+      </c>
+      <c r="G48" s="23"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="11"/>
+      <c r="G50" s="11"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="D51" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="G40" s="20" t="s">
+      <c r="G51" s="20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="19" t="str">
-        <f>'data'!$B$4</f>
-      </c>
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="22"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19" t="str">
-        <f>'data'!$B$3</f>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="19">
+    <row r="52">
+      <c r="A52" s="19" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="B52" s="19"/>
+      <c r="C52" s="19"/>
+      <c r="D52" s="22"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="19">
         <v>1</v>
       </c>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="22"/>
-      <c r="F42" s="22"/>
-      <c r="G42" s="19">
+      <c r="B53" s="22"/>
+      <c r="C53" s="22"/>
+      <c r="D53" s="22"/>
+      <c r="E53" s="22"/>
+      <c r="F53" s="22"/>
+      <c r="G53" s="19">
         <v>1</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="19">
+    <row r="54">
+      <c r="A54" s="19">
         <v>2</v>
       </c>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="22"/>
-      <c r="G43" s="19">
+      <c r="B54" s="22"/>
+      <c r="C54" s="22"/>
+      <c r="D54" s="22"/>
+      <c r="E54" s="22"/>
+      <c r="F54" s="22"/>
+      <c r="G54" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="19">
+    <row r="55">
+      <c r="A55" s="19">
         <v>3</v>
       </c>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="22"/>
-      <c r="G44" s="19">
+      <c r="B55" s="22"/>
+      <c r="C55" s="22"/>
+      <c r="D55" s="22"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="22"/>
+      <c r="G55" s="19">
         <v>3</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="19">
+    <row r="56">
+      <c r="A56" s="19">
         <v>4</v>
       </c>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="22"/>
-      <c r="F45" s="22"/>
-      <c r="G45" s="19">
+      <c r="B56" s="22"/>
+      <c r="C56" s="22"/>
+      <c r="D56" s="22"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="22"/>
+      <c r="G56" s="19">
         <v>4</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="19">
+    <row r="57">
+      <c r="A57" s="19">
         <v>5</v>
       </c>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="19">
+      <c r="B57" s="22"/>
+      <c r="C57" s="22"/>
+      <c r="D57" s="22"/>
+      <c r="E57" s="22"/>
+      <c r="F57" s="22"/>
+      <c r="G57" s="19">
         <v>5</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="19" t="str">
-        <f>'data'!$B$4</f>
-      </c>
-      <c r="B48" s="19" t="s">
+    <row r="59">
+      <c r="A59" s="19" t="str">
+        <f>'data'!$B$12</f>
+      </c>
+      <c r="B59" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C59" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D48" s="19"/>
-      <c r="E48" s="19" t="s">
+      <c r="D59" s="19"/>
+      <c r="E59" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="F48" s="19" t="s">
+      <c r="F59" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G48" s="19" t="str">
-        <f>'data'!$B$3</f>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="19" t="s">
+      <c r="G59" s="19" t="str">
+        <f>'data'!$B$11</f>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B49" s="19" t="str">
-        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C49" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D49" s="19"/>
-      <c r="E49" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F49" s="19" t="str">
-        <f>IF(UPPER(D42)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F42," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B42," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C42," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D43)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F43," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B43," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C43," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D44)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F44," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B44," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C44," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D45)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F45," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B45," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C45," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D46)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F46," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B46," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C46," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G49" s="19" t="s">
+      <c r="B60" s="19" t="str">
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="C60" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19" t="str">
+        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))</f>
+      </c>
+      <c r="F60" s="19" t="str">
+        <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))),1,0))</f>
+      </c>
+      <c r="G60" s="19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="52">
-      <c r="F52" t="s">
+    <row r="63">
+      <c r="F63" t="s">
         <v>38</v>
       </c>
-      <c r="G52" s="23"/>
-    </row>
-    <row r="53">
-      <c r="F53" t="s">
+      <c r="G63" s="23"/>
+    </row>
+    <row r="64">
+      <c r="F64" t="s">
         <v>39</v>
       </c>
-      <c r="G53" s="23"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="B55" s="11"/>
-      <c r="C55" s="11"/>
-      <c r="D55" s="11"/>
-      <c r="E55" s="11"/>
-      <c r="F55" s="11"/>
-      <c r="G55" s="11"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="D56" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="G56" s="20" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G15)</f>
-      </c>
-      <c r="B57" s="19"/>
-      <c r="C57" s="19"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="19"/>
-      <c r="F57" s="19"/>
-      <c r="G57" s="19" t="str">
-        <f>'data'!$B$5</f>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="19">
-        <v>1</v>
-      </c>
-      <c r="B58" s="22"/>
-      <c r="C58" s="22"/>
-      <c r="D58" s="22"/>
-      <c r="E58" s="22"/>
-      <c r="F58" s="22"/>
-      <c r="G58" s="19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="19">
-        <v>2</v>
-      </c>
-      <c r="B59" s="22"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="22"/>
-      <c r="E59" s="22"/>
-      <c r="F59" s="22"/>
-      <c r="G59" s="19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="19">
-        <v>3</v>
-      </c>
-      <c r="B60" s="22"/>
-      <c r="C60" s="22"/>
-      <c r="D60" s="22"/>
-      <c r="E60" s="22"/>
-      <c r="F60" s="22"/>
-      <c r="G60" s="19">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="19">
-        <v>4</v>
-      </c>
-      <c r="B61" s="22"/>
-      <c r="C61" s="22"/>
-      <c r="D61" s="22"/>
-      <c r="E61" s="22"/>
-      <c r="F61" s="22"/>
-      <c r="G61" s="19">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="19">
-        <v>5</v>
-      </c>
-      <c r="B62" s="22"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="19">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="19" t="str">
-        <f>CONCATENATE("M 1 ",G15)</f>
-      </c>
-      <c r="B64" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="C64" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="D64" s="19"/>
-      <c r="E64" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="F64" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="G64" s="19" t="str">
-        <f>'data'!$B$5</f>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B65" s="19" t="str">
-        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="C65" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="D65" s="19"/>
-      <c r="E65" s="19" t="str">
-        <f>LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-",""))</f>
-      </c>
-      <c r="F65" s="19" t="str">
-        <f>IF(UPPER(D58)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F58," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B58," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C58," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D59)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F59," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B59," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C59," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D60)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F60," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B60," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C60," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D61)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F61," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B61," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C61," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D62)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F62," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B62," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C62," ",""),"0",""),"-",""))),1,0))</f>
-      </c>
-      <c r="G65" s="19" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="F68" t="s">
-        <v>38</v>
-      </c>
-      <c r="G68" s="23"/>
-    </row>
-    <row r="69">
-      <c r="F69" t="s">
-        <v>39</v>
-      </c>
-      <c r="G69" s="23"/>
+      <c r="G64" s="23"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
@@ -1804,7 +1804,7 @@
     </row>
     <row r="73">
       <c r="A73" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>CONCATENATE("M 2 ",G31)</f>
       </c>
       <c r="B73" s="19"/>
       <c r="C73" s="19"/>
@@ -1812,7 +1812,7 @@
       <c r="E73" s="19"/>
       <c r="F73" s="19"/>
       <c r="G73" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="74">
@@ -1882,7 +1882,7 @@
     </row>
     <row r="80">
       <c r="A80" s="19" t="str">
-        <f>'data'!$B$9</f>
+        <f>CONCATENATE("M 2 ",G31)</f>
       </c>
       <c r="B80" s="19" t="s">
         <v>35</v>
@@ -1898,7 +1898,7 @@
         <v>35</v>
       </c>
       <c r="G80" s="19" t="str">
-        <f>'data'!$B$8</f>
+        <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="81">
@@ -1958,7 +1958,7 @@
     </row>
     <row r="89">
       <c r="A89" s="19" t="str">
-        <f>CONCATENATE("M 2 ",G31)</f>
+        <f>CONCATENATE("M 4 ",G63)</f>
       </c>
       <c r="B89" s="19"/>
       <c r="C89" s="19"/>
@@ -2036,7 +2036,7 @@
     </row>
     <row r="96">
       <c r="A96" s="19" t="str">
-        <f>CONCATENATE("M 2 ",G31)</f>
+        <f>CONCATENATE("M 4 ",G63)</f>
       </c>
       <c r="B96" s="19" t="s">
         <v>35</v>
@@ -2112,7 +2112,7 @@
     </row>
     <row r="110">
       <c r="A110" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G68)</f>
+        <f>CONCATENATE("M 5 ",G84)</f>
       </c>
       <c r="B110" s="19"/>
       <c r="C110" s="19"/>
@@ -2120,7 +2120,7 @@
       <c r="E110" s="19"/>
       <c r="F110" s="19"/>
       <c r="G110" s="19" t="str">
-        <f>CONCATENATE("M 3 ",G52)</f>
+        <f>CONCATENATE("M 1 ",G15)</f>
       </c>
     </row>
     <row r="111">
@@ -2190,7 +2190,7 @@
     </row>
     <row r="117">
       <c r="A117" s="19" t="str">
-        <f>CONCATENATE("M 4 ",G68)</f>
+        <f>CONCATENATE("M 5 ",G84)</f>
       </c>
       <c r="B117" s="19" t="s">
         <v>35</v>
@@ -2206,7 +2206,7 @@
         <v>35</v>
       </c>
       <c r="G117" s="19" t="str">
-        <f>CONCATENATE("M 3 ",G52)</f>
+        <f>CONCATENATE("M 1 ",G15)</f>
       </c>
     </row>
     <row r="118">
@@ -2274,7 +2274,7 @@
       <c r="E126" s="19"/>
       <c r="F126" s="19"/>
       <c r="G126" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G84)</f>
+        <f>CONCATENATE("M 3 ",G47)</f>
       </c>
     </row>
     <row r="127">
@@ -2360,7 +2360,7 @@
         <v>35</v>
       </c>
       <c r="G133" s="19" t="str">
-        <f>CONCATENATE("M 5 ",G84)</f>
+        <f>CONCATENATE("M 3 ",G47)</f>
       </c>
     </row>
     <row r="134">
@@ -2556,8 +2556,8 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A18:G18"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="A50:G50"/>
     <mergeCell ref="A71:G71"/>
     <mergeCell ref="A87:G87"/>
     <mergeCell ref="A108:G108"/>
@@ -2567,7 +2567,7 @@
   <printOptions horizontalCentered="true" verticalCentered="true"/>
   <pageSetup fitToHeight="0" fitToWidth="1" orientation="portrait" pageOrder="downThenOver" paperSize="9"/>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="38" max="16383" man="true"/>
+    <brk id="33" max="16383" man="true"/>
     <brk id="70" max="16383" man="true"/>
     <brk id="107" max="16383" man="true"/>
     <brk id="144" max="16383" man="true"/>
@@ -2605,35 +2605,29 @@
       <c r="J1" s="11"/>
       <c r="K1" s="11"/>
     </row>
+    <row r="5">
+      <c r="C5" s="16" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="6">
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>15</v>
+      <c r="D6" s="14"/>
+      <c r="E6" s="13">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="F7" s="14"/>
-      <c r="G7" s="12"/>
-    </row>
-    <row r="8">
-      <c r="G8" s="13">
-        <v>3</v>
-      </c>
+      <c r="C7" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="15"/>
+      <c r="E7" s="12"/>
     </row>
     <row r="9">
-      <c r="G9" s="12"/>
       <c r="H9" s="14"/>
       <c r="I9" s="12"/>
     </row>
     <row r="10">
-      <c r="C10" s="16"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="12"/>
       <c r="I10" s="12"/>
     </row>
     <row r="11">
@@ -2666,7 +2660,7 @@
     </row>
     <row r="16">
       <c r="G16" s="13">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15"/>
       <c r="I16" s="12"/>
@@ -2682,7 +2676,7 @@
     <row r="18">
       <c r="D18" s="14"/>
       <c r="E18" s="13">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F18" s="15"/>
       <c r="G18" s="12"/>
@@ -2702,41 +2696,35 @@
       </c>
     </row>
     <row r="21">
+      <c r="C21" s="16" t="s">
+        <v>25</v>
+      </c>
       <c r="K21" s="12"/>
     </row>
     <row r="22">
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16" t="s">
-        <v>25</v>
+      <c r="D22" s="14"/>
+      <c r="E22" s="13">
+        <v>3</v>
       </c>
       <c r="K22" s="12"/>
     </row>
     <row r="23">
-      <c r="F23" s="14"/>
-      <c r="G23" s="12"/>
+      <c r="C23" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="D23" s="15"/>
+      <c r="E23" s="12"/>
       <c r="K23" s="12"/>
     </row>
     <row r="24">
-      <c r="G24" s="13">
-        <v>5</v>
-      </c>
       <c r="K24" s="12"/>
     </row>
     <row r="25">
-      <c r="G25" s="12"/>
       <c r="H25" s="14"/>
       <c r="I25" s="12"/>
       <c r="K25" s="12"/>
     </row>
     <row r="26">
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="15"/>
-      <c r="G26" s="12"/>
       <c r="I26" s="12"/>
       <c r="K26" s="12"/>
     </row>
@@ -2783,7 +2771,7 @@
     <row r="34">
       <c r="D34" s="14"/>
       <c r="E34" s="13">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F34" s="15"/>
       <c r="G34" s="12"/>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t>Number of pools</t>
   </si>
@@ -67,6 +67,9 @@
     <t>Player Dojo</t>
   </si>
   <si>
+    <t>Player Number</t>
+  </si>
+  <si>
     <t>Metadata</t>
   </si>
   <si>
@@ -76,43 +79,73 @@
     <t>Team Alpha</t>
   </si>
   <si>
+    <t>K1</t>
+  </si>
+  <si>
     <t>Luke Rodriguez</t>
   </si>
   <si>
     <t>Team Beta</t>
   </si>
   <si>
+    <t>K2</t>
+  </si>
+  <si>
     <t>Michael Lewis</t>
   </si>
   <si>
     <t>Team Gamma</t>
   </si>
   <si>
+    <t>K3</t>
+  </si>
+  <si>
     <t>Nathan Lee</t>
   </si>
   <si>
     <t>Team Delta</t>
   </si>
   <si>
+    <t>K4</t>
+  </si>
+  <si>
     <t>Oliver Walker</t>
   </si>
   <si>
     <t>Team Epsilon</t>
   </si>
   <si>
+    <t>K5</t>
+  </si>
+  <si>
     <t>Paul Hall</t>
   </si>
   <si>
+    <t>K6</t>
+  </si>
+  <si>
     <t>Quentin Allen</t>
   </si>
   <si>
+    <t>K7</t>
+  </si>
+  <si>
     <t>Robert Young</t>
   </si>
   <si>
+    <t>K8</t>
+  </si>
+  <si>
     <t>Steven Hernandez</t>
   </si>
   <si>
+    <t>K9</t>
+  </si>
+  <si>
     <t>Thomas King</t>
+  </si>
+  <si>
+    <t>K10</t>
   </si>
   <si>
     <t>Shiaijo A</t>
@@ -739,8 +772,11 @@
       <c r="C2" t="s">
         <v>13</v>
       </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -748,10 +784,13 @@
         <v>0</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -759,10 +798,13 @@
         <v>1</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
@@ -770,10 +812,13 @@
         <v>2</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="6">
@@ -781,10 +826,13 @@
         <v>3</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -792,10 +840,13 @@
         <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C7" t="s">
-        <v>24</v>
+        <v>29</v>
+      </c>
+      <c r="D7" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="8">
@@ -803,10 +854,13 @@
         <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="9">
@@ -814,10 +868,13 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C9" t="s">
-        <v>18</v>
+        <v>20</v>
+      </c>
+      <c r="D9" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -825,10 +882,13 @@
         <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -836,10 +896,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C11" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="12">
@@ -847,10 +910,13 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" t="s">
         <v>29</v>
       </c>
-      <c r="C12" t="s">
-        <v>24</v>
+      <c r="D12" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1059,7 +1125,7 @@
     </row>
     <row r="13">
       <c r="E13" s="11" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="F13" s="11"/>
       <c r="G13" s="11"/>
@@ -1070,7 +1136,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>49</v>
+        <v>60</v>
       </c>
       <c r="F14" s="25"/>
       <c r="G14" s="25"/>
@@ -1080,7 +1146,7 @@
     </row>
     <row r="15">
       <c r="E15" s="25" t="s">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="F15" s="25"/>
       <c r="G15" s="25"/>
@@ -1090,7 +1156,7 @@
     </row>
     <row r="16">
       <c r="E16" s="25" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="F16" s="25"/>
       <c r="G16" s="25"/>
@@ -1100,7 +1166,7 @@
     </row>
     <row r="17">
       <c r="E17" s="25" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="F17" s="25"/>
       <c r="G17" s="25"/>
@@ -1110,7 +1176,7 @@
     </row>
     <row r="18">
       <c r="E18" s="11" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="F18" s="11"/>
       <c r="G18" s="11"/>
@@ -1120,7 +1186,7 @@
     </row>
     <row r="19">
       <c r="E19" s="11" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
@@ -1155,7 +1221,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="11" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -1166,7 +1232,7 @@
     </row>
     <row r="2">
       <c r="A2" s="11" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
@@ -1177,13 +1243,13 @@
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4">
@@ -1269,17 +1335,17 @@
         <f>'data'!$B$4</f>
       </c>
       <c r="B11" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G11" s="19" t="str">
         <f>'data'!$B$3</f>
@@ -1287,7 +1353,7 @@
     </row>
     <row r="12">
       <c r="A12" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B12" s="19" t="str">
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-",""))),1,0))</f>
@@ -1303,24 +1369,24 @@
         <f>IF(UPPER(D5)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F5," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B5," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C5," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D6)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F6," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B6," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C6," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D7)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F7," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B7," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C7," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D8)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F8," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B8," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C8," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D9)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F9," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B9," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C9," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G12" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15">
       <c r="F15" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G15" s="23"/>
     </row>
     <row r="16">
       <c r="F16" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G16" s="23"/>
     </row>
     <row r="18">
       <c r="A18" s="11" t="s">
-        <v>40</v>
+        <v>51</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1331,13 +1397,13 @@
     </row>
     <row r="19">
       <c r="A19" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G19" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20">
@@ -1423,17 +1489,17 @@
         <f>'data'!$B$7</f>
       </c>
       <c r="B27" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C27" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F27" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G27" s="19" t="str">
         <f>'data'!$B$6</f>
@@ -1441,7 +1507,7 @@
     </row>
     <row r="28">
       <c r="A28" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B28" s="19" t="str">
         <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-",""))),1,0))</f>
@@ -1457,24 +1523,24 @@
         <f>IF(UPPER(D21)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F21," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B21," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C21," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D22)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F22," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B22," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C22," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D23)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F23," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B23," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C23," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D24)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F24," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B24," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C24," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D25)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F25," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B25," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C25," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G28" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31">
       <c r="F31" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G31" s="23"/>
     </row>
     <row r="32">
       <c r="F32" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G32" s="23"/>
     </row>
     <row r="34">
       <c r="A34" s="11" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B34" s="11"/>
       <c r="C34" s="11"/>
@@ -1485,13 +1551,13 @@
     </row>
     <row r="35">
       <c r="A35" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="36">
@@ -1577,17 +1643,17 @@
         <f>'data'!$B$9</f>
       </c>
       <c r="B43" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C43" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G43" s="19" t="str">
         <f>'data'!$B$8</f>
@@ -1595,7 +1661,7 @@
     </row>
     <row r="44">
       <c r="A44" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B44" s="19" t="str">
         <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-",""))),1,0))</f>
@@ -1611,24 +1677,24 @@
         <f>IF(UPPER(D37)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F37," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B37," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C37," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D38)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F38," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B38," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C38," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D39)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F39," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B39," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C39," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D40)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F40," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B40," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C40," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D41)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F41," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B41," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C41," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G44" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47">
       <c r="F47" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G47" s="23"/>
     </row>
     <row r="48">
       <c r="F48" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G48" s="23"/>
     </row>
     <row r="50">
       <c r="A50" s="11" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="B50" s="11"/>
       <c r="C50" s="11"/>
@@ -1639,13 +1705,13 @@
     </row>
     <row r="51">
       <c r="A51" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D51" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G51" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -1731,17 +1797,17 @@
         <f>'data'!$B$12</f>
       </c>
       <c r="B59" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C59" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F59" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G59" s="19" t="str">
         <f>'data'!$B$11</f>
@@ -1749,7 +1815,7 @@
     </row>
     <row r="60">
       <c r="A60" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B60" s="19" t="str">
         <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-",""))),1,0))</f>
@@ -1765,24 +1831,24 @@
         <f>IF(UPPER(D53)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F53," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B53," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C53," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D54)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F54," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B54," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C54," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D55)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F55," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B55," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C55," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D56)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F56," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B56," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C56," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D57)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F57," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B57," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C57," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G60" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63">
       <c r="F63" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G63" s="23"/>
     </row>
     <row r="64">
       <c r="F64" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G64" s="23"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="B71" s="11"/>
       <c r="C71" s="11"/>
@@ -1793,13 +1859,13 @@
     </row>
     <row r="72">
       <c r="A72" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D72" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G72" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -1885,17 +1951,17 @@
         <f>CONCATENATE("M 2 ",G31)</f>
       </c>
       <c r="B80" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C80" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D80" s="19"/>
       <c r="E80" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F80" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G80" s="19" t="str">
         <f>'data'!$B$5</f>
@@ -1903,7 +1969,7 @@
     </row>
     <row r="81">
       <c r="A81" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B81" s="19" t="str">
         <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-",""))),1,0))</f>
@@ -1919,24 +1985,24 @@
         <f>IF(UPPER(D74)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F74," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B74," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C74," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D75)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F75," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B75," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C75," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D76)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F76," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B76," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C76," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D77)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F77," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B77," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C77," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D78)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F78," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B78," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C78," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G81" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="84">
       <c r="F84" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G84" s="23"/>
     </row>
     <row r="85">
       <c r="F85" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G85" s="23"/>
     </row>
     <row r="87">
       <c r="A87" s="11" t="s">
-        <v>44</v>
+        <v>55</v>
       </c>
       <c r="B87" s="11"/>
       <c r="C87" s="11"/>
@@ -1947,13 +2013,13 @@
     </row>
     <row r="88">
       <c r="A88" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D88" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G88" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="89">
@@ -2039,17 +2105,17 @@
         <f>CONCATENATE("M 4 ",G63)</f>
       </c>
       <c r="B96" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C96" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D96" s="19"/>
       <c r="E96" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F96" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G96" s="19" t="str">
         <f>'data'!$B$10</f>
@@ -2057,7 +2123,7 @@
     </row>
     <row r="97">
       <c r="A97" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B97" s="19" t="str">
         <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-",""))),1,0))</f>
@@ -2073,24 +2139,24 @@
         <f>IF(UPPER(D90)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F90," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B90," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C90," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D91)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F91," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B91," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C91," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D92)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F92," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B92," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C92," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D93)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F93," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B93," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C93," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D94)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F94," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B94," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C94," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G97" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="100">
       <c r="F100" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G100" s="23"/>
     </row>
     <row r="101">
       <c r="F101" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G101" s="23"/>
     </row>
     <row r="108">
       <c r="A108" s="11" t="s">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="B108" s="11"/>
       <c r="C108" s="11"/>
@@ -2101,13 +2167,13 @@
     </row>
     <row r="109">
       <c r="A109" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D109" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G109" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="110">
@@ -2193,17 +2259,17 @@
         <f>CONCATENATE("M 5 ",G84)</f>
       </c>
       <c r="B117" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C117" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D117" s="19"/>
       <c r="E117" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F117" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G117" s="19" t="str">
         <f>CONCATENATE("M 1 ",G15)</f>
@@ -2211,7 +2277,7 @@
     </row>
     <row r="118">
       <c r="A118" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B118" s="19" t="str">
         <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-",""))),1,0))</f>
@@ -2227,24 +2293,24 @@
         <f>IF(UPPER(D111)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F111," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B111," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C111," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D112)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F112," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B112," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C112," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D113)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F113," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B113," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C113," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D114)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F114," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B114," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C114," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D115)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F115," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B115," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C115," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G118" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="121">
       <c r="F121" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G121" s="23"/>
     </row>
     <row r="122">
       <c r="F122" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G122" s="23"/>
     </row>
     <row r="124">
       <c r="A124" s="11" t="s">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="B124" s="11"/>
       <c r="C124" s="11"/>
@@ -2255,13 +2321,13 @@
     </row>
     <row r="125">
       <c r="A125" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D125" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G125" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="126">
@@ -2347,17 +2413,17 @@
         <f>CONCATENATE("M 6 ",G100)</f>
       </c>
       <c r="B133" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C133" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D133" s="19"/>
       <c r="E133" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F133" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G133" s="19" t="str">
         <f>CONCATENATE("M 3 ",G47)</f>
@@ -2365,7 +2431,7 @@
     </row>
     <row r="134">
       <c r="A134" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B134" s="19" t="str">
         <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-",""))),1,0))</f>
@@ -2381,24 +2447,24 @@
         <f>IF(UPPER(D127)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F127," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B127," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C127," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D128)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F128," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B128," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C128," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D129)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F129," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B129," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C129," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D130)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F130," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B130," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C130," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D131)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F131," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B131," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C131," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G134" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="137">
       <c r="F137" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G137" s="23"/>
     </row>
     <row r="138">
       <c r="F138" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G138" s="23"/>
     </row>
     <row r="145">
       <c r="A145" s="11" t="s">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="B145" s="11"/>
       <c r="C145" s="11"/>
@@ -2409,13 +2475,13 @@
     </row>
     <row r="146">
       <c r="A146" s="21" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="D146" s="19" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="G146" s="20" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
     </row>
     <row r="147">
@@ -2501,17 +2567,17 @@
         <f>CONCATENATE("M 8 ",G137)</f>
       </c>
       <c r="B154" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C154" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="D154" s="19"/>
       <c r="E154" s="19" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="F154" s="19" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G154" s="19" t="str">
         <f>CONCATENATE("M 7 ",G121)</f>
@@ -2519,7 +2585,7 @@
     </row>
     <row r="155">
       <c r="A155" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="B155" s="19" t="str">
         <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-",""))),1,0))</f>
@@ -2535,18 +2601,18 @@
         <f>IF(UPPER(D148)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F148," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B148," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C148," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D149)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F149," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B149," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C149," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D150)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F150," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B150," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C150," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D151)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F151," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B151," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C151," ",""),"0",""),"-",""))),1,0))+IF(UPPER(D152)="X",0,IF((LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(E152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(F152," ",""),"0",""),"-","")))&gt;(LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(B152," ",""),"0",""),"-",""))+LEN(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(C152," ",""),"0",""),"-",""))),1,0))</f>
       </c>
       <c r="G155" s="19" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="158">
       <c r="F158" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="G158" s="23"/>
     </row>
     <row r="159">
       <c r="F159" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="G159" s="23"/>
     </row>
@@ -2607,7 +2673,7 @@
     </row>
     <row r="5">
       <c r="C5" s="16" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -2618,7 +2684,7 @@
     </row>
     <row r="7">
       <c r="C7" s="16" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" s="15"/>
       <c r="E7" s="12"/>
@@ -2647,7 +2713,7 @@
       <c r="C14" s="16"/>
       <c r="D14" s="16"/>
       <c r="E14" s="16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="I14" s="12"/>
       <c r="K14" s="12"/>
@@ -2668,7 +2734,7 @@
     </row>
     <row r="17">
       <c r="C17" s="16" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G17" s="12"/>
       <c r="K17" s="12"/>
@@ -2684,7 +2750,7 @@
     </row>
     <row r="19">
       <c r="C19" s="16" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D19" s="15"/>
       <c r="E19" s="12"/>
@@ -2697,7 +2763,7 @@
     </row>
     <row r="21">
       <c r="C21" s="16" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="K21" s="12"/>
     </row>
@@ -2710,7 +2776,7 @@
     </row>
     <row r="23">
       <c r="C23" s="16" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="D23" s="15"/>
       <c r="E23" s="12"/>
@@ -2746,7 +2812,7 @@
       <c r="C30" s="16"/>
       <c r="D30" s="16"/>
       <c r="E30" s="16" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="I30" s="12"/>
     </row>
@@ -2764,7 +2830,7 @@
     </row>
     <row r="33">
       <c r="C33" s="16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="G33" s="12"/>
     </row>
@@ -2778,7 +2844,7 @@
     </row>
     <row r="35">
       <c r="C35" s="16" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="D35" s="15"/>
       <c r="E35" s="12"/>
@@ -2802,80 +2868,80 @@
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">
-      <c r="A1" s="17">
-        <v>0</v>
+      <c r="A1" s="17" t="str">
+        <f>'data'!$D$3</f>
       </c>
       <c r="B1" s="18" t="str">
         <f>'data'!$B$3</f>
       </c>
     </row>
     <row r="2" ht="270" customHeight="true">
-      <c r="A2" s="17">
-        <v>1</v>
+      <c r="A2" s="17" t="str">
+        <f>'data'!$D$4</f>
       </c>
       <c r="B2" s="18" t="str">
         <f>'data'!$B$4</f>
       </c>
     </row>
     <row r="3" ht="270" customHeight="true">
-      <c r="A3" s="17">
-        <v>2</v>
+      <c r="A3" s="17" t="str">
+        <f>'data'!$D$5</f>
       </c>
       <c r="B3" s="18" t="str">
         <f>'data'!$B$5</f>
       </c>
     </row>
     <row r="4" ht="270" customHeight="true">
-      <c r="A4" s="17">
-        <v>3</v>
+      <c r="A4" s="17" t="str">
+        <f>'data'!$D$6</f>
       </c>
       <c r="B4" s="18" t="str">
         <f>'data'!$B$6</f>
       </c>
     </row>
     <row r="5" ht="270" customHeight="true">
-      <c r="A5" s="17">
-        <v>4</v>
+      <c r="A5" s="17" t="str">
+        <f>'data'!$D$7</f>
       </c>
       <c r="B5" s="18" t="str">
         <f>'data'!$B$7</f>
       </c>
     </row>
     <row r="6" ht="270" customHeight="true">
-      <c r="A6" s="17">
-        <v>5</v>
+      <c r="A6" s="17" t="str">
+        <f>'data'!$D$8</f>
       </c>
       <c r="B6" s="18" t="str">
         <f>'data'!$B$8</f>
       </c>
     </row>
     <row r="7" ht="270" customHeight="true">
-      <c r="A7" s="17">
-        <v>6</v>
+      <c r="A7" s="17" t="str">
+        <f>'data'!$D$9</f>
       </c>
       <c r="B7" s="18" t="str">
         <f>'data'!$B$9</f>
       </c>
     </row>
     <row r="8" ht="270" customHeight="true">
-      <c r="A8" s="17">
-        <v>7</v>
+      <c r="A8" s="17" t="str">
+        <f>'data'!$D$10</f>
       </c>
       <c r="B8" s="18" t="str">
         <f>'data'!$B$10</f>
       </c>
     </row>
     <row r="9" ht="270" customHeight="true">
-      <c r="A9" s="17">
-        <v>8</v>
+      <c r="A9" s="17" t="str">
+        <f>'data'!$D$11</f>
       </c>
       <c r="B9" s="18" t="str">
         <f>'data'!$B$11</f>
       </c>
     </row>
     <row r="10" ht="270" customHeight="true">
-      <c r="A10" s="17">
-        <v>9</v>
+      <c r="A10" s="17" t="str">
+        <f>'data'!$D$12</f>
       </c>
       <c r="B10" s="18" t="str">
         <f>'data'!$B$12</f>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -58,7 +58,7 @@
     <t/>
   </si>
   <si>
-    <t>Number</t>
+    <t>Draw order</t>
   </si>
   <si>
     <t>Player Name</t>
@@ -445,7 +445,7 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" t="s">
         <v>16</v>
@@ -795,7 +795,7 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
@@ -823,7 +823,7 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
@@ -837,7 +837,7 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>28</v>
@@ -851,7 +851,7 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
         <v>31</v>
@@ -865,7 +865,7 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>33</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
@@ -893,7 +893,7 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
         <v>37</v>
@@ -907,7 +907,7 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>39</v>

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -448,7 +448,7 @@
       <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" shrinkToFit="true" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -2863,8 +2863,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="30"/>
-    <col customWidth="true" max="2" min="2" width="160"/>
+    <col customWidth="true" max="1" min="1" width="40"/>
+    <col customWidth="true" max="2" min="2" width="140"/>
   </cols>
   <sheetData>
     <row r="1" ht="270" customHeight="true">

--- a/playoffs-example-small.xlsx
+++ b/playoffs-example-small.xlsx
@@ -58,7 +58,7 @@
     <t/>
   </si>
   <si>
-    <t>Draw order</t>
+    <t>Entry order</t>
   </si>
   <si>
     <t>Player Name</t>
